--- a/Fig.S9(a).xlsx
+++ b/Fig.S9(a).xlsx
@@ -372,7 +372,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -380,7 +380,7 @@
         <v>0.15598000000000001</v>
       </c>
       <c r="B8" s="1">
-        <v>-3.0861400000000002E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -388,7 +388,7 @@
         <v>0.31197000000000003</v>
       </c>
       <c r="B9" s="1">
-        <v>1.02871E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -396,7 +396,7 @@
         <v>0.46794999999999998</v>
       </c>
       <c r="B10" s="1">
-        <v>3.42904E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -412,7 +412,7 @@
         <v>0.78127000000000002</v>
       </c>
       <c r="B12" s="1">
-        <v>1.71452E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -420,7 +420,7 @@
         <v>0.93725999999999998</v>
       </c>
       <c r="B13" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -428,7 +428,7 @@
         <v>1.09324</v>
       </c>
       <c r="B14" s="1">
-        <v>1.02871E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -436,7 +436,7 @@
         <v>1.24922</v>
       </c>
       <c r="B15" s="1">
-        <v>-1.71452E-5</v>
+        <v>-3.42904E-6</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -444,7 +444,7 @@
         <v>1.4052100000000001</v>
       </c>
       <c r="B16" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -452,7 +452,7 @@
         <v>1.5625500000000001</v>
       </c>
       <c r="B17" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -460,7 +460,7 @@
         <v>1.7185299999999999</v>
       </c>
       <c r="B18" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -468,7 +468,7 @@
         <v>1.87452</v>
       </c>
       <c r="B19" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -476,7 +476,7 @@
         <v>2.0305</v>
       </c>
       <c r="B20" s="1">
-        <v>1.71452E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -484,7 +484,7 @@
         <v>2.18648</v>
       </c>
       <c r="B21" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -500,15 +500,15 @@
         <v>2.4998100000000001</v>
       </c>
       <c r="B23" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2.6557900000000001</v>
       </c>
-      <c r="B24">
-        <v>0</v>
+      <c r="B24" s="1">
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -516,7 +516,7 @@
         <v>2.8117700000000001</v>
       </c>
       <c r="B25" s="1">
-        <v>-3.42904E-6</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +524,7 @@
         <v>2.9677600000000002</v>
       </c>
       <c r="B26" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +532,7 @@
         <v>3.1251000000000002</v>
       </c>
       <c r="B27" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -540,15 +540,15 @@
         <v>3.2810800000000002</v>
       </c>
       <c r="B28" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3.4370599999999998</v>
       </c>
-      <c r="B29">
-        <v>0</v>
+      <c r="B29" s="1">
+        <v>-6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +556,7 @@
         <v>3.5930499999999999</v>
       </c>
       <c r="B30" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>-3.7719499999999997E-5</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +564,7 @@
         <v>3.7490299999999999</v>
       </c>
       <c r="B31" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +572,7 @@
         <v>3.9063699999999999</v>
       </c>
       <c r="B32" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>3.7719499999999997E-5</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +580,7 @@
         <v>4.0623500000000003</v>
       </c>
       <c r="B33" s="1">
-        <v>1.02871E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +588,7 @@
         <v>4.2183400000000004</v>
       </c>
       <c r="B34" s="1">
-        <v>1.02871E-5</v>
+        <v>8.5725999999999999E-5</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>4.37432</v>
       </c>
       <c r="B35" s="1">
-        <v>1.71452E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
         <v>4.5303000000000004</v>
       </c>
       <c r="B36" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -612,7 +612,7 @@
         <v>4.68764</v>
       </c>
       <c r="B37" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,7 +620,7 @@
         <v>4.8436300000000001</v>
       </c>
       <c r="B38" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
         <v>4.9996099999999997</v>
       </c>
       <c r="B39" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -636,7 +636,7 @@
         <v>5.1555900000000001</v>
       </c>
       <c r="B40" s="1">
-        <v>6.8580799999999999E-5</v>
+        <v>-1.71452E-5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>5.3115800000000002</v>
       </c>
       <c r="B41" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,7 +652,7 @@
         <v>5.4689199999999998</v>
       </c>
       <c r="B42" s="1">
-        <v>1.71452E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,7 +660,7 @@
         <v>5.6249000000000002</v>
       </c>
       <c r="B43" s="1">
-        <v>1.71452E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -668,15 +668,15 @@
         <v>5.7808799999999998</v>
       </c>
       <c r="B44" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5.9368699999999999</v>
       </c>
-      <c r="B45">
-        <v>0</v>
+      <c r="B45" s="1">
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>6.0928500000000003</v>
       </c>
       <c r="B46" s="1">
-        <v>1.02871E-5</v>
+        <v>4.8006600000000002E-5</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -692,7 +692,7 @@
         <v>6.2501899999999999</v>
       </c>
       <c r="B47" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -708,7 +708,7 @@
         <v>6.5621600000000004</v>
       </c>
       <c r="B49" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -716,7 +716,7 @@
         <v>6.71814</v>
       </c>
       <c r="B50" s="1">
-        <v>-1.02871E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -724,7 +724,7 @@
         <v>6.8741300000000001</v>
       </c>
       <c r="B51" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -732,7 +732,7 @@
         <v>7.0314699999999997</v>
       </c>
       <c r="B52" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -740,7 +740,7 @@
         <v>7.1874500000000001</v>
       </c>
       <c r="B53" s="1">
-        <v>8.5725999999999999E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -748,7 +748,7 @@
         <v>7.3434299999999997</v>
       </c>
       <c r="B54" s="1">
-        <v>7.8868000000000005E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>7.4994199999999998</v>
       </c>
       <c r="B55" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>-1.02871E-5</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -764,7 +764,7 @@
         <v>7.6554000000000002</v>
       </c>
       <c r="B56" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>-1.02871E-5</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +780,7 @@
         <v>7.9687200000000002</v>
       </c>
       <c r="B58" s="1">
-        <v>-1.71452E-5</v>
+        <v>7.54389E-5</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,7 +788,7 @@
         <v>8.1247100000000003</v>
       </c>
       <c r="B59" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -796,7 +796,7 @@
         <v>8.2806899999999999</v>
       </c>
       <c r="B60" s="1">
-        <v>3.42904E-5</v>
+        <v>-2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -804,7 +804,7 @@
         <v>8.4366699999999994</v>
       </c>
       <c r="B61" s="1">
-        <v>-2.7432300000000002E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -812,7 +812,7 @@
         <v>8.5940100000000008</v>
       </c>
       <c r="B62" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -820,15 +820,15 @@
         <v>8.75</v>
       </c>
       <c r="B63" s="1">
-        <v>3.42904E-6</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>8.9059799999999996</v>
       </c>
-      <c r="B64">
-        <v>0</v>
+      <c r="B64" s="1">
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -836,7 +836,7 @@
         <v>9.0619599999999991</v>
       </c>
       <c r="B65" s="1">
-        <v>3.42904E-6</v>
+        <v>-1.02871E-5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -844,7 +844,7 @@
         <v>9.2179500000000001</v>
       </c>
       <c r="B66" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>9.3752899999999997</v>
       </c>
       <c r="B67" s="1">
-        <v>3.42904E-5</v>
+        <v>4.8006600000000002E-5</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -860,7 +860,7 @@
         <v>9.5312699999999992</v>
       </c>
       <c r="B68" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
         <v>9.6872500000000006</v>
       </c>
       <c r="B69" s="1">
-        <v>6.8580799999999999E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>9.8432399999999998</v>
       </c>
       <c r="B70" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -884,7 +884,7 @@
         <v>9.9992199999999993</v>
       </c>
       <c r="B71" s="1">
-        <v>5.4864699999999997E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -892,7 +892,7 @@
         <v>10.156560000000001</v>
       </c>
       <c r="B72" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -900,15 +900,15 @@
         <v>10.31254</v>
       </c>
       <c r="B73" s="1">
-        <v>1.02871E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10.468529999999999</v>
       </c>
-      <c r="B74">
-        <v>0</v>
+      <c r="B74" s="1">
+        <v>6.5151800000000002E-5</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -916,7 +916,7 @@
         <v>10.624510000000001</v>
       </c>
       <c r="B75" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -932,7 +932,7 @@
         <v>10.93783</v>
       </c>
       <c r="B77" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -940,7 +940,7 @@
         <v>11.093819999999999</v>
       </c>
       <c r="B78" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -948,7 +948,7 @@
         <v>11.2498</v>
       </c>
       <c r="B79" s="1">
-        <v>1.71452E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -956,7 +956,7 @@
         <v>11.40578</v>
       </c>
       <c r="B80" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -964,7 +964,7 @@
         <v>11.561769999999999</v>
       </c>
       <c r="B81" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -972,7 +972,7 @@
         <v>11.719110000000001</v>
       </c>
       <c r="B82" s="1">
-        <v>7.8868000000000005E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>11.87509</v>
       </c>
       <c r="B83" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>-1.02871E-5</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -988,7 +988,7 @@
         <v>12.03107</v>
       </c>
       <c r="B84" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -996,7 +996,7 @@
         <v>12.187060000000001</v>
       </c>
       <c r="B85" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>7.8868000000000005E-5</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -1004,7 +1004,7 @@
         <v>12.34304</v>
       </c>
       <c r="B86" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1012,7 +1012,7 @@
         <v>12.50038</v>
       </c>
       <c r="B87" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1020,7 +1020,7 @@
         <v>12.656370000000001</v>
       </c>
       <c r="B88" s="1">
-        <v>-1.71452E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1028,7 +1028,7 @@
         <v>12.81235</v>
       </c>
       <c r="B89" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>9.25841E-5</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1036,7 +1036,7 @@
         <v>12.96833</v>
       </c>
       <c r="B90" s="1">
-        <v>1.71452E-5</v>
+        <v>4.4577499999999998E-5</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1044,15 +1044,15 @@
         <v>13.124320000000001</v>
       </c>
       <c r="B91" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>13.28166</v>
       </c>
-      <c r="B92">
-        <v>0</v>
+      <c r="B92" s="1">
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -1060,7 +1060,7 @@
         <v>13.43764</v>
       </c>
       <c r="B93" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -1068,7 +1068,7 @@
         <v>13.59362</v>
       </c>
       <c r="B94" s="1">
-        <v>-1.3716199999999999E-5</v>
+        <v>-2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1076,7 +1076,7 @@
         <v>13.749610000000001</v>
       </c>
       <c r="B95" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1084,7 +1084,7 @@
         <v>13.90559</v>
       </c>
       <c r="B96" s="1">
-        <v>7.8868000000000005E-5</v>
+        <v>-6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>14.06293</v>
       </c>
       <c r="B97" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
         <v>14.218909999999999</v>
       </c>
       <c r="B98" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>4.4577499999999998E-5</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -1108,7 +1108,7 @@
         <v>14.3749</v>
       </c>
       <c r="B99" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>6.5151800000000002E-5</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,7 +1116,7 @@
         <v>14.53088</v>
       </c>
       <c r="B100" s="1">
-        <v>1.71452E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
         <v>14.686859999999999</v>
       </c>
       <c r="B101" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -1132,7 +1132,7 @@
         <v>14.844200000000001</v>
       </c>
       <c r="B102" s="1">
-        <v>6.8580799999999999E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -1140,7 +1140,7 @@
         <v>15.00019</v>
       </c>
       <c r="B103" s="1">
-        <v>-1.3716199999999999E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -1148,7 +1148,7 @@
         <v>15.156169999999999</v>
       </c>
       <c r="B104" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>15.312150000000001</v>
       </c>
       <c r="B105" s="1">
-        <v>3.42904E-6</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1164,7 +1164,7 @@
         <v>15.46814</v>
       </c>
       <c r="B106" s="1">
-        <v>3.42904E-5</v>
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>15.62548</v>
       </c>
       <c r="B107" s="1">
-        <v>1.71452E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -1180,7 +1180,7 @@
         <v>15.781459999999999</v>
       </c>
       <c r="B108" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>1.09E-3</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>15.93744</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>4.3899999999999998E-3</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -1196,7 +1196,7 @@
         <v>16.093430000000001</v>
       </c>
       <c r="B110" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>1.004E-2</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -1204,7 +1204,7 @@
         <v>16.249410000000001</v>
       </c>
       <c r="B111" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>1.553E-2</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
         <v>16.406749999999999</v>
       </c>
       <c r="B112" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>2.103E-2</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -1220,7 +1220,7 @@
         <v>16.562729999999998</v>
       </c>
       <c r="B113" s="1">
-        <v>-3.42904E-6</v>
+        <v>2.5149999999999999E-2</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -1228,7 +1228,7 @@
         <v>16.718720000000001</v>
       </c>
       <c r="B114" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>2.8420000000000001E-2</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -1236,7 +1236,7 @@
         <v>16.874700000000001</v>
       </c>
       <c r="B115" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>3.0720000000000001E-2</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
         <v>17.03069</v>
       </c>
       <c r="B116" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>3.2370000000000003E-2</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -1252,7 +1252,7 @@
         <v>17.188020000000002</v>
       </c>
       <c r="B117" s="1">
-        <v>1.02871E-5</v>
+        <v>3.4090000000000002E-2</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>17.344010000000001</v>
       </c>
       <c r="B118" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>3.5200000000000002E-2</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
         <v>17.49999</v>
       </c>
       <c r="B119" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>3.5959999999999999E-2</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -1276,7 +1276,7 @@
         <v>17.65598</v>
       </c>
       <c r="B120" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>3.6450000000000003E-2</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
         <v>17.811959999999999</v>
       </c>
       <c r="B121" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>3.6839999999999998E-2</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -1292,7 +1292,7 @@
         <v>17.9693</v>
       </c>
       <c r="B122" s="1">
-        <v>3.42904E-5</v>
+        <v>3.7150000000000002E-2</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -1300,7 +1300,7 @@
         <v>18.12528</v>
       </c>
       <c r="B123" s="1">
-        <v>-1.02871E-5</v>
+        <v>3.7420000000000002E-2</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -1308,7 +1308,7 @@
         <v>18.281269999999999</v>
       </c>
       <c r="B124" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>3.7780000000000001E-2</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -1316,7 +1316,7 @@
         <v>18.437249999999999</v>
       </c>
       <c r="B125" s="1">
-        <v>3.42904E-5</v>
+        <v>3.8129999999999997E-2</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -1324,7 +1324,7 @@
         <v>18.593229999999998</v>
       </c>
       <c r="B126" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>3.8460000000000001E-2</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
         <v>18.75057</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>3.8760000000000003E-2</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>18.906559999999999</v>
       </c>
       <c r="B128" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>3.9070000000000001E-2</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -1348,7 +1348,7 @@
         <v>19.062539999999998</v>
       </c>
       <c r="B129" s="1">
-        <v>-3.42904E-6</v>
+        <v>3.9469999999999998E-2</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -1356,7 +1356,7 @@
         <v>19.218520000000002</v>
       </c>
       <c r="B130" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>3.9730000000000001E-2</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -1364,7 +1364,7 @@
         <v>19.374510000000001</v>
       </c>
       <c r="B131" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>4.0090000000000001E-2</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -1372,7 +1372,7 @@
         <v>19.531849999999999</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>4.036E-2</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -1380,7 +1380,7 @@
         <v>19.687830000000002</v>
       </c>
       <c r="B133" s="1">
-        <v>-1.02871E-5</v>
+        <v>4.0730000000000002E-2</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -1388,7 +1388,7 @@
         <v>19.843810000000001</v>
       </c>
       <c r="B134" s="1">
-        <v>1.71452E-5</v>
+        <v>4.1050000000000003E-2</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -1396,7 +1396,7 @@
         <v>19.9998</v>
       </c>
       <c r="B135" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>4.1360000000000001E-2</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -1404,7 +1404,7 @@
         <v>20.15578</v>
       </c>
       <c r="B136" s="1">
-        <v>1.02871E-5</v>
+        <v>4.1709999999999997E-2</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -1412,7 +1412,7 @@
         <v>20.313120000000001</v>
       </c>
       <c r="B137" s="1">
-        <v>3.42904E-5</v>
+        <v>4.2040000000000001E-2</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
         <v>20.469100000000001</v>
       </c>
       <c r="B138" s="1">
-        <v>3.42904E-6</v>
+        <v>4.233E-2</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -1428,7 +1428,7 @@
         <v>20.62509</v>
       </c>
       <c r="B139" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>4.2630000000000001E-2</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -1436,7 +1436,7 @@
         <v>20.78107</v>
       </c>
       <c r="B140" s="1">
-        <v>1.71452E-5</v>
+        <v>4.2930000000000003E-2</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -1444,7 +1444,7 @@
         <v>20.937049999999999</v>
       </c>
       <c r="B141" s="1">
-        <v>1.0972900000000001E-4</v>
+        <v>4.3310000000000001E-2</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -1452,7 +1452,7 @@
         <v>21.094390000000001</v>
       </c>
       <c r="B142" s="1">
-        <v>7.3381499999999997E-4</v>
+        <v>4.3589999999999997E-2</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -1460,7 +1460,7 @@
         <v>21.25038</v>
       </c>
       <c r="B143">
-        <v>2.7029999999999998E-2</v>
+        <v>4.3959999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -1468,7 +1468,7 @@
         <v>21.406359999999999</v>
       </c>
       <c r="B144">
-        <v>3.7319999999999999E-2</v>
+        <v>4.4229999999999998E-2</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -1476,7 +1476,7 @@
         <v>21.562339999999999</v>
       </c>
       <c r="B145">
-        <v>3.8129999999999997E-2</v>
+        <v>4.4580000000000002E-2</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -1484,7 +1484,7 @@
         <v>21.718330000000002</v>
       </c>
       <c r="B146">
-        <v>3.8379999999999997E-2</v>
+        <v>4.4880000000000003E-2</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21.87567</v>
       </c>
       <c r="B147">
-        <v>3.866E-2</v>
+        <v>4.5240000000000002E-2</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -1500,7 +1500,7 @@
         <v>22.031649999999999</v>
       </c>
       <c r="B148">
-        <v>3.8929999999999999E-2</v>
+        <v>4.5569999999999999E-2</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -1508,7 +1508,7 @@
         <v>22.187639999999998</v>
       </c>
       <c r="B149">
-        <v>3.9190000000000003E-2</v>
+        <v>4.5870000000000001E-2</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -1516,7 +1516,7 @@
         <v>22.343620000000001</v>
       </c>
       <c r="B150">
-        <v>3.9530000000000003E-2</v>
+        <v>4.6170000000000003E-2</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -1524,7 +1524,7 @@
         <v>22.499600000000001</v>
       </c>
       <c r="B151">
-        <v>3.9759999999999997E-2</v>
+        <v>4.6580000000000003E-2</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -1532,7 +1532,7 @@
         <v>22.656939999999999</v>
       </c>
       <c r="B152">
-        <v>4.002E-2</v>
+        <v>4.6820000000000001E-2</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -1540,7 +1540,7 @@
         <v>22.812930000000001</v>
       </c>
       <c r="B153">
-        <v>4.0280000000000003E-2</v>
+        <v>4.7210000000000002E-2</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -1548,7 +1548,7 @@
         <v>22.968910000000001</v>
       </c>
       <c r="B154">
-        <v>4.0599999999999997E-2</v>
+        <v>4.7480000000000001E-2</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -1556,7 +1556,7 @@
         <v>23.124890000000001</v>
       </c>
       <c r="B155">
-        <v>4.0910000000000002E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -1564,7 +1564,7 @@
         <v>23.28088</v>
       </c>
       <c r="B156">
-        <v>4.1160000000000002E-2</v>
+        <v>4.8140000000000002E-2</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -1572,7 +1572,7 @@
         <v>23.438220000000001</v>
       </c>
       <c r="B157">
-        <v>4.1410000000000002E-2</v>
+        <v>4.8520000000000001E-2</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
         <v>23.594200000000001</v>
       </c>
       <c r="B158">
-        <v>4.1709999999999997E-2</v>
+        <v>4.8840000000000001E-2</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -1588,7 +1588,7 @@
         <v>23.75018</v>
       </c>
       <c r="B159">
-        <v>4.19E-2</v>
+        <v>4.9119999999999997E-2</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
         <v>23.906169999999999</v>
       </c>
       <c r="B160">
-        <v>4.2299999999999997E-2</v>
+        <v>4.9459999999999997E-2</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -1604,7 +1604,7 @@
         <v>24.062149999999999</v>
       </c>
       <c r="B161">
-        <v>4.2549999999999998E-2</v>
+        <v>4.9770000000000002E-2</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -1612,7 +1612,7 @@
         <v>24.21949</v>
       </c>
       <c r="B162">
-        <v>4.283E-2</v>
+        <v>5.008E-2</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -1620,7 +1620,7 @@
         <v>24.37547</v>
       </c>
       <c r="B163">
-        <v>4.3110000000000002E-2</v>
+        <v>5.0470000000000001E-2</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -1628,7 +1628,7 @@
         <v>24.531459999999999</v>
       </c>
       <c r="B164">
-        <v>4.3360000000000003E-2</v>
+        <v>5.076E-2</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -1636,7 +1636,7 @@
         <v>24.687439999999999</v>
       </c>
       <c r="B165">
-        <v>4.3709999999999999E-2</v>
+        <v>5.11E-2</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>24.843419999999998</v>
       </c>
       <c r="B166">
-        <v>4.3970000000000002E-2</v>
+        <v>5.1380000000000002E-2</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
         <v>25.00076</v>
       </c>
       <c r="B167">
-        <v>4.4209999999999999E-2</v>
+        <v>5.1720000000000002E-2</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -1660,7 +1660,7 @@
         <v>25.156749999999999</v>
       </c>
       <c r="B168">
-        <v>4.4420000000000001E-2</v>
+        <v>5.2049999999999999E-2</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -1668,7 +1668,7 @@
         <v>25.312729999999998</v>
       </c>
       <c r="B169">
-        <v>4.4699999999999997E-2</v>
+        <v>5.2339999999999998E-2</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -1676,7 +1676,7 @@
         <v>25.468710000000002</v>
       </c>
       <c r="B170">
-        <v>4.5030000000000001E-2</v>
+        <v>5.2639999999999999E-2</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -1684,7 +1684,7 @@
         <v>25.624700000000001</v>
       </c>
       <c r="B171">
-        <v>4.5289999999999997E-2</v>
+        <v>5.2970000000000003E-2</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -1692,7 +1692,7 @@
         <v>25.782039999999999</v>
       </c>
       <c r="B172">
-        <v>4.5589999999999999E-2</v>
+        <v>5.3240000000000003E-2</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -1700,7 +1700,7 @@
         <v>25.938020000000002</v>
       </c>
       <c r="B173">
-        <v>4.5870000000000001E-2</v>
+        <v>5.3699999999999998E-2</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -1708,7 +1708,7 @@
         <v>26.094000000000001</v>
       </c>
       <c r="B174">
-        <v>4.6120000000000001E-2</v>
+        <v>5.4019999999999999E-2</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -1716,7 +1716,7 @@
         <v>26.24999</v>
       </c>
       <c r="B175">
-        <v>4.6429999999999999E-2</v>
+        <v>5.4330000000000003E-2</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
         <v>26.40597</v>
       </c>
       <c r="B176">
-        <v>4.6690000000000002E-2</v>
+        <v>5.4690000000000003E-2</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -1732,7 +1732,7 @@
         <v>26.563310000000001</v>
       </c>
       <c r="B177">
-        <v>4.6960000000000002E-2</v>
+        <v>5.4969999999999998E-2</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
         <v>26.719290000000001</v>
       </c>
       <c r="B178">
-        <v>4.7219999999999998E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -1748,7 +1748,7 @@
         <v>26.87528</v>
       </c>
       <c r="B179">
-        <v>4.7509999999999997E-2</v>
+        <v>5.5579999999999997E-2</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -1756,7 +1756,7 @@
         <v>27.03126</v>
       </c>
       <c r="B180">
-        <v>4.7809999999999998E-2</v>
+        <v>5.5890000000000002E-2</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -1764,7 +1764,7 @@
         <v>27.187239999999999</v>
       </c>
       <c r="B181">
-        <v>4.8039999999999999E-2</v>
+        <v>5.6219999999999999E-2</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
         <v>27.34459</v>
       </c>
       <c r="B182">
-        <v>4.8340000000000001E-2</v>
+        <v>5.6559999999999999E-2</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -1780,7 +1780,7 @@
         <v>27.50057</v>
       </c>
       <c r="B183">
-        <v>4.863E-2</v>
+        <v>5.6849999999999998E-2</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -1788,7 +1788,7 @@
         <v>27.656549999999999</v>
       </c>
       <c r="B184">
-        <v>4.8869999999999997E-2</v>
+        <v>5.7290000000000001E-2</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>27.812529999999999</v>
       </c>
       <c r="B185">
-        <v>4.9160000000000002E-2</v>
+        <v>5.7619999999999998E-2</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -1804,7 +1804,7 @@
         <v>27.968520000000002</v>
       </c>
       <c r="B186">
-        <v>4.9430000000000002E-2</v>
+        <v>5.7880000000000001E-2</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -1812,7 +1812,7 @@
         <v>28.125859999999999</v>
       </c>
       <c r="B187">
-        <v>4.9689999999999998E-2</v>
+        <v>5.824E-2</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -1820,7 +1820,7 @@
         <v>28.281839999999999</v>
       </c>
       <c r="B188">
-        <v>0.05</v>
+        <v>5.851E-2</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -1828,7 +1828,7 @@
         <v>28.437830000000002</v>
       </c>
       <c r="B189">
-        <v>5.0259999999999999E-2</v>
+        <v>5.885E-2</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -1836,7 +1836,7 @@
         <v>28.593810000000001</v>
       </c>
       <c r="B190">
-        <v>5.0520000000000002E-2</v>
+        <v>5.9200000000000003E-2</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -1844,7 +1844,7 @@
         <v>28.749790000000001</v>
       </c>
       <c r="B191">
-        <v>5.0869999999999999E-2</v>
+        <v>5.9569999999999998E-2</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -1852,7 +1852,7 @@
         <v>28.907129999999999</v>
       </c>
       <c r="B192">
-        <v>5.1139999999999998E-2</v>
+        <v>5.9810000000000002E-2</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -1860,7 +1860,7 @@
         <v>29.063120000000001</v>
       </c>
       <c r="B193">
-        <v>5.142E-2</v>
+        <v>6.0150000000000002E-2</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -1868,7 +1868,7 @@
         <v>29.219100000000001</v>
       </c>
       <c r="B194">
-        <v>5.1679999999999997E-2</v>
+        <v>6.0409999999999998E-2</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -1876,7 +1876,7 @@
         <v>29.375080000000001</v>
       </c>
       <c r="B195">
-        <v>5.1950000000000003E-2</v>
+        <v>6.0819999999999999E-2</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -1884,7 +1884,7 @@
         <v>29.53107</v>
       </c>
       <c r="B196">
-        <v>5.219E-2</v>
+        <v>6.1120000000000001E-2</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -1892,7 +1892,7 @@
         <v>29.688410000000001</v>
       </c>
       <c r="B197">
-        <v>5.2510000000000001E-2</v>
+        <v>6.1460000000000001E-2</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -1900,7 +1900,7 @@
         <v>29.844390000000001</v>
       </c>
       <c r="B198">
-        <v>5.2769999999999997E-2</v>
+        <v>6.1769999999999999E-2</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -1908,7 +1908,7 @@
         <v>30.00037</v>
       </c>
       <c r="B199">
-        <v>5.3089999999999998E-2</v>
+        <v>6.2170000000000003E-2</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -1916,7 +1916,7 @@
         <v>30.156359999999999</v>
       </c>
       <c r="B200">
-        <v>5.3310000000000003E-2</v>
+        <v>6.2469999999999998E-2</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -1924,7 +1924,7 @@
         <v>30.312339999999999</v>
       </c>
       <c r="B201">
-        <v>5.3629999999999997E-2</v>
+        <v>6.2740000000000004E-2</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -1932,7 +1932,7 @@
         <v>30.46968</v>
       </c>
       <c r="B202">
-        <v>5.3839999999999999E-2</v>
+        <v>6.3149999999999998E-2</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
         <v>30.62566</v>
       </c>
       <c r="B203">
-        <v>5.4100000000000002E-2</v>
+        <v>6.3399999999999998E-2</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>30.781649999999999</v>
       </c>
       <c r="B204">
-        <v>5.4350000000000002E-2</v>
+        <v>6.3780000000000003E-2</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -1956,7 +1956,7 @@
         <v>30.937629999999999</v>
       </c>
       <c r="B205">
-        <v>5.475E-2</v>
+        <v>6.4049999999999996E-2</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -1964,7 +1964,7 @@
         <v>31.093610000000002</v>
       </c>
       <c r="B206">
-        <v>5.4969999999999998E-2</v>
+        <v>6.4360000000000001E-2</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -1972,7 +1972,7 @@
         <v>31.25095</v>
       </c>
       <c r="B207">
-        <v>5.5300000000000002E-2</v>
+        <v>6.4729999999999996E-2</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -1980,7 +1980,7 @@
         <v>31.406939999999999</v>
       </c>
       <c r="B208">
-        <v>5.552E-2</v>
+        <v>6.5049999999999997E-2</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -1988,7 +1988,7 @@
         <v>31.562919999999998</v>
       </c>
       <c r="B209">
-        <v>5.5809999999999998E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -1996,7 +1996,7 @@
         <v>31.718900000000001</v>
       </c>
       <c r="B210">
-        <v>5.6090000000000001E-2</v>
+        <v>6.5640000000000004E-2</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <v>31.874890000000001</v>
       </c>
       <c r="B211">
-        <v>5.6399999999999999E-2</v>
+        <v>6.6019999999999995E-2</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
         <v>32.032229999999998</v>
       </c>
       <c r="B212">
-        <v>5.6649999999999999E-2</v>
+        <v>6.6309999999999994E-2</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
         <v>32.188209999999998</v>
       </c>
       <c r="B213">
-        <v>5.6980000000000003E-2</v>
+        <v>6.6650000000000001E-2</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -2028,7 +2028,7 @@
         <v>32.344200000000001</v>
       </c>
       <c r="B214">
-        <v>5.7169999999999999E-2</v>
+        <v>6.6979999999999998E-2</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>32.50018</v>
       </c>
       <c r="B215">
-        <v>5.747E-2</v>
+        <v>6.7379999999999995E-2</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -2044,7 +2044,7 @@
         <v>32.65616</v>
       </c>
       <c r="B216">
-        <v>5.7759999999999999E-2</v>
+        <v>6.7669999999999994E-2</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -2052,7 +2052,7 @@
         <v>32.813499999999998</v>
       </c>
       <c r="B217">
-        <v>5.8040000000000001E-2</v>
+        <v>6.7970000000000003E-2</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -2060,7 +2060,7 @@
         <v>32.96949</v>
       </c>
       <c r="B218">
-        <v>5.8310000000000001E-2</v>
+        <v>6.8250000000000005E-2</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -2068,7 +2068,7 @@
         <v>33.12547</v>
       </c>
       <c r="B219">
-        <v>5.8560000000000001E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>33.28145</v>
       </c>
       <c r="B220">
-        <v>5.8860000000000003E-2</v>
+        <v>6.8890000000000007E-2</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -2084,7 +2084,7 @@
         <v>33.437440000000002</v>
       </c>
       <c r="B221">
-        <v>5.917E-2</v>
+        <v>6.9220000000000004E-2</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>33.59478</v>
       </c>
       <c r="B222">
-        <v>5.9360000000000003E-2</v>
+        <v>6.9599999999999995E-2</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>33.75076</v>
       </c>
       <c r="B223">
-        <v>5.969E-2</v>
+        <v>6.9879999999999998E-2</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -2108,7 +2108,7 @@
         <v>33.906739999999999</v>
       </c>
       <c r="B224">
-        <v>5.9959999999999999E-2</v>
+        <v>7.0209999999999995E-2</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -2116,7 +2116,7 @@
         <v>34.062730000000002</v>
       </c>
       <c r="B225">
-        <v>6.0319999999999999E-2</v>
+        <v>7.0639999999999994E-2</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -2124,7 +2124,7 @@
         <v>34.218710000000002</v>
       </c>
       <c r="B226">
-        <v>6.053E-2</v>
+        <v>7.0879999999999999E-2</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>34.376049999999999</v>
       </c>
       <c r="B227">
-        <v>6.08E-2</v>
+        <v>7.1179999999999993E-2</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -2140,7 +2140,7 @@
         <v>34.532029999999999</v>
       </c>
       <c r="B228">
-        <v>6.1080000000000002E-2</v>
+        <v>7.1529999999999996E-2</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -2148,7 +2148,7 @@
         <v>34.688009999999998</v>
       </c>
       <c r="B229">
-        <v>6.1379999999999997E-2</v>
+        <v>7.1879999999999999E-2</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -2156,7 +2156,7 @@
         <v>34.844000000000001</v>
       </c>
       <c r="B230">
-        <v>6.166E-2</v>
+        <v>7.2160000000000002E-2</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -2164,7 +2164,7 @@
         <v>34.999980000000001</v>
       </c>
       <c r="B231">
-        <v>6.1949999999999998E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -2172,7 +2172,7 @@
         <v>35.157319999999999</v>
       </c>
       <c r="B232">
-        <v>6.2239999999999997E-2</v>
+        <v>7.2900000000000006E-2</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>35.313299999999998</v>
       </c>
       <c r="B233">
-        <v>6.2469999999999998E-2</v>
+        <v>7.3169999999999999E-2</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -2188,7 +2188,7 @@
         <v>35.469290000000001</v>
       </c>
       <c r="B234">
-        <v>6.2789999999999999E-2</v>
+        <v>7.3440000000000005E-2</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -2196,7 +2196,7 @@
         <v>35.62527</v>
       </c>
       <c r="B235">
-        <v>6.3E-2</v>
+        <v>7.3789999999999994E-2</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>35.781260000000003</v>
       </c>
       <c r="B236">
-        <v>6.3329999999999997E-2</v>
+        <v>7.4149999999999994E-2</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>35.938600000000001</v>
       </c>
       <c r="B237">
-        <v>6.3589999999999994E-2</v>
+        <v>7.4380000000000002E-2</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -2220,7 +2220,7 @@
         <v>36.094580000000001</v>
       </c>
       <c r="B238">
-        <v>6.3839999999999994E-2</v>
+        <v>7.4810000000000001E-2</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -2228,7 +2228,7 @@
         <v>36.25056</v>
       </c>
       <c r="B239">
-        <v>6.4159999999999995E-2</v>
+        <v>7.51E-2</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -2236,7 +2236,7 @@
         <v>36.406550000000003</v>
       </c>
       <c r="B240">
-        <v>6.4420000000000005E-2</v>
+        <v>7.5410000000000005E-2</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -2244,7 +2244,7 @@
         <v>36.562530000000002</v>
       </c>
       <c r="B241">
-        <v>6.4659999999999995E-2</v>
+        <v>7.5810000000000002E-2</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>36.71987</v>
       </c>
       <c r="B242">
-        <v>6.5019999999999994E-2</v>
+        <v>7.6109999999999997E-2</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -2260,7 +2260,7 @@
         <v>36.87585</v>
       </c>
       <c r="B243">
-        <v>6.5240000000000006E-2</v>
+        <v>7.6429999999999998E-2</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -2268,7 +2268,7 @@
         <v>37.031840000000003</v>
       </c>
       <c r="B244">
-        <v>6.5559999999999993E-2</v>
+        <v>7.6719999999999997E-2</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,7 +2276,7 @@
         <v>37.187820000000002</v>
       </c>
       <c r="B245">
-        <v>6.5839999999999996E-2</v>
+        <v>7.7130000000000004E-2</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -2284,7 +2284,7 @@
         <v>37.343800000000002</v>
       </c>
       <c r="B246">
-        <v>6.6119999999999998E-2</v>
+        <v>7.7399999999999997E-2</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -2292,7 +2292,7 @@
         <v>37.501139999999999</v>
       </c>
       <c r="B247">
-        <v>6.6420000000000007E-2</v>
+        <v>7.7740000000000004E-2</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>37.657130000000002</v>
       </c>
       <c r="B248">
-        <v>6.6669999999999993E-2</v>
+        <v>7.8079999999999997E-2</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -2308,7 +2308,7 @@
         <v>37.813110000000002</v>
       </c>
       <c r="B249">
-        <v>6.6949999999999996E-2</v>
+        <v>7.8289999999999998E-2</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -2316,7 +2316,7 @@
         <v>37.969090000000001</v>
       </c>
       <c r="B250">
-        <v>6.7229999999999998E-2</v>
+        <v>7.8719999999999998E-2</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -2324,7 +2324,7 @@
         <v>38.125079999999997</v>
       </c>
       <c r="B251">
-        <v>6.7460000000000006E-2</v>
+        <v>7.9070000000000001E-2</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <v>38.282420000000002</v>
       </c>
       <c r="B252">
-        <v>6.7729999999999999E-2</v>
+        <v>7.9380000000000006E-2</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>38.438400000000001</v>
       </c>
       <c r="B253">
-        <v>6.8040000000000003E-2</v>
+        <v>7.9689999999999997E-2</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -2348,7 +2348,7 @@
         <v>38.594389999999997</v>
       </c>
       <c r="B254">
-        <v>6.83E-2</v>
+        <v>7.9930000000000001E-2</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -2356,7 +2356,7 @@
         <v>38.750369999999997</v>
       </c>
       <c r="B255">
-        <v>6.862E-2</v>
+        <v>8.0320000000000003E-2</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
         <v>38.906350000000003</v>
       </c>
       <c r="B256">
-        <v>6.8879999999999997E-2</v>
+        <v>8.072E-2</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -2372,7 +2372,7 @@
         <v>39.063690000000001</v>
       </c>
       <c r="B257">
-        <v>6.9169999999999995E-2</v>
+        <v>8.0990000000000006E-2</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -2380,7 +2380,7 @@
         <v>39.219679999999997</v>
       </c>
       <c r="B258">
-        <v>6.9400000000000003E-2</v>
+        <v>8.1309999999999993E-2</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -2388,7 +2388,7 @@
         <v>39.375660000000003</v>
       </c>
       <c r="B259">
-        <v>6.9760000000000003E-2</v>
+        <v>8.1689999999999999E-2</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -2396,7 +2396,7 @@
         <v>39.531640000000003</v>
       </c>
       <c r="B260">
-        <v>6.9970000000000004E-2</v>
+        <v>8.1909999999999997E-2</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>39.687629999999999</v>
       </c>
       <c r="B261">
-        <v>7.0309999999999997E-2</v>
+        <v>8.2320000000000004E-2</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -2412,7 +2412,7 @@
         <v>39.844970000000004</v>
       </c>
       <c r="B262">
-        <v>7.059E-2</v>
+        <v>8.2600000000000007E-2</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -2420,7 +2420,7 @@
         <v>39.999589999999998</v>
       </c>
       <c r="B263">
-        <v>7.0870000000000002E-2</v>
+        <v>8.2960000000000006E-2</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -2428,7 +2428,7 @@
         <v>39.844970000000004</v>
       </c>
       <c r="B264">
-        <v>7.0650000000000004E-2</v>
+        <v>8.2640000000000005E-2</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -2436,7 +2436,7 @@
         <v>39.687629999999999</v>
       </c>
       <c r="B265">
-        <v>7.0370000000000002E-2</v>
+        <v>8.2239999999999994E-2</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -2444,7 +2444,7 @@
         <v>39.531640000000003</v>
       </c>
       <c r="B266">
-        <v>7.0040000000000005E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>39.375660000000003</v>
       </c>
       <c r="B267">
-        <v>6.9779999999999995E-2</v>
+        <v>8.1680000000000003E-2</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -2460,7 +2460,7 @@
         <v>39.219679999999997</v>
       </c>
       <c r="B268">
-        <v>6.9529999999999995E-2</v>
+        <v>8.1390000000000004E-2</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <v>39.063690000000001</v>
       </c>
       <c r="B269">
-        <v>6.923E-2</v>
+        <v>8.1049999999999997E-2</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
         <v>38.906350000000003</v>
       </c>
       <c r="B270">
-        <v>6.8909999999999999E-2</v>
+        <v>8.0729999999999996E-2</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
         <v>38.750369999999997</v>
       </c>
       <c r="B271">
-        <v>6.8659999999999999E-2</v>
+        <v>8.0379999999999993E-2</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -2492,7 +2492,7 @@
         <v>38.594389999999997</v>
       </c>
       <c r="B272">
-        <v>6.8379999999999996E-2</v>
+        <v>8.0049999999999996E-2</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -2500,7 +2500,7 @@
         <v>38.438400000000001</v>
       </c>
       <c r="B273">
-        <v>6.8089999999999998E-2</v>
+        <v>7.9729999999999995E-2</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -2508,7 +2508,7 @@
         <v>38.282420000000002</v>
       </c>
       <c r="B274">
-        <v>6.7809999999999995E-2</v>
+        <v>7.9450000000000007E-2</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -2516,7 +2516,7 @@
         <v>38.125079999999997</v>
       </c>
       <c r="B275">
-        <v>6.7530000000000007E-2</v>
+        <v>7.9060000000000005E-2</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -2524,7 +2524,7 @@
         <v>37.969090000000001</v>
       </c>
       <c r="B276">
-        <v>6.7229999999999998E-2</v>
+        <v>7.8770000000000007E-2</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
         <v>37.813110000000002</v>
       </c>
       <c r="B277">
-        <v>6.6930000000000003E-2</v>
+        <v>7.8450000000000006E-2</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -2540,7 +2540,7 @@
         <v>37.657130000000002</v>
       </c>
       <c r="B278">
-        <v>6.6729999999999998E-2</v>
+        <v>7.8170000000000003E-2</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>37.501139999999999</v>
       </c>
       <c r="B279">
-        <v>6.6460000000000005E-2</v>
+        <v>7.7829999999999996E-2</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>37.343800000000002</v>
       </c>
       <c r="B280">
-        <v>6.6170000000000007E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
         <v>37.187820000000002</v>
       </c>
       <c r="B281">
-        <v>6.583E-2</v>
+        <v>7.7119999999999994E-2</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -2572,7 +2572,7 @@
         <v>37.031840000000003</v>
       </c>
       <c r="B282">
-        <v>6.5640000000000004E-2</v>
+        <v>7.6810000000000003E-2</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -2580,7 +2580,7 @@
         <v>36.87585</v>
       </c>
       <c r="B283">
-        <v>6.5259999999999999E-2</v>
+        <v>7.646E-2</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -2588,7 +2588,7 @@
         <v>36.71987</v>
       </c>
       <c r="B284">
-        <v>6.5019999999999994E-2</v>
+        <v>7.6149999999999995E-2</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -2596,7 +2596,7 @@
         <v>36.562530000000002</v>
       </c>
       <c r="B285">
-        <v>6.4710000000000004E-2</v>
+        <v>7.5840000000000005E-2</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -2604,7 +2604,7 @@
         <v>36.406550000000003</v>
       </c>
       <c r="B286">
-        <v>6.4439999999999997E-2</v>
+        <v>7.5550000000000006E-2</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -2612,7 +2612,7 @@
         <v>36.25056</v>
       </c>
       <c r="B287">
-        <v>6.4159999999999995E-2</v>
+        <v>7.5120000000000006E-2</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -2620,7 +2620,7 @@
         <v>36.094580000000001</v>
       </c>
       <c r="B288">
-        <v>6.3930000000000001E-2</v>
+        <v>7.4870000000000006E-2</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -2628,7 +2628,7 @@
         <v>35.938600000000001</v>
       </c>
       <c r="B289">
-        <v>6.3649999999999998E-2</v>
+        <v>7.4520000000000003E-2</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -2636,7 +2636,7 @@
         <v>35.781260000000003</v>
       </c>
       <c r="B290">
-        <v>6.3350000000000004E-2</v>
+        <v>7.4200000000000002E-2</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
@@ -2644,7 +2644,7 @@
         <v>35.62527</v>
       </c>
       <c r="B291">
-        <v>6.3070000000000001E-2</v>
+        <v>7.3889999999999997E-2</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
@@ -2652,7 +2652,7 @@
         <v>35.469290000000001</v>
       </c>
       <c r="B292">
-        <v>6.2810000000000005E-2</v>
+        <v>7.3539999999999994E-2</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
@@ -2660,7 +2660,7 @@
         <v>35.313299999999998</v>
       </c>
       <c r="B293">
-        <v>6.2539999999999998E-2</v>
+        <v>7.3200000000000001E-2</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
@@ -2668,7 +2668,7 @@
         <v>35.157319999999999</v>
       </c>
       <c r="B294">
-        <v>6.2190000000000002E-2</v>
+        <v>7.288E-2</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
@@ -2676,7 +2676,7 @@
         <v>34.999980000000001</v>
       </c>
       <c r="B295">
-        <v>6.2039999999999998E-2</v>
+        <v>7.2590000000000002E-2</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
@@ -2684,7 +2684,7 @@
         <v>34.844000000000001</v>
       </c>
       <c r="B296">
-        <v>6.1650000000000003E-2</v>
+        <v>7.2249999999999995E-2</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -2692,7 +2692,7 @@
         <v>34.688009999999998</v>
       </c>
       <c r="B297">
-        <v>6.1460000000000001E-2</v>
+        <v>7.1900000000000006E-2</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -2700,7 +2700,7 @@
         <v>34.532029999999999</v>
       </c>
       <c r="B298">
-        <v>6.1120000000000001E-2</v>
+        <v>7.1609999999999993E-2</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>34.376049999999999</v>
       </c>
       <c r="B299">
-        <v>6.0900000000000003E-2</v>
+        <v>7.1330000000000005E-2</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
@@ -2716,7 +2716,7 @@
         <v>34.218710000000002</v>
       </c>
       <c r="B300">
-        <v>6.0539999999999997E-2</v>
+        <v>7.0919999999999997E-2</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
@@ -2724,7 +2724,7 @@
         <v>34.062730000000002</v>
       </c>
       <c r="B301">
-        <v>6.028E-2</v>
+        <v>7.0639999999999994E-2</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -2732,7 +2732,7 @@
         <v>33.906739999999999</v>
       </c>
       <c r="B302">
-        <v>6.003E-2</v>
+        <v>7.0269999999999999E-2</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -2740,7 +2740,7 @@
         <v>33.75076</v>
       </c>
       <c r="B303">
-        <v>5.9709999999999999E-2</v>
+        <v>7.0010000000000003E-2</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -2748,7 +2748,7 @@
         <v>33.59478</v>
       </c>
       <c r="B304">
-        <v>5.9490000000000001E-2</v>
+        <v>6.9610000000000005E-2</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -2756,7 +2756,7 @@
         <v>33.437440000000002</v>
       </c>
       <c r="B305">
-        <v>5.9150000000000001E-2</v>
+        <v>6.9309999999999997E-2</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -2764,7 +2764,7 @@
         <v>33.28145</v>
       </c>
       <c r="B306">
-        <v>5.8889999999999998E-2</v>
+        <v>6.8959999999999994E-2</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -2772,7 +2772,7 @@
         <v>33.12547</v>
       </c>
       <c r="B307">
-        <v>5.8630000000000002E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -2780,7 +2780,7 @@
         <v>32.96949</v>
       </c>
       <c r="B308">
-        <v>5.8389999999999997E-2</v>
+        <v>6.8390000000000006E-2</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -2788,7 +2788,7 @@
         <v>32.813499999999998</v>
       </c>
       <c r="B309">
-        <v>5.8110000000000002E-2</v>
+        <v>6.7960000000000007E-2</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -2796,7 +2796,7 @@
         <v>32.65616</v>
       </c>
       <c r="B310">
-        <v>5.781E-2</v>
+        <v>6.7720000000000002E-2</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -2804,7 +2804,7 @@
         <v>32.50018</v>
       </c>
       <c r="B311">
-        <v>5.7529999999999998E-2</v>
+        <v>6.7379999999999995E-2</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -2812,7 +2812,7 @@
         <v>32.344200000000001</v>
       </c>
       <c r="B312">
-        <v>5.7200000000000001E-2</v>
+        <v>6.7100000000000007E-2</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -2820,7 +2820,7 @@
         <v>32.188209999999998</v>
       </c>
       <c r="B313">
-        <v>5.6910000000000002E-2</v>
+        <v>6.6739999999999994E-2</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -2828,7 +2828,7 @@
         <v>32.032229999999998</v>
       </c>
       <c r="B314">
-        <v>5.6669999999999998E-2</v>
+        <v>6.6400000000000001E-2</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -2836,7 +2836,7 @@
         <v>31.874890000000001</v>
       </c>
       <c r="B315">
-        <v>5.6399999999999999E-2</v>
+        <v>6.608E-2</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -2844,7 +2844,7 @@
         <v>31.718900000000001</v>
       </c>
       <c r="B316">
-        <v>5.6189999999999997E-2</v>
+        <v>6.5769999999999995E-2</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -2852,7 +2852,7 @@
         <v>31.562919999999998</v>
       </c>
       <c r="B317">
-        <v>5.5820000000000002E-2</v>
+        <v>6.5439999999999998E-2</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>31.406939999999999</v>
       </c>
       <c r="B318">
-        <v>5.5570000000000001E-2</v>
+        <v>6.5100000000000005E-2</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -2868,7 +2868,7 @@
         <v>31.25095</v>
       </c>
       <c r="B319">
-        <v>5.5289999999999999E-2</v>
+        <v>6.4740000000000006E-2</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -2876,7 +2876,7 @@
         <v>31.093610000000002</v>
       </c>
       <c r="B320">
-        <v>5.5030000000000003E-2</v>
+        <v>6.4460000000000003E-2</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>30.937629999999999</v>
       </c>
       <c r="B321">
-        <v>5.475E-2</v>
+        <v>6.4130000000000006E-2</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>30.781649999999999</v>
       </c>
       <c r="B322">
-        <v>5.4449999999999998E-2</v>
+        <v>6.3780000000000003E-2</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -2900,7 +2900,7 @@
         <v>30.62566</v>
       </c>
       <c r="B323">
-        <v>5.4170000000000003E-2</v>
+        <v>6.3469999999999999E-2</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -2908,7 +2908,7 @@
         <v>30.46968</v>
       </c>
       <c r="B324">
-        <v>5.391E-2</v>
+        <v>6.3119999999999996E-2</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -2916,7 +2916,7 @@
         <v>30.312339999999999</v>
       </c>
       <c r="B325">
-        <v>5.364E-2</v>
+        <v>6.2780000000000002E-2</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -2924,7 +2924,7 @@
         <v>30.156359999999999</v>
       </c>
       <c r="B326">
-        <v>5.3350000000000002E-2</v>
+        <v>6.2520000000000006E-2</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -2932,7 +2932,7 @@
         <v>30.00037</v>
       </c>
       <c r="B327">
-        <v>5.3109999999999997E-2</v>
+        <v>6.2210000000000001E-2</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -2940,7 +2940,7 @@
         <v>29.844390000000001</v>
       </c>
       <c r="B328">
-        <v>5.28E-2</v>
+        <v>6.1890000000000001E-2</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -2948,7 +2948,7 @@
         <v>29.688410000000001</v>
       </c>
       <c r="B329">
-        <v>5.2549999999999999E-2</v>
+        <v>6.1499999999999999E-2</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -2956,7 +2956,7 @@
         <v>29.53107</v>
       </c>
       <c r="B330">
-        <v>5.228E-2</v>
+        <v>6.1179999999999998E-2</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -2964,7 +2964,7 @@
         <v>29.375080000000001</v>
       </c>
       <c r="B331">
-        <v>5.194E-2</v>
+        <v>6.0879999999999997E-2</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -2972,7 +2972,7 @@
         <v>29.219100000000001</v>
       </c>
       <c r="B332">
-        <v>5.1639999999999998E-2</v>
+        <v>6.0560000000000003E-2</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -2980,7 +2980,7 @@
         <v>29.063120000000001</v>
       </c>
       <c r="B333">
-        <v>5.144E-2</v>
+        <v>6.0199999999999997E-2</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -2988,7 +2988,7 @@
         <v>28.907129999999999</v>
       </c>
       <c r="B334">
-        <v>5.1159999999999997E-2</v>
+        <v>5.9909999999999998E-2</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
@@ -2996,7 +2996,7 @@
         <v>28.749790000000001</v>
       </c>
       <c r="B335">
-        <v>5.0860000000000002E-2</v>
+        <v>5.953E-2</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
@@ -3004,7 +3004,7 @@
         <v>28.593810000000001</v>
       </c>
       <c r="B336">
-        <v>5.0569999999999997E-2</v>
+        <v>5.9249999999999997E-2</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>28.437830000000002</v>
       </c>
       <c r="B337">
-        <v>5.033E-2</v>
+        <v>5.8909999999999997E-2</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
@@ -3020,7 +3020,7 @@
         <v>28.281839999999999</v>
       </c>
       <c r="B338">
-        <v>5.0020000000000002E-2</v>
+        <v>5.851E-2</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
@@ -3028,7 +3028,7 @@
         <v>28.125859999999999</v>
       </c>
       <c r="B339">
-        <v>4.9700000000000001E-2</v>
+        <v>5.8259999999999999E-2</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
@@ -3036,7 +3036,7 @@
         <v>27.968520000000002</v>
       </c>
       <c r="B340">
-        <v>4.9540000000000001E-2</v>
+        <v>5.7889999999999997E-2</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
@@ -3044,7 +3044,7 @@
         <v>27.812529999999999</v>
       </c>
       <c r="B341">
-        <v>4.9239999999999999E-2</v>
+        <v>5.7549999999999997E-2</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
@@ -3052,7 +3052,7 @@
         <v>27.656549999999999</v>
       </c>
       <c r="B342">
-        <v>4.895E-2</v>
+        <v>5.7259999999999998E-2</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
@@ -3060,7 +3060,7 @@
         <v>27.50057</v>
       </c>
       <c r="B343">
-        <v>4.8660000000000002E-2</v>
+        <v>5.6980000000000003E-2</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
@@ -3068,7 +3068,7 @@
         <v>27.34459</v>
       </c>
       <c r="B344">
-        <v>4.8370000000000003E-2</v>
+        <v>5.663E-2</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
@@ -3076,7 +3076,7 @@
         <v>27.187239999999999</v>
       </c>
       <c r="B345">
-        <v>4.8079999999999998E-2</v>
+        <v>5.6270000000000001E-2</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
@@ -3084,7 +3084,7 @@
         <v>27.03126</v>
       </c>
       <c r="B346">
-        <v>4.7789999999999999E-2</v>
+        <v>5.5960000000000003E-2</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
@@ -3092,7 +3092,7 @@
         <v>26.87528</v>
       </c>
       <c r="B347">
-        <v>4.7489999999999997E-2</v>
+        <v>5.5690000000000003E-2</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
@@ -3100,7 +3100,7 @@
         <v>26.719290000000001</v>
       </c>
       <c r="B348">
-        <v>4.7289999999999999E-2</v>
+        <v>5.534E-2</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
@@ -3108,7 +3108,7 @@
         <v>26.563310000000001</v>
       </c>
       <c r="B349">
-        <v>4.7010000000000003E-2</v>
+        <v>5.4989999999999997E-2</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -3116,7 +3116,7 @@
         <v>26.40597</v>
       </c>
       <c r="B350">
-        <v>4.6730000000000001E-2</v>
+        <v>5.4649999999999997E-2</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -3124,7 +3124,7 @@
         <v>26.24999</v>
       </c>
       <c r="B351">
-        <v>4.6420000000000003E-2</v>
+        <v>5.4309999999999997E-2</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -3132,7 +3132,7 @@
         <v>26.094000000000001</v>
       </c>
       <c r="B352">
-        <v>4.6120000000000001E-2</v>
+        <v>5.4030000000000002E-2</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -3140,7 +3140,7 @@
         <v>25.938020000000002</v>
       </c>
       <c r="B353">
-        <v>4.5809999999999997E-2</v>
+        <v>5.3740000000000003E-2</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -3148,7 +3148,7 @@
         <v>25.782039999999999</v>
       </c>
       <c r="B354">
-        <v>4.5650000000000003E-2</v>
+        <v>5.3449999999999998E-2</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>25.624700000000001</v>
       </c>
       <c r="B355">
-        <v>4.5269999999999998E-2</v>
+        <v>5.3039999999999997E-2</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>25.468710000000002</v>
       </c>
       <c r="B356">
-        <v>4.5089999999999998E-2</v>
+        <v>5.2699999999999997E-2</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -3172,7 +3172,7 @@
         <v>25.312729999999998</v>
       </c>
       <c r="B357">
-        <v>4.4740000000000002E-2</v>
+        <v>5.2479999999999999E-2</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -3180,7 +3180,7 @@
         <v>25.156749999999999</v>
       </c>
       <c r="B358">
-        <v>4.4429999999999997E-2</v>
+        <v>5.203E-2</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -3188,7 +3188,7 @@
         <v>25.00076</v>
       </c>
       <c r="B359">
-        <v>4.4220000000000002E-2</v>
+        <v>5.1769999999999997E-2</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -3196,7 +3196,7 @@
         <v>24.843419999999998</v>
       </c>
       <c r="B360">
-        <v>4.3860000000000003E-2</v>
+        <v>5.1429999999999997E-2</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -3204,7 +3204,7 @@
         <v>24.687439999999999</v>
       </c>
       <c r="B361">
-        <v>4.3650000000000001E-2</v>
+        <v>5.1159999999999997E-2</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
         <v>24.531459999999999</v>
       </c>
       <c r="B362">
-        <v>4.342E-2</v>
+        <v>5.0810000000000001E-2</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -3220,7 +3220,7 @@
         <v>24.37547</v>
       </c>
       <c r="B363">
-        <v>4.3110000000000002E-2</v>
+        <v>5.0470000000000001E-2</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -3228,7 +3228,7 @@
         <v>24.21949</v>
       </c>
       <c r="B364">
-        <v>4.2849999999999999E-2</v>
+        <v>5.0229999999999997E-2</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
         <v>24.062149999999999</v>
       </c>
       <c r="B365">
-        <v>4.2529999999999998E-2</v>
+        <v>4.981E-2</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -3244,7 +3244,7 @@
         <v>23.906169999999999</v>
       </c>
       <c r="B366">
-        <v>4.2250000000000003E-2</v>
+        <v>4.9529999999999998E-2</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -3252,7 +3252,7 @@
         <v>23.75018</v>
       </c>
       <c r="B367">
-        <v>4.1939999999999998E-2</v>
+        <v>4.913E-2</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -3260,7 +3260,7 @@
         <v>23.594200000000001</v>
       </c>
       <c r="B368">
-        <v>4.1759999999999999E-2</v>
+        <v>4.888E-2</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -3268,7 +3268,7 @@
         <v>23.438220000000001</v>
       </c>
       <c r="B369">
-        <v>4.1450000000000001E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -3276,7 +3276,7 @@
         <v>23.28088</v>
       </c>
       <c r="B370">
-        <v>4.1189999999999997E-2</v>
+        <v>4.8210000000000003E-2</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -3284,7 +3284,7 @@
         <v>23.124890000000001</v>
       </c>
       <c r="B371">
-        <v>4.095E-2</v>
+        <v>4.7890000000000002E-2</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -3292,7 +3292,7 @@
         <v>22.968910000000001</v>
       </c>
       <c r="B372">
-        <v>4.0599999999999997E-2</v>
+        <v>4.7570000000000001E-2</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -3300,7 +3300,7 @@
         <v>22.812930000000001</v>
       </c>
       <c r="B373">
-        <v>4.0349999999999997E-2</v>
+        <v>4.7260000000000003E-2</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -3308,7 +3308,7 @@
         <v>22.656939999999999</v>
       </c>
       <c r="B374">
-        <v>4.0079999999999998E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>22.499600000000001</v>
       </c>
       <c r="B375">
-        <v>3.984E-2</v>
+        <v>4.657E-2</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -3324,7 +3324,7 @@
         <v>22.343620000000001</v>
       </c>
       <c r="B376">
-        <v>3.9510000000000003E-2</v>
+        <v>4.6280000000000002E-2</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -3332,7 +3332,7 @@
         <v>22.187639999999998</v>
       </c>
       <c r="B377">
-        <v>3.925E-2</v>
+        <v>4.5960000000000001E-2</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -3340,7 +3340,7 @@
         <v>22.031649999999999</v>
       </c>
       <c r="B378">
-        <v>3.8920000000000003E-2</v>
+        <v>4.5609999999999998E-2</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -3348,7 +3348,7 @@
         <v>21.87567</v>
       </c>
       <c r="B379">
-        <v>3.866E-2</v>
+        <v>4.5269999999999998E-2</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -3356,7 +3356,7 @@
         <v>21.718330000000002</v>
       </c>
       <c r="B380">
-        <v>3.8429999999999999E-2</v>
+        <v>4.4990000000000002E-2</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>21.562339999999999</v>
       </c>
       <c r="B381">
-        <v>3.8129999999999997E-2</v>
+        <v>4.4659999999999998E-2</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -3372,7 +3372,7 @@
         <v>21.406359999999999</v>
       </c>
       <c r="B382">
-        <v>3.7830000000000003E-2</v>
+        <v>4.4260000000000001E-2</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -3380,7 +3380,7 @@
         <v>21.25038</v>
       </c>
       <c r="B383">
-        <v>3.7530000000000001E-2</v>
+        <v>4.3970000000000002E-2</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -3388,7 +3388,7 @@
         <v>21.094390000000001</v>
       </c>
       <c r="B384">
-        <v>3.7359999999999997E-2</v>
+        <v>4.3630000000000002E-2</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -3396,7 +3396,7 @@
         <v>20.937049999999999</v>
       </c>
       <c r="B385">
-        <v>3.7069999999999999E-2</v>
+        <v>4.3380000000000002E-2</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -3404,7 +3404,7 @@
         <v>20.78107</v>
       </c>
       <c r="B386">
-        <v>3.6790000000000003E-2</v>
+        <v>4.3040000000000002E-2</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -3412,7 +3412,7 @@
         <v>20.62509</v>
       </c>
       <c r="B387">
-        <v>3.644E-2</v>
+        <v>4.2729999999999997E-2</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <v>20.469100000000001</v>
       </c>
       <c r="B388">
-        <v>3.6200000000000003E-2</v>
+        <v>4.2360000000000002E-2</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -3428,7 +3428,7 @@
         <v>20.313120000000001</v>
       </c>
       <c r="B389">
-        <v>3.5950000000000003E-2</v>
+        <v>4.2029999999999998E-2</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -3436,7 +3436,7 @@
         <v>20.15578</v>
       </c>
       <c r="B390">
-        <v>3.5569999999999997E-2</v>
+        <v>4.1739999999999999E-2</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -3444,7 +3444,7 @@
         <v>19.9998</v>
       </c>
       <c r="B391">
-        <v>3.5409999999999997E-2</v>
+        <v>4.1430000000000002E-2</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -3452,7 +3452,7 @@
         <v>19.843810000000001</v>
       </c>
       <c r="B392">
-        <v>3.5040000000000002E-2</v>
+        <v>4.113E-2</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
         <v>19.687830000000002</v>
       </c>
       <c r="B393">
-        <v>3.4790000000000001E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>19.531849999999999</v>
       </c>
       <c r="B394">
-        <v>3.4540000000000001E-2</v>
+        <v>4.0370000000000003E-2</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <v>19.374510000000001</v>
       </c>
       <c r="B395">
-        <v>3.4290000000000001E-2</v>
+        <v>4.0149999999999998E-2</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -3484,7 +3484,7 @@
         <v>19.218520000000002</v>
       </c>
       <c r="B396">
-        <v>3.3989999999999999E-2</v>
+        <v>3.9870000000000003E-2</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -3492,7 +3492,7 @@
         <v>19.062539999999998</v>
       </c>
       <c r="B397">
-        <v>3.3700000000000001E-2</v>
+        <v>3.9440000000000003E-2</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>18.906559999999999</v>
       </c>
       <c r="B398">
-        <v>3.3439999999999998E-2</v>
+        <v>3.9120000000000002E-2</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -3508,7 +3508,7 @@
         <v>18.75057</v>
       </c>
       <c r="B399">
-        <v>3.3160000000000002E-2</v>
+        <v>3.8859999999999999E-2</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -3516,7 +3516,7 @@
         <v>18.593229999999998</v>
       </c>
       <c r="B400">
-        <v>3.288E-2</v>
+        <v>3.8530000000000002E-2</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -3524,7 +3524,7 @@
         <v>18.437249999999999</v>
       </c>
       <c r="B401">
-        <v>3.2629999999999999E-2</v>
+        <v>3.8170000000000003E-2</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -3532,7 +3532,7 @@
         <v>18.281269999999999</v>
       </c>
       <c r="B402">
-        <v>3.2320000000000002E-2</v>
+        <v>3.7830000000000003E-2</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -3540,7 +3540,7 @@
         <v>18.12528</v>
       </c>
       <c r="B403">
-        <v>3.2140000000000002E-2</v>
+        <v>3.7530000000000001E-2</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -3548,7 +3548,7 @@
         <v>17.9693</v>
       </c>
       <c r="B404">
-        <v>3.1800000000000002E-2</v>
+        <v>3.7190000000000001E-2</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -3556,7 +3556,7 @@
         <v>17.811959999999999</v>
       </c>
       <c r="B405">
-        <v>3.1440000000000003E-2</v>
+        <v>3.6839999999999998E-2</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -3564,7 +3564,7 @@
         <v>17.65598</v>
       </c>
       <c r="B406">
-        <v>3.1179999999999999E-2</v>
+        <v>3.6519999999999997E-2</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -3572,7 +3572,7 @@
         <v>17.49999</v>
       </c>
       <c r="B407">
-        <v>3.0949999999999998E-2</v>
+        <v>3.6240000000000001E-2</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -3580,7 +3580,7 @@
         <v>17.344010000000001</v>
       </c>
       <c r="B408">
-        <v>3.0630000000000001E-2</v>
+        <v>3.5839999999999997E-2</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -3588,7 +3588,7 @@
         <v>17.188020000000002</v>
       </c>
       <c r="B409">
-        <v>3.0429999999999999E-2</v>
+        <v>3.5560000000000001E-2</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -3596,7 +3596,7 @@
         <v>17.03069</v>
       </c>
       <c r="B410">
-        <v>3.0130000000000001E-2</v>
+        <v>3.5270000000000003E-2</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -3604,7 +3604,7 @@
         <v>16.874700000000001</v>
       </c>
       <c r="B411">
-        <v>2.9819999999999999E-2</v>
+        <v>3.4939999999999999E-2</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -3612,7 +3612,7 @@
         <v>16.718720000000001</v>
       </c>
       <c r="B412">
-        <v>2.9520000000000001E-2</v>
+        <v>3.4590000000000003E-2</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>16.562729999999998</v>
       </c>
       <c r="B413">
-        <v>2.929E-2</v>
+        <v>3.4290000000000001E-2</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -3628,7 +3628,7 @@
         <v>16.406749999999999</v>
       </c>
       <c r="B414">
-        <v>2.9010000000000001E-2</v>
+        <v>3.397E-2</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -3636,7 +3636,7 @@
         <v>16.249410000000001</v>
       </c>
       <c r="B415">
-        <v>2.8670000000000001E-2</v>
+        <v>3.3599999999999998E-2</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -3644,7 +3644,7 @@
         <v>16.093430000000001</v>
       </c>
       <c r="B416">
-        <v>2.8379999999999999E-2</v>
+        <v>3.3349999999999998E-2</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -3652,7 +3652,7 @@
         <v>15.93744</v>
       </c>
       <c r="B417">
-        <v>2.8139999999999998E-2</v>
+        <v>3.3029999999999997E-2</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -3660,7 +3660,7 @@
         <v>15.781459999999999</v>
       </c>
       <c r="B418">
-        <v>2.7859999999999999E-2</v>
+        <v>3.2680000000000001E-2</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -3668,7 +3668,7 @@
         <v>15.62548</v>
       </c>
       <c r="B419">
-        <v>2.7650000000000001E-2</v>
+        <v>3.2309999999999998E-2</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -3676,7 +3676,7 @@
         <v>15.46814</v>
       </c>
       <c r="B420">
-        <v>2.7359999999999999E-2</v>
+        <v>3.202E-2</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -3684,7 +3684,7 @@
         <v>15.312150000000001</v>
       </c>
       <c r="B421">
-        <v>2.707E-2</v>
+        <v>3.1730000000000001E-2</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -3692,7 +3692,7 @@
         <v>15.156169999999999</v>
       </c>
       <c r="B422">
-        <v>2.682E-2</v>
+        <v>3.1359999999999999E-2</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -3700,7 +3700,7 @@
         <v>15.00019</v>
       </c>
       <c r="B423">
-        <v>2.6509999999999999E-2</v>
+        <v>3.1050000000000001E-2</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -3708,7 +3708,7 @@
         <v>14.844200000000001</v>
       </c>
       <c r="B424">
-        <v>2.6249999999999999E-2</v>
+        <v>3.0689999999999999E-2</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -3716,7 +3716,7 @@
         <v>14.686859999999999</v>
       </c>
       <c r="B425">
-        <v>2.5989999999999999E-2</v>
+        <v>3.0380000000000001E-2</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -3724,7 +3724,7 @@
         <v>14.53088</v>
       </c>
       <c r="B426">
-        <v>2.571E-2</v>
+        <v>3.0089999999999999E-2</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -3732,7 +3732,7 @@
         <v>14.3749</v>
       </c>
       <c r="B427">
-        <v>2.5420000000000002E-2</v>
+        <v>2.9760000000000002E-2</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
         <v>14.218909999999999</v>
       </c>
       <c r="B428">
-        <v>2.5159999999999998E-2</v>
+        <v>2.946E-2</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -3748,7 +3748,7 @@
         <v>14.06293</v>
       </c>
       <c r="B429">
-        <v>2.477E-2</v>
+        <v>2.9090000000000001E-2</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
@@ -3756,7 +3756,7 @@
         <v>13.90559</v>
       </c>
       <c r="B430">
-        <v>2.4590000000000001E-2</v>
+        <v>2.8799999999999999E-2</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>13.749610000000001</v>
       </c>
       <c r="B431">
-        <v>2.427E-2</v>
+        <v>2.845E-2</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>13.59362</v>
       </c>
       <c r="B432">
-        <v>2.4039999999999999E-2</v>
+        <v>2.8150000000000001E-2</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -3780,7 +3780,7 @@
         <v>13.43764</v>
       </c>
       <c r="B433">
-        <v>2.3789999999999999E-2</v>
+        <v>2.7830000000000001E-2</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -3788,7 +3788,7 @@
         <v>13.28166</v>
       </c>
       <c r="B434">
-        <v>2.3480000000000001E-2</v>
+        <v>2.7470000000000001E-2</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -3796,7 +3796,7 @@
         <v>13.124320000000001</v>
       </c>
       <c r="B435">
-        <v>2.324E-2</v>
+        <v>2.7220000000000001E-2</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>12.96833</v>
       </c>
       <c r="B436">
-        <v>2.2950000000000002E-2</v>
+        <v>2.6839999999999999E-2</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
@@ -3812,7 +3812,7 @@
         <v>12.81235</v>
       </c>
       <c r="B437">
-        <v>2.265E-2</v>
+        <v>2.6530000000000001E-2</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -3820,7 +3820,7 @@
         <v>12.656370000000001</v>
       </c>
       <c r="B438">
-        <v>2.2339999999999999E-2</v>
+        <v>2.6169999999999999E-2</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -3828,7 +3828,7 @@
         <v>12.50038</v>
       </c>
       <c r="B439">
-        <v>2.2069999999999999E-2</v>
+        <v>2.5909999999999999E-2</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -3836,7 +3836,7 @@
         <v>12.34304</v>
       </c>
       <c r="B440">
-        <v>2.172E-2</v>
+        <v>2.554E-2</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -3844,7 +3844,7 @@
         <v>12.187060000000001</v>
       </c>
       <c r="B441">
-        <v>2.1409999999999998E-2</v>
+        <v>2.5180000000000001E-2</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -3852,7 +3852,7 @@
         <v>12.03107</v>
       </c>
       <c r="B442">
-        <v>2.111E-2</v>
+        <v>2.4889999999999999E-2</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -3860,7 +3860,7 @@
         <v>11.87509</v>
       </c>
       <c r="B443">
-        <v>2.0709999999999999E-2</v>
+        <v>2.4629999999999999E-2</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -3868,7 +3868,7 @@
         <v>11.719110000000001</v>
       </c>
       <c r="B444">
-        <v>2.018E-2</v>
+        <v>2.4299999999999999E-2</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -3876,7 +3876,7 @@
         <v>11.561769999999999</v>
       </c>
       <c r="B445">
-        <v>1.9560000000000001E-2</v>
+        <v>2.3910000000000001E-2</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -3884,7 +3884,7 @@
         <v>11.40578</v>
       </c>
       <c r="B446">
-        <v>1.8939999999999999E-2</v>
+        <v>2.3650000000000001E-2</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -3892,7 +3892,7 @@
         <v>11.2498</v>
       </c>
       <c r="B447">
-        <v>1.83E-2</v>
+        <v>2.332E-2</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
@@ -3900,7 +3900,7 @@
         <v>11.093819999999999</v>
       </c>
       <c r="B448">
-        <v>1.7569999999999999E-2</v>
+        <v>2.2929999999999999E-2</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
@@ -3908,7 +3908,7 @@
         <v>10.93783</v>
       </c>
       <c r="B449">
-        <v>1.6889999999999999E-2</v>
+        <v>2.264E-2</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
@@ -3916,7 +3916,7 @@
         <v>10.78049</v>
       </c>
       <c r="B450">
-        <v>1.6230000000000001E-2</v>
+        <v>2.23E-2</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>10.624510000000001</v>
       </c>
       <c r="B451">
-        <v>1.5509999999999999E-2</v>
+        <v>2.196E-2</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
@@ -3932,7 +3932,7 @@
         <v>10.468529999999999</v>
       </c>
       <c r="B452">
-        <v>1.461E-2</v>
+        <v>2.163E-2</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
@@ -3940,7 +3940,7 @@
         <v>10.31254</v>
       </c>
       <c r="B453">
-        <v>1.3599999999999999E-2</v>
+        <v>2.137E-2</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -3948,7 +3948,7 @@
         <v>10.156560000000001</v>
       </c>
       <c r="B454">
-        <v>1.2449999999999999E-2</v>
+        <v>2.102E-2</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -3956,7 +3956,7 @@
         <v>9.9992199999999993</v>
       </c>
       <c r="B455">
-        <v>1.112E-2</v>
+        <v>2.0709999999999999E-2</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -3964,7 +3964,7 @@
         <v>9.8432399999999998</v>
       </c>
       <c r="B456">
-        <v>8.8400000000000006E-3</v>
+        <v>2.0389999999999998E-2</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
@@ -3972,7 +3972,7 @@
         <v>9.6872500000000006</v>
       </c>
       <c r="B457">
-        <v>3.1700000000000001E-3</v>
+        <v>2.0080000000000001E-2</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
@@ -3980,7 +3980,7 @@
         <v>9.5312699999999992</v>
       </c>
       <c r="B458" s="1">
-        <v>3.0175599999999998E-4</v>
+        <v>1.9740000000000001E-2</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
@@ -3988,7 +3988,7 @@
         <v>9.3752899999999997</v>
       </c>
       <c r="B459" s="1">
-        <v>1.2344600000000001E-4</v>
+        <v>1.9429999999999999E-2</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
@@ -3996,7 +3996,7 @@
         <v>9.2179500000000001</v>
       </c>
       <c r="B460" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>1.9120000000000002E-2</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
@@ -4004,7 +4004,7 @@
         <v>9.0619599999999991</v>
       </c>
       <c r="B461" s="1">
-        <v>1.71452E-5</v>
+        <v>1.8800000000000001E-2</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
@@ -4012,7 +4012,7 @@
         <v>8.9059799999999996</v>
       </c>
       <c r="B462" s="1">
-        <v>3.42904E-6</v>
+        <v>1.8489999999999999E-2</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
@@ -4020,7 +4020,7 @@
         <v>8.75</v>
       </c>
       <c r="B463" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.8100000000000002E-2</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <v>8.5940100000000008</v>
       </c>
       <c r="B464" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>1.7809999999999999E-2</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
@@ -4036,7 +4036,7 @@
         <v>8.4366699999999994</v>
       </c>
       <c r="B465" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>1.7489999999999999E-2</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
@@ -4044,7 +4044,7 @@
         <v>8.2806899999999999</v>
       </c>
       <c r="B466" s="1">
-        <v>-1.02871E-5</v>
+        <v>1.7129999999999999E-2</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
@@ -4052,7 +4052,7 @@
         <v>8.1247100000000003</v>
       </c>
       <c r="B467" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>1.6809999999999999E-2</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
@@ -4060,7 +4060,7 @@
         <v>7.9687200000000002</v>
       </c>
       <c r="B468">
-        <v>0</v>
+        <v>1.6469999999999999E-2</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
@@ -4068,7 +4068,7 @@
         <v>7.8127399999999998</v>
       </c>
       <c r="B469" s="1">
-        <v>-1.02871E-5</v>
+        <v>1.6160000000000001E-2</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>7.6554000000000002</v>
       </c>
       <c r="B470" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.585E-2</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
@@ -4084,7 +4084,7 @@
         <v>7.4994199999999998</v>
       </c>
       <c r="B471" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>1.5559999999999999E-2</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -4092,7 +4092,7 @@
         <v>7.3434299999999997</v>
       </c>
       <c r="B472" s="1">
-        <v>-3.42904E-6</v>
+        <v>1.5180000000000001E-2</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
@@ -4100,7 +4100,7 @@
         <v>7.1874500000000001</v>
       </c>
       <c r="B473" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>1.489E-2</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
@@ -4108,7 +4108,7 @@
         <v>7.0314699999999997</v>
       </c>
       <c r="B474" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>1.4579999999999999E-2</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
@@ -4116,7 +4116,7 @@
         <v>6.8741300000000001</v>
       </c>
       <c r="B475" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.4239999999999999E-2</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
@@ -4124,7 +4124,7 @@
         <v>6.71814</v>
       </c>
       <c r="B476" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>1.3950000000000001E-2</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
@@ -4132,7 +4132,7 @@
         <v>6.5621600000000004</v>
       </c>
       <c r="B477" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.359E-2</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
@@ -4140,7 +4140,7 @@
         <v>6.4061700000000004</v>
       </c>
       <c r="B478" s="1">
-        <v>1.02871E-5</v>
+        <v>1.3270000000000001E-2</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
@@ -4148,7 +4148,7 @@
         <v>6.2501899999999999</v>
       </c>
       <c r="B479" s="1">
-        <v>5.4864699999999997E-5</v>
+        <v>1.294E-2</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
@@ -4156,7 +4156,7 @@
         <v>6.0928500000000003</v>
       </c>
       <c r="B480" s="1">
-        <v>-2.4003300000000001E-5</v>
+        <v>1.2659999999999999E-2</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -4164,7 +4164,7 @@
         <v>5.9368699999999999</v>
       </c>
       <c r="B481" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>1.225E-2</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
@@ -4172,7 +4172,7 @@
         <v>5.7808799999999998</v>
       </c>
       <c r="B482" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>1.2019999999999999E-2</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>5.6249000000000002</v>
       </c>
       <c r="B483" s="1">
-        <v>3.42904E-5</v>
+        <v>1.167E-2</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
@@ -4188,7 +4188,7 @@
         <v>5.4689199999999998</v>
       </c>
       <c r="B484" s="1">
-        <v>-3.42904E-6</v>
+        <v>1.1310000000000001E-2</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
@@ -4196,7 +4196,7 @@
         <v>5.3115800000000002</v>
       </c>
       <c r="B485" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.103E-2</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
@@ -4204,7 +4204,7 @@
         <v>5.1555900000000001</v>
       </c>
       <c r="B486" s="1">
-        <v>1.71452E-5</v>
+        <v>1.064E-2</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
@@ -4212,7 +4212,7 @@
         <v>4.9996099999999997</v>
       </c>
       <c r="B487" s="1">
-        <v>1.02871E-5</v>
+        <v>1.0290000000000001E-2</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
@@ -4220,7 +4220,7 @@
         <v>4.8436300000000001</v>
       </c>
       <c r="B488" s="1">
-        <v>-3.42904E-6</v>
+        <v>9.8399999999999998E-3</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>4.68764</v>
       </c>
       <c r="B489" s="1">
-        <v>3.42904E-5</v>
+        <v>9.4500000000000001E-3</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
@@ -4236,7 +4236,7 @@
         <v>4.5303000000000004</v>
       </c>
       <c r="B490" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>8.9499999999999996E-3</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
@@ -4244,7 +4244,7 @@
         <v>4.37432</v>
       </c>
       <c r="B491" s="1">
-        <v>6.5151800000000002E-5</v>
+        <v>8.4899999999999993E-3</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
@@ -4252,7 +4252,7 @@
         <v>4.2183400000000004</v>
       </c>
       <c r="B492" s="1">
-        <v>3.42904E-5</v>
+        <v>7.9699999999999997E-3</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
         <v>4.0623500000000003</v>
       </c>
       <c r="B493" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>7.43E-3</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
@@ -4268,7 +4268,7 @@
         <v>3.9063699999999999</v>
       </c>
       <c r="B494" s="1">
-        <v>-3.42904E-6</v>
+        <v>6.9199999999999999E-3</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
@@ -4276,7 +4276,7 @@
         <v>3.7490299999999999</v>
       </c>
       <c r="B495" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>6.4900000000000001E-3</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
@@ -4284,7 +4284,7 @@
         <v>3.5930499999999999</v>
       </c>
       <c r="B496" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>6.0400000000000002E-3</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
@@ -4292,7 +4292,7 @@
         <v>3.4370599999999998</v>
       </c>
       <c r="B497" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>5.6299999999999996E-3</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>3.2810800000000002</v>
       </c>
       <c r="B498" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>5.2100000000000002E-3</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
@@ -4308,7 +4308,7 @@
         <v>3.1251000000000002</v>
       </c>
       <c r="B499" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>4.8399999999999997E-3</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
@@ -4316,7 +4316,7 @@
         <v>2.9677600000000002</v>
       </c>
       <c r="B500" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>4.4200000000000003E-3</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
@@ -4324,7 +4324,7 @@
         <v>2.8117700000000001</v>
       </c>
       <c r="B501" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>3.9899999999999996E-3</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
@@ -4332,7 +4332,7 @@
         <v>2.6557900000000001</v>
       </c>
       <c r="B502" s="1">
-        <v>1.02871E-5</v>
+        <v>3.6900000000000001E-3</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
@@ -4340,7 +4340,7 @@
         <v>2.4998100000000001</v>
       </c>
       <c r="B503" s="1">
-        <v>-3.42904E-6</v>
+        <v>3.2699999999999999E-3</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
@@ -4348,7 +4348,7 @@
         <v>2.34382</v>
       </c>
       <c r="B504" s="1">
-        <v>-1.3716199999999999E-5</v>
+        <v>2.9099999999999998E-3</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
@@ -4356,7 +4356,7 @@
         <v>2.18648</v>
       </c>
       <c r="B505" s="1">
-        <v>-4.1148500000000001E-5</v>
+        <v>2.5699999999999998E-3</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
@@ -4364,7 +4364,7 @@
         <v>2.0305</v>
       </c>
       <c r="B506" s="1">
-        <v>-2.4003300000000001E-5</v>
+        <v>2.1800000000000001E-3</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
@@ -4372,7 +4372,7 @@
         <v>1.87452</v>
       </c>
       <c r="B507" s="1">
-        <v>3.42904E-5</v>
+        <v>1.7899999999999999E-3</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>1.7185299999999999</v>
       </c>
       <c r="B508" s="1">
-        <v>7.54389E-5</v>
+        <v>1.4599999999999999E-3</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
@@ -4388,7 +4388,7 @@
         <v>1.5625500000000001</v>
       </c>
       <c r="B509" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>1.0200000000000001E-3</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
@@ -4396,7 +4396,7 @@
         <v>1.4052100000000001</v>
       </c>
       <c r="B510" s="1">
-        <v>3.42904E-5</v>
+        <v>6.1036900000000004E-4</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
@@ -4404,7 +4404,7 @@
         <v>1.24922</v>
       </c>
       <c r="B511" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>3.2233000000000001E-4</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
@@ -4412,7 +4412,7 @@
         <v>1.09324</v>
       </c>
       <c r="B512" s="1">
-        <v>1.71452E-5</v>
+        <v>1.37162E-4</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
@@ -4420,7 +4420,7 @@
         <v>0.93725999999999998</v>
       </c>
       <c r="B513" s="1">
-        <v>1.71452E-5</v>
+        <v>1.0972900000000001E-4</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
@@ -4428,7 +4428,7 @@
         <v>0.78127000000000002</v>
       </c>
       <c r="B514" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>7.54389E-5</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
@@ -4436,7 +4436,7 @@
         <v>0.62392999999999998</v>
       </c>
       <c r="B515" s="1">
-        <v>-1.02871E-5</v>
+        <v>4.4577499999999998E-5</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
@@ -4444,7 +4444,7 @@
         <v>0.46794999999999998</v>
       </c>
       <c r="B516" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
@@ -4452,7 +4452,7 @@
         <v>0.31197000000000003</v>
       </c>
       <c r="B517" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>6.5151800000000002E-5</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
@@ -4460,7 +4460,7 @@
         <v>0.15598000000000001</v>
       </c>
       <c r="B518" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-3.42904E-6</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="B519" s="1">
-        <v>-1.02871E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
@@ -4476,7 +4476,7 @@
         <v>-0.15598000000000001</v>
       </c>
       <c r="B520" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
@@ -4484,15 +4484,15 @@
         <v>-0.31197000000000003</v>
       </c>
       <c r="B521" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>-0.46794999999999998</v>
       </c>
-      <c r="B522">
-        <v>0</v>
+      <c r="B522" s="1">
+        <v>-1.71452E-5</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
@@ -4500,7 +4500,7 @@
         <v>-0.62392999999999998</v>
       </c>
       <c r="B523" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
@@ -4508,7 +4508,7 @@
         <v>-0.78127000000000002</v>
       </c>
       <c r="B524" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
@@ -4516,7 +4516,7 @@
         <v>-0.93725999999999998</v>
       </c>
       <c r="B525" s="1">
-        <v>3.42904E-6</v>
+        <v>8.9155100000000003E-5</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
@@ -4524,7 +4524,7 @@
         <v>-1.09324</v>
       </c>
       <c r="B526" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>6.5151800000000002E-5</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
@@ -4532,23 +4532,23 @@
         <v>-1.24922</v>
       </c>
       <c r="B527" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>-1.4052100000000001</v>
       </c>
-      <c r="B528">
-        <v>0</v>
+      <c r="B528" s="1">
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>-1.5625500000000001</v>
       </c>
-      <c r="B529">
-        <v>0</v>
+      <c r="B529" s="1">
+        <v>3.7719499999999997E-5</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
@@ -4556,7 +4556,7 @@
         <v>-1.7185299999999999</v>
       </c>
       <c r="B530" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
@@ -4564,7 +4564,7 @@
         <v>-1.87452</v>
       </c>
       <c r="B531" s="1">
-        <v>8.2297000000000002E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
@@ -4572,7 +4572,7 @@
         <v>-2.0305</v>
       </c>
       <c r="B532" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
@@ -4580,7 +4580,7 @@
         <v>-2.18648</v>
       </c>
       <c r="B533" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
@@ -4588,7 +4588,7 @@
         <v>-2.34382</v>
       </c>
       <c r="B534" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
@@ -4596,7 +4596,7 @@
         <v>-2.4998100000000001</v>
       </c>
       <c r="B535" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
@@ -4604,15 +4604,15 @@
         <v>-2.6557900000000001</v>
       </c>
       <c r="B536" s="1">
-        <v>1.71452E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>-2.8117700000000001</v>
       </c>
-      <c r="B537">
-        <v>0</v>
+      <c r="B537" s="1">
+        <v>5.4864699999999997E-5</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
@@ -4620,7 +4620,7 @@
         <v>-2.9677600000000002</v>
       </c>
       <c r="B538" s="1">
-        <v>8.9155100000000003E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
@@ -4628,7 +4628,7 @@
         <v>-3.1251000000000002</v>
       </c>
       <c r="B539" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
@@ -4636,7 +4636,7 @@
         <v>-3.2810800000000002</v>
       </c>
       <c r="B540" s="1">
-        <v>5.4864699999999997E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
@@ -4644,7 +4644,7 @@
         <v>-3.4370599999999998</v>
       </c>
       <c r="B541" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>3.42904E-6</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
@@ -4652,7 +4652,7 @@
         <v>-3.5930499999999999</v>
       </c>
       <c r="B542" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>-2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
@@ -4660,7 +4660,7 @@
         <v>-3.7490299999999999</v>
       </c>
       <c r="B543" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
@@ -4668,15 +4668,15 @@
         <v>-3.9063699999999999</v>
       </c>
       <c r="B544" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>-4.0623500000000003</v>
       </c>
-      <c r="B545">
-        <v>0</v>
+      <c r="B545" s="1">
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>-4.2183400000000004</v>
       </c>
       <c r="B546" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
         <v>-4.37432</v>
       </c>
       <c r="B547" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
@@ -4700,15 +4700,15 @@
         <v>-4.5303000000000004</v>
       </c>
       <c r="B548" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>-4.68764</v>
       </c>
-      <c r="B549">
-        <v>0</v>
+      <c r="B549" s="1">
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
@@ -4716,7 +4716,7 @@
         <v>-4.8436300000000001</v>
       </c>
       <c r="B550" s="1">
-        <v>1.71452E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.25">
@@ -4724,7 +4724,7 @@
         <v>-4.9996099999999997</v>
       </c>
       <c r="B551" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.25">
@@ -4732,7 +4732,7 @@
         <v>-5.1555900000000001</v>
       </c>
       <c r="B552" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>-3.42904E-6</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.25">
@@ -4740,7 +4740,7 @@
         <v>-5.3115800000000002</v>
       </c>
       <c r="B553" s="1">
-        <v>-3.0861400000000002E-5</v>
+        <v>4.1148500000000001E-5</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.25">
@@ -4748,7 +4748,7 @@
         <v>-5.4689199999999998</v>
       </c>
       <c r="B554" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.25">
@@ -4756,7 +4756,7 @@
         <v>-5.6249000000000002</v>
       </c>
       <c r="B555" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.25">
@@ -4764,7 +4764,7 @@
         <v>-5.7808799999999998</v>
       </c>
       <c r="B556" s="1">
-        <v>3.42904E-5</v>
+        <v>3.0861400000000002E-5</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.25">
@@ -4772,7 +4772,7 @@
         <v>-5.9368699999999999</v>
       </c>
       <c r="B557" s="1">
-        <v>-3.42904E-6</v>
+        <v>6.1722699999999998E-5</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>-6.0928500000000003</v>
       </c>
       <c r="B558" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.25">
@@ -4796,7 +4796,7 @@
         <v>-6.4061700000000004</v>
       </c>
       <c r="B560" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>-1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.25">
@@ -4804,7 +4804,7 @@
         <v>-6.5621600000000004</v>
       </c>
       <c r="B561" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>-3.42904E-6</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.25">
@@ -4812,7 +4812,7 @@
         <v>-6.71814</v>
       </c>
       <c r="B562" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>-6.8741300000000001</v>
       </c>
       <c r="B563" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>-1.71452E-5</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.25">
@@ -4828,7 +4828,7 @@
         <v>-7.0314699999999997</v>
       </c>
       <c r="B564" s="1">
-        <v>-1.02871E-5</v>
+        <v>-6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>-7.1874500000000001</v>
       </c>
       <c r="B565" s="1">
-        <v>3.42904E-6</v>
+        <v>-2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
@@ -4844,7 +4844,7 @@
         <v>-7.3434299999999997</v>
       </c>
       <c r="B566" s="1">
-        <v>3.42904E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
@@ -4852,7 +4852,7 @@
         <v>-7.4994199999999998</v>
       </c>
       <c r="B567" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>1.02871E-5</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>-7.6554000000000002</v>
       </c>
       <c r="B568" s="1">
-        <v>-1.71452E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
@@ -4868,7 +4868,7 @@
         <v>-7.8127399999999998</v>
       </c>
       <c r="B569" s="1">
-        <v>1.02871E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.25">
@@ -4876,7 +4876,7 @@
         <v>-7.9687200000000002</v>
       </c>
       <c r="B570" s="1">
-        <v>-1.3716199999999999E-5</v>
+        <v>4.8006600000000002E-5</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.25">
@@ -4884,7 +4884,7 @@
         <v>-8.1247100000000003</v>
       </c>
       <c r="B571" s="1">
-        <v>-1.71452E-5</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.25">
@@ -4892,7 +4892,7 @@
         <v>-8.2806899999999999</v>
       </c>
       <c r="B572" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.25">
@@ -4900,7 +4900,7 @@
         <v>-8.4366699999999994</v>
       </c>
       <c r="B573" s="1">
-        <v>1.02871E-5</v>
+        <v>-1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.25">
@@ -4908,7 +4908,7 @@
         <v>-8.5940100000000008</v>
       </c>
       <c r="B574" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>5.1435599999999999E-5</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.25">
@@ -4916,7 +4916,7 @@
         <v>-8.75</v>
       </c>
       <c r="B575" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.25">
@@ -4924,7 +4924,7 @@
         <v>-8.9059799999999996</v>
       </c>
       <c r="B576" s="1">
-        <v>-1.02871E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.25">
@@ -4932,7 +4932,7 @@
         <v>-9.0619599999999991</v>
       </c>
       <c r="B577" s="1">
-        <v>-3.0861400000000002E-5</v>
+        <v>3.42904E-5</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>-9.2179500000000001</v>
       </c>
       <c r="B578" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
         <v>-9.3752899999999997</v>
       </c>
       <c r="B579" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
@@ -4956,7 +4956,7 @@
         <v>-9.5312699999999992</v>
       </c>
       <c r="B580" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.25">
@@ -4964,15 +4964,15 @@
         <v>-9.6872500000000006</v>
       </c>
       <c r="B581" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>-9.8432399999999998</v>
       </c>
-      <c r="B582">
-        <v>0</v>
+      <c r="B582" s="1">
+        <v>-3.42904E-6</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.25">
@@ -4980,7 +4980,7 @@
         <v>-9.9992199999999993</v>
       </c>
       <c r="B583" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>-10.156560000000001</v>
       </c>
       <c r="B584" s="1">
-        <v>1.02871E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
@@ -4996,7 +4996,7 @@
         <v>-10.31254</v>
       </c>
       <c r="B585" s="1">
-        <v>1.02871E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.25">
@@ -5004,7 +5004,7 @@
         <v>-10.468529999999999</v>
       </c>
       <c r="B586" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
@@ -5012,7 +5012,7 @@
         <v>-10.624510000000001</v>
       </c>
       <c r="B587" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.25">
@@ -5020,7 +5020,7 @@
         <v>-10.78049</v>
       </c>
       <c r="B588" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.25">
@@ -5028,7 +5028,7 @@
         <v>-10.93783</v>
       </c>
       <c r="B589" s="1">
-        <v>7.54389E-5</v>
+        <v>5.8293700000000001E-5</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.25">
@@ -5036,7 +5036,7 @@
         <v>-11.093819999999999</v>
       </c>
       <c r="B590" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>1.71452E-5</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.25">
@@ -5044,7 +5044,7 @@
         <v>-11.2498</v>
       </c>
       <c r="B591" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>1.3716199999999999E-5</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.25">
@@ -5052,7 +5052,7 @@
         <v>-11.40578</v>
       </c>
       <c r="B592" s="1">
-        <v>-2.7432300000000002E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.25">
@@ -5060,7 +5060,7 @@
         <v>-11.561769999999999</v>
       </c>
       <c r="B593" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>2.4003300000000001E-5</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.25">
@@ -5068,7 +5068,7 @@
         <v>-11.719110000000001</v>
       </c>
       <c r="B594" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>-6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.25">
@@ -5076,7 +5076,7 @@
         <v>-11.87509</v>
       </c>
       <c r="B595" s="1">
-        <v>6.1722699999999998E-5</v>
+        <v>2.7432300000000002E-5</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
@@ -5084,7 +5084,7 @@
         <v>-12.03107</v>
       </c>
       <c r="B596" s="1">
-        <v>-3.42904E-6</v>
+        <v>6.8580799999999999E-6</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
@@ -5092,7 +5092,7 @@
         <v>-12.187060000000001</v>
       </c>
       <c r="B597" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>2.0574300000000001E-5</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
@@ -5100,7 +5100,7 @@
         <v>-12.34304</v>
       </c>
       <c r="B598" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>1.6067999999999999E-5</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
@@ -5108,7 +5108,7 @@
         <v>-12.50038</v>
       </c>
       <c r="B599" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>-1.1433299999999999E-5</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
@@ -5116,7 +5116,7 @@
         <v>-12.656370000000001</v>
       </c>
       <c r="B600" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>3.7711300000000002E-6</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.25">
@@ -5124,7 +5124,7 @@
         <v>-12.81235</v>
       </c>
       <c r="B601" s="1">
-        <v>5.4864699999999997E-5</v>
+        <v>-1.00382E-5</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>-12.96833</v>
       </c>
       <c r="B602" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>2.31752E-6</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>-13.124320000000001</v>
       </c>
       <c r="B603" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-2.3847500000000002E-5</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.25">
@@ -5148,7 +5148,7 @@
         <v>-13.28166</v>
       </c>
       <c r="B604" s="1">
-        <v>6.5151800000000002E-5</v>
+        <v>2.1214500000000002E-5</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.25">
@@ -5156,7 +5156,7 @@
         <v>-13.43764</v>
       </c>
       <c r="B605" s="1">
-        <v>3.42904E-5</v>
+        <v>-3.25692E-5</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
@@ -5164,7 +5164,7 @@
         <v>-13.59362</v>
       </c>
       <c r="B606" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>-3.693E-5</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
@@ -5172,7 +5172,7 @@
         <v>-13.749610000000001</v>
       </c>
       <c r="B607" s="1">
-        <v>1.02871E-5</v>
+        <v>-3.4749599999999997E-5</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
@@ -5180,7 +5180,7 @@
         <v>-13.90559</v>
       </c>
       <c r="B608" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>3.7711300000000002E-6</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.25">
@@ -5188,7 +5188,7 @@
         <v>-14.06293</v>
       </c>
       <c r="B609" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-4.3471299999999998E-5</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.25">
@@ -5196,7 +5196,7 @@
         <v>-14.218909999999999</v>
       </c>
       <c r="B610" s="1">
-        <v>1.02871E-5</v>
+        <v>-7.0363099999999997E-5</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.25">
@@ -5204,7 +5204,7 @@
         <v>-14.3749</v>
       </c>
       <c r="B611" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-7.8357900000000004E-5</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.25">
@@ -5212,7 +5212,7 @@
         <v>-14.53088</v>
       </c>
       <c r="B612" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-5.5826999999999999E-5</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.25">
@@ -5220,7 +5220,7 @@
         <v>-14.686859999999999</v>
       </c>
       <c r="B613" s="1">
-        <v>-1.02871E-5</v>
+        <v>-1.08157E-4</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.25">
@@ -5228,7 +5228,7 @@
         <v>-14.844200000000001</v>
       </c>
       <c r="B614" s="1">
-        <v>-1.02871E-5</v>
+        <v>-7.4021799999999995E-4</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.25">
@@ -5236,7 +5236,7 @@
         <v>-15.00019</v>
       </c>
       <c r="B615" s="1">
-        <v>3.42904E-6</v>
+        <v>-5.9899999999999997E-3</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.25">
@@ -5244,7 +5244,7 @@
         <v>-15.156169999999999</v>
       </c>
       <c r="B616" s="1">
-        <v>-1.02871E-5</v>
+        <v>-1.558E-2</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.25">
@@ -5252,7 +5252,7 @@
         <v>-15.312150000000001</v>
       </c>
       <c r="B617" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-2.3970000000000002E-2</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
@@ -5260,7 +5260,7 @@
         <v>-15.46814</v>
       </c>
       <c r="B618" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-2.8330000000000001E-2</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.25">
@@ -5268,7 +5268,7 @@
         <v>-15.62548</v>
       </c>
       <c r="B619" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-3.0290000000000001E-2</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.25">
@@ -5276,7 +5276,7 @@
         <v>-15.781459999999999</v>
       </c>
       <c r="B620" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>-3.168E-2</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>-15.93744</v>
       </c>
       <c r="B621" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-3.2210000000000003E-2</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.25">
@@ -5292,7 +5292,7 @@
         <v>-16.093430000000001</v>
       </c>
       <c r="B622" s="1">
-        <v>-3.42904E-6</v>
+        <v>-3.2989999999999998E-2</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.25">
@@ -5300,7 +5300,7 @@
         <v>-16.249410000000001</v>
       </c>
       <c r="B623" s="1">
-        <v>1.02871E-5</v>
+        <v>-3.3579999999999999E-2</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.25">
@@ -5308,7 +5308,7 @@
         <v>-16.406749999999999</v>
       </c>
       <c r="B624" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-3.3910000000000003E-2</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -5316,7 +5316,7 @@
         <v>-16.562729999999998</v>
       </c>
       <c r="B625" s="1">
-        <v>1.02871E-5</v>
+        <v>-3.4209999999999997E-2</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -5324,7 +5324,7 @@
         <v>-16.718720000000001</v>
       </c>
       <c r="B626" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>-3.4540000000000001E-2</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.25">
@@ -5332,7 +5332,7 @@
         <v>-16.874700000000001</v>
       </c>
       <c r="B627" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>-3.4790000000000001E-2</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.25">
@@ -5340,7 +5340,7 @@
         <v>-17.03069</v>
       </c>
       <c r="B628" s="1">
-        <v>-3.42904E-6</v>
+        <v>-3.5130000000000002E-2</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.25">
@@ -5348,7 +5348,7 @@
         <v>-17.188020000000002</v>
       </c>
       <c r="B629" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>-3.551E-2</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.25">
@@ -5356,7 +5356,7 @@
         <v>-17.344010000000001</v>
       </c>
       <c r="B630" s="1">
-        <v>1.71452E-5</v>
+        <v>-3.5819999999999998E-2</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.25">
@@ -5364,7 +5364,7 @@
         <v>-17.49999</v>
       </c>
       <c r="B631" s="1">
-        <v>3.42904E-5</v>
+        <v>-3.6150000000000002E-2</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.25">
@@ -5372,7 +5372,7 @@
         <v>-17.65598</v>
       </c>
       <c r="B632" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>-3.6459999999999999E-2</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.25">
@@ -5380,7 +5380,7 @@
         <v>-17.811959999999999</v>
       </c>
       <c r="B633" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>-3.6799999999999999E-2</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.25">
@@ -5388,7 +5388,7 @@
         <v>-17.9693</v>
       </c>
       <c r="B634" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>-3.7179999999999998E-2</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.25">
@@ -5396,7 +5396,7 @@
         <v>-18.12528</v>
       </c>
       <c r="B635" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>-3.7400000000000003E-2</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.25">
@@ -5404,7 +5404,7 @@
         <v>-18.281269999999999</v>
       </c>
       <c r="B636" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>-3.7769999999999998E-2</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.25">
@@ -5412,7 +5412,7 @@
         <v>-18.437249999999999</v>
       </c>
       <c r="B637" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-3.8059999999999997E-2</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.25">
@@ -5420,7 +5420,7 @@
         <v>-18.593229999999998</v>
       </c>
       <c r="B638" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>-3.8449999999999998E-2</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.25">
@@ -5428,7 +5428,7 @@
         <v>-18.75057</v>
       </c>
       <c r="B639" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-3.8760000000000003E-2</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.25">
@@ -5436,7 +5436,7 @@
         <v>-18.906559999999999</v>
       </c>
       <c r="B640" s="1">
-        <v>1.71452E-5</v>
+        <v>-3.909E-2</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
@@ -5444,7 +5444,7 @@
         <v>-19.062539999999998</v>
       </c>
       <c r="B641" s="1">
-        <v>3.42904E-6</v>
+        <v>-3.9370000000000002E-2</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.25">
@@ -5452,7 +5452,7 @@
         <v>-19.218520000000002</v>
       </c>
       <c r="B642" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>-3.9730000000000001E-2</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.25">
@@ -5460,7 +5460,7 @@
         <v>-19.374510000000001</v>
       </c>
       <c r="B643" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-4.0030000000000003E-2</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.25">
@@ -5468,7 +5468,7 @@
         <v>-19.531849999999999</v>
       </c>
       <c r="B644" s="1">
-        <v>-2.4003300000000001E-5</v>
+        <v>-4.0349999999999997E-2</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>-19.687830000000002</v>
       </c>
       <c r="B645" s="1">
-        <v>-1.5706100000000001E-4</v>
+        <v>-4.07E-2</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.25">
@@ -5484,7 +5484,7 @@
         <v>-19.843810000000001</v>
       </c>
       <c r="B646">
-        <v>-1.14E-3</v>
+        <v>-4.0980000000000003E-2</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.25">
@@ -5492,7 +5492,7 @@
         <v>-19.9998</v>
       </c>
       <c r="B647">
-        <v>-9.0399999999999994E-3</v>
+        <v>-4.1320000000000003E-2</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.25">
@@ -5500,7 +5500,7 @@
         <v>-20.15578</v>
       </c>
       <c r="B648">
-        <v>-3.3529999999999997E-2</v>
+        <v>-4.163E-2</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.25">
@@ -5508,7 +5508,7 @@
         <v>-20.313120000000001</v>
       </c>
       <c r="B649">
-        <v>-3.601E-2</v>
+        <v>-4.197E-2</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.25">
@@ -5516,7 +5516,7 @@
         <v>-20.469100000000001</v>
       </c>
       <c r="B650">
-        <v>-3.6360000000000003E-2</v>
+        <v>-4.2290000000000001E-2</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.25">
@@ -5524,7 +5524,7 @@
         <v>-20.62509</v>
       </c>
       <c r="B651">
-        <v>-3.6519999999999997E-2</v>
+        <v>-4.2619999999999998E-2</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
@@ -5532,7 +5532,7 @@
         <v>-20.78107</v>
       </c>
       <c r="B652">
-        <v>-3.6679999999999997E-2</v>
+        <v>-4.2950000000000002E-2</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.25">
@@ -5540,7 +5540,7 @@
         <v>-20.937049999999999</v>
       </c>
       <c r="B653">
-        <v>-3.6920000000000001E-2</v>
+        <v>-4.3270000000000003E-2</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.25">
@@ -5548,7 +5548,7 @@
         <v>-21.094390000000001</v>
       </c>
       <c r="B654">
-        <v>-3.7190000000000001E-2</v>
+        <v>-4.3580000000000001E-2</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.25">
@@ -5556,7 +5556,7 @@
         <v>-21.25038</v>
       </c>
       <c r="B655">
-        <v>-3.7479999999999999E-2</v>
+        <v>-4.394E-2</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.25">
@@ -5564,7 +5564,7 @@
         <v>-21.406359999999999</v>
       </c>
       <c r="B656">
-        <v>-3.7760000000000002E-2</v>
+        <v>-4.4209999999999999E-2</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.25">
@@ -5572,7 +5572,7 @@
         <v>-21.562339999999999</v>
       </c>
       <c r="B657">
-        <v>-3.8019999999999998E-2</v>
+        <v>-4.4589999999999998E-2</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.25">
@@ -5580,7 +5580,7 @@
         <v>-21.718330000000002</v>
       </c>
       <c r="B658">
-        <v>-3.8289999999999998E-2</v>
+        <v>-4.4909999999999999E-2</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.25">
@@ -5588,7 +5588,7 @@
         <v>-21.87567</v>
       </c>
       <c r="B659">
-        <v>-3.8589999999999999E-2</v>
+        <v>-4.5220000000000003E-2</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.25">
@@ -5596,7 +5596,7 @@
         <v>-22.031649999999999</v>
       </c>
       <c r="B660">
-        <v>-3.8850000000000003E-2</v>
+        <v>-4.5539999999999997E-2</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.25">
@@ -5604,7 +5604,7 @@
         <v>-22.187639999999998</v>
       </c>
       <c r="B661">
-        <v>-3.9149999999999997E-2</v>
+        <v>-4.5850000000000002E-2</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.25">
@@ -5612,7 +5612,7 @@
         <v>-22.343620000000001</v>
       </c>
       <c r="B662">
-        <v>-3.9449999999999999E-2</v>
+        <v>-4.6199999999999998E-2</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.25">
@@ -5620,7 +5620,7 @@
         <v>-22.499600000000001</v>
       </c>
       <c r="B663">
-        <v>-3.9699999999999999E-2</v>
+        <v>-4.6530000000000002E-2</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.25">
@@ -5628,7 +5628,7 @@
         <v>-22.656939999999999</v>
       </c>
       <c r="B664">
-        <v>-0.04</v>
+        <v>-4.684E-2</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.25">
@@ -5636,7 +5636,7 @@
         <v>-22.812930000000001</v>
       </c>
       <c r="B665">
-        <v>-4.0289999999999999E-2</v>
+        <v>-4.7190000000000003E-2</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.25">
@@ -5644,7 +5644,7 @@
         <v>-22.968910000000001</v>
       </c>
       <c r="B666">
-        <v>-4.052E-2</v>
+        <v>-4.7489999999999997E-2</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.25">
@@ -5652,7 +5652,7 @@
         <v>-23.124890000000001</v>
       </c>
       <c r="B667">
-        <v>-4.0820000000000002E-2</v>
+        <v>-4.7800000000000002E-2</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.25">
@@ -5660,7 +5660,7 @@
         <v>-23.28088</v>
       </c>
       <c r="B668">
-        <v>-4.1079999999999998E-2</v>
+        <v>-4.811E-2</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.25">
@@ -5668,7 +5668,7 @@
         <v>-23.438220000000001</v>
       </c>
       <c r="B669">
-        <v>-4.1369999999999997E-2</v>
+        <v>-4.8480000000000002E-2</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.25">
@@ -5676,7 +5676,7 @@
         <v>-23.594200000000001</v>
       </c>
       <c r="B670">
-        <v>-4.1640000000000003E-2</v>
+        <v>-4.879E-2</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.25">
@@ -5684,7 +5684,7 @@
         <v>-23.75018</v>
       </c>
       <c r="B671">
-        <v>-4.1919999999999999E-2</v>
+        <v>-4.9110000000000001E-2</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.25">
@@ -5692,7 +5692,7 @@
         <v>-23.906169999999999</v>
       </c>
       <c r="B672">
-        <v>-4.2180000000000002E-2</v>
+        <v>-4.9439999999999998E-2</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.25">
@@ -5700,7 +5700,7 @@
         <v>-24.062149999999999</v>
       </c>
       <c r="B673">
-        <v>-4.2479999999999997E-2</v>
+        <v>-4.972E-2</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.25">
@@ -5708,7 +5708,7 @@
         <v>-24.21949</v>
       </c>
       <c r="B674">
-        <v>-4.2790000000000002E-2</v>
+        <v>-5.0040000000000001E-2</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
         <v>-24.37547</v>
       </c>
       <c r="B675">
-        <v>-4.3049999999999998E-2</v>
+        <v>-5.0389999999999997E-2</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.25">
@@ -5724,7 +5724,7 @@
         <v>-24.531459999999999</v>
       </c>
       <c r="B676">
-        <v>-4.3279999999999999E-2</v>
+        <v>-5.0709999999999998E-2</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.25">
@@ -5732,7 +5732,7 @@
         <v>-24.687439999999999</v>
       </c>
       <c r="B677">
-        <v>-4.3589999999999997E-2</v>
+        <v>-5.1069999999999997E-2</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.25">
@@ -5740,7 +5740,7 @@
         <v>-24.843419999999998</v>
       </c>
       <c r="B678">
-        <v>-4.3860000000000003E-2</v>
+        <v>-5.1380000000000002E-2</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.25">
@@ -5748,7 +5748,7 @@
         <v>-25.00076</v>
       </c>
       <c r="B679">
-        <v>-4.4150000000000002E-2</v>
+        <v>-5.169E-2</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.25">
@@ -5756,7 +5756,7 @@
         <v>-25.156749999999999</v>
       </c>
       <c r="B680">
-        <v>-4.4420000000000001E-2</v>
+        <v>-5.203E-2</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.25">
@@ -5764,7 +5764,7 @@
         <v>-25.312729999999998</v>
       </c>
       <c r="B681">
-        <v>-4.4679999999999997E-2</v>
+        <v>-5.2350000000000001E-2</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.25">
@@ -5772,7 +5772,7 @@
         <v>-25.468710000000002</v>
       </c>
       <c r="B682">
-        <v>-4.4990000000000002E-2</v>
+        <v>-5.2650000000000002E-2</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.25">
@@ -5780,7 +5780,7 @@
         <v>-25.624700000000001</v>
       </c>
       <c r="B683">
-        <v>-4.5240000000000002E-2</v>
+        <v>-5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.25">
@@ -5788,7 +5788,7 @@
         <v>-25.782039999999999</v>
       </c>
       <c r="B684">
-        <v>-4.5510000000000002E-2</v>
+        <v>-5.3330000000000002E-2</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.25">
@@ -5796,7 +5796,7 @@
         <v>-25.938020000000002</v>
       </c>
       <c r="B685">
-        <v>-4.5780000000000001E-2</v>
+        <v>-5.364E-2</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
@@ -5804,7 +5804,7 @@
         <v>-26.094000000000001</v>
       </c>
       <c r="B686">
-        <v>-4.6059999999999997E-2</v>
+        <v>-5.3949999999999998E-2</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
@@ -5812,7 +5812,7 @@
         <v>-26.24999</v>
       </c>
       <c r="B687">
-        <v>-4.6370000000000001E-2</v>
+        <v>-5.4309999999999997E-2</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.25">
@@ -5820,7 +5820,7 @@
         <v>-26.40597</v>
       </c>
       <c r="B688">
-        <v>-4.6640000000000001E-2</v>
+        <v>-5.4629999999999998E-2</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
         <v>-26.563310000000001</v>
       </c>
       <c r="B689">
-        <v>-4.691E-2</v>
+        <v>-5.4960000000000002E-2</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.25">
@@ -5836,7 +5836,7 @@
         <v>-26.719290000000001</v>
       </c>
       <c r="B690">
-        <v>-4.718E-2</v>
+        <v>-5.525E-2</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.25">
@@ -5844,7 +5844,7 @@
         <v>-26.87528</v>
       </c>
       <c r="B691">
-        <v>-4.743E-2</v>
+        <v>-5.5590000000000001E-2</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.25">
@@ -5852,7 +5852,7 @@
         <v>-27.03126</v>
       </c>
       <c r="B692">
-        <v>-4.7759999999999997E-2</v>
+        <v>-5.5960000000000003E-2</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.25">
@@ -5860,7 +5860,7 @@
         <v>-27.187239999999999</v>
       </c>
       <c r="B693">
-        <v>-4.802E-2</v>
+        <v>-5.6219999999999999E-2</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.25">
@@ -5868,7 +5868,7 @@
         <v>-27.34459</v>
       </c>
       <c r="B694">
-        <v>-4.8309999999999999E-2</v>
+        <v>-5.6520000000000001E-2</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
@@ -5876,7 +5876,7 @@
         <v>-27.50057</v>
       </c>
       <c r="B695">
-        <v>-4.8559999999999999E-2</v>
+        <v>-5.688E-2</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.25">
@@ -5884,7 +5884,7 @@
         <v>-27.656549999999999</v>
       </c>
       <c r="B696">
-        <v>-4.8840000000000001E-2</v>
+        <v>-5.722E-2</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.25">
@@ -5892,7 +5892,7 @@
         <v>-27.812529999999999</v>
       </c>
       <c r="B697">
-        <v>-4.913E-2</v>
+        <v>-5.7549999999999997E-2</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
         <v>-27.968520000000002</v>
       </c>
       <c r="B698">
-        <v>-4.9390000000000003E-2</v>
+        <v>-5.79E-2</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.25">
@@ -5908,7 +5908,7 @@
         <v>-28.125859999999999</v>
       </c>
       <c r="B699">
-        <v>-4.9639999999999997E-2</v>
+        <v>-5.8220000000000001E-2</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.25">
@@ -5916,7 +5916,7 @@
         <v>-28.281839999999999</v>
       </c>
       <c r="B700">
-        <v>-4.9950000000000001E-2</v>
+        <v>-5.8500000000000003E-2</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.25">
@@ -5924,7 +5924,7 @@
         <v>-28.437830000000002</v>
       </c>
       <c r="B701">
-        <v>-5.0220000000000001E-2</v>
+        <v>-5.8810000000000001E-2</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
@@ -5932,7 +5932,7 @@
         <v>-28.593810000000001</v>
       </c>
       <c r="B702">
-        <v>-5.049E-2</v>
+        <v>-5.919E-2</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
@@ -5940,7 +5940,7 @@
         <v>-28.749790000000001</v>
       </c>
       <c r="B703">
-        <v>-5.0770000000000003E-2</v>
+        <v>-5.9499999999999997E-2</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.25">
@@ -5948,7 +5948,7 @@
         <v>-28.907129999999999</v>
       </c>
       <c r="B704">
-        <v>-5.1049999999999998E-2</v>
+        <v>-5.9810000000000002E-2</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -5956,7 +5956,7 @@
         <v>-29.063120000000001</v>
       </c>
       <c r="B705">
-        <v>-5.1310000000000001E-2</v>
+        <v>-6.0130000000000003E-2</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.25">
@@ -5964,7 +5964,7 @@
         <v>-29.219100000000001</v>
       </c>
       <c r="B706">
-        <v>-5.16E-2</v>
+        <v>-6.0490000000000002E-2</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.25">
@@ -5972,7 +5972,7 @@
         <v>-29.375080000000001</v>
       </c>
       <c r="B707">
-        <v>-5.1889999999999999E-2</v>
+        <v>-6.0749999999999998E-2</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.25">
@@ -5980,7 +5980,7 @@
         <v>-29.53107</v>
       </c>
       <c r="B708">
-        <v>-5.2139999999999999E-2</v>
+        <v>-6.1109999999999998E-2</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.25">
@@ -5988,7 +5988,7 @@
         <v>-29.688410000000001</v>
       </c>
       <c r="B709">
-        <v>-5.2409999999999998E-2</v>
+        <v>-6.1440000000000002E-2</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.25">
@@ -5996,7 +5996,7 @@
         <v>-29.844390000000001</v>
       </c>
       <c r="B710">
-        <v>-5.2740000000000002E-2</v>
+        <v>-6.173E-2</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.25">
@@ -6004,7 +6004,7 @@
         <v>-30.00037</v>
       </c>
       <c r="B711">
-        <v>-5.2999999999999999E-2</v>
+        <v>-6.2059999999999997E-2</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>-30.156359999999999</v>
       </c>
       <c r="B712">
-        <v>-5.3310000000000003E-2</v>
+        <v>-6.2429999999999999E-2</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.25">
@@ -6020,7 +6020,7 @@
         <v>-30.312339999999999</v>
       </c>
       <c r="B713">
-        <v>-5.357E-2</v>
+        <v>-6.2740000000000004E-2</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.25">
@@ -6028,7 +6028,7 @@
         <v>-30.46968</v>
       </c>
       <c r="B714">
-        <v>-5.3839999999999999E-2</v>
+        <v>-6.3049999999999995E-2</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.25">
@@ -6036,7 +6036,7 @@
         <v>-30.62566</v>
       </c>
       <c r="B715">
-        <v>-5.4109999999999998E-2</v>
+        <v>-6.3399999999999998E-2</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.25">
@@ -6044,7 +6044,7 @@
         <v>-30.781649999999999</v>
       </c>
       <c r="B716">
-        <v>-5.441E-2</v>
+        <v>-6.368E-2</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.25">
@@ -6052,7 +6052,7 @@
         <v>-30.937629999999999</v>
       </c>
       <c r="B717">
-        <v>-5.4679999999999999E-2</v>
+        <v>-6.4009999999999997E-2</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.25">
@@ -6060,7 +6060,7 @@
         <v>-31.093610000000002</v>
       </c>
       <c r="B718">
-        <v>-5.4949999999999999E-2</v>
+        <v>-6.4350000000000004E-2</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.25">
@@ -6068,7 +6068,7 @@
         <v>-31.25095</v>
       </c>
       <c r="B719">
-        <v>-5.5259999999999997E-2</v>
+        <v>-6.4670000000000005E-2</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.25">
@@ -6076,7 +6076,7 @@
         <v>-31.406939999999999</v>
       </c>
       <c r="B720">
-        <v>-5.5480000000000002E-2</v>
+        <v>-6.5009999999999998E-2</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.25">
@@ -6084,7 +6084,7 @@
         <v>-31.562919999999998</v>
       </c>
       <c r="B721">
-        <v>-5.5730000000000002E-2</v>
+        <v>-6.5320000000000003E-2</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.25">
@@ -6092,7 +6092,7 @@
         <v>-31.718900000000001</v>
       </c>
       <c r="B722">
-        <v>-5.604E-2</v>
+        <v>-6.5680000000000002E-2</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.25">
@@ -6100,7 +6100,7 @@
         <v>-31.874890000000001</v>
       </c>
       <c r="B723">
-        <v>-5.6320000000000002E-2</v>
+        <v>-6.6009999999999999E-2</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.25">
@@ -6108,7 +6108,7 @@
         <v>-32.032229999999998</v>
       </c>
       <c r="B724">
-        <v>-5.6599999999999998E-2</v>
+        <v>-6.6299999999999998E-2</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.25">
@@ -6116,7 +6116,7 @@
         <v>-32.188209999999998</v>
       </c>
       <c r="B725">
-        <v>-5.6869999999999997E-2</v>
+        <v>-6.6600000000000006E-2</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -6124,7 +6124,7 @@
         <v>-32.344200000000001</v>
       </c>
       <c r="B726">
-        <v>-5.7169999999999999E-2</v>
+        <v>-6.6949999999999996E-2</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.25">
@@ -6132,7 +6132,7 @@
         <v>-32.50018</v>
       </c>
       <c r="B727">
-        <v>-5.7450000000000001E-2</v>
+        <v>-6.7299999999999999E-2</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.25">
@@ -6140,7 +6140,7 @@
         <v>-32.65616</v>
       </c>
       <c r="B728">
-        <v>-5.774E-2</v>
+        <v>-6.7599999999999993E-2</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.25">
@@ -6148,7 +6148,7 @@
         <v>-32.813499999999998</v>
       </c>
       <c r="B729">
-        <v>-5.8009999999999999E-2</v>
+        <v>-6.7949999999999997E-2</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.25">
@@ -6156,7 +6156,7 @@
         <v>-32.96949</v>
       </c>
       <c r="B730">
-        <v>-5.824E-2</v>
+        <v>-6.8260000000000001E-2</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.25">
@@ -6164,7 +6164,7 @@
         <v>-33.12547</v>
       </c>
       <c r="B731">
-        <v>-5.8569999999999997E-2</v>
+        <v>-6.8580000000000002E-2</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.25">
@@ -6172,7 +6172,7 @@
         <v>-33.28145</v>
       </c>
       <c r="B732">
-        <v>-5.883E-2</v>
+        <v>-6.8930000000000005E-2</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.25">
@@ -6180,7 +6180,7 @@
         <v>-33.437440000000002</v>
       </c>
       <c r="B733">
-        <v>-5.9089999999999997E-2</v>
+        <v>-6.9250000000000006E-2</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -6188,7 +6188,7 @@
         <v>-33.59478</v>
       </c>
       <c r="B734">
-        <v>-5.9380000000000002E-2</v>
+        <v>-6.9540000000000005E-2</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.25">
@@ -6196,7 +6196,7 @@
         <v>-33.75076</v>
       </c>
       <c r="B735">
-        <v>-5.9679999999999997E-2</v>
+        <v>-6.991E-2</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.25">
@@ -6204,7 +6204,7 @@
         <v>-33.906739999999999</v>
       </c>
       <c r="B736">
-        <v>-5.9950000000000003E-2</v>
+        <v>-7.0190000000000002E-2</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.25">
@@ -6212,7 +6212,7 @@
         <v>-34.062730000000002</v>
       </c>
       <c r="B737">
-        <v>-6.0229999999999999E-2</v>
+        <v>-7.0569999999999994E-2</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.25">
@@ -6220,7 +6220,7 @@
         <v>-34.218710000000002</v>
       </c>
       <c r="B738">
-        <v>-6.0470000000000003E-2</v>
+        <v>-7.0870000000000002E-2</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.25">
@@ -6228,7 +6228,7 @@
         <v>-34.376049999999999</v>
       </c>
       <c r="B739">
-        <v>-6.0789999999999997E-2</v>
+        <v>-7.1190000000000003E-2</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.25">
@@ -6236,7 +6236,7 @@
         <v>-34.532029999999999</v>
       </c>
       <c r="B740">
-        <v>-6.105E-2</v>
+        <v>-7.152E-2</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -6244,7 +6244,7 @@
         <v>-34.688009999999998</v>
       </c>
       <c r="B741">
-        <v>-6.1359999999999998E-2</v>
+        <v>-7.1859999999999993E-2</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.25">
@@ -6252,7 +6252,7 @@
         <v>-34.844000000000001</v>
       </c>
       <c r="B742">
-        <v>-6.164E-2</v>
+        <v>-7.2160000000000002E-2</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.25">
@@ -6260,7 +6260,7 @@
         <v>-34.999980000000001</v>
       </c>
       <c r="B743">
-        <v>-6.1870000000000001E-2</v>
+        <v>-7.2480000000000003E-2</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.25">
@@ -6268,7 +6268,7 @@
         <v>-35.157319999999999</v>
       </c>
       <c r="B744">
-        <v>-6.2140000000000001E-2</v>
+        <v>-7.2849999999999998E-2</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.25">
@@ -6276,7 +6276,7 @@
         <v>-35.313299999999998</v>
       </c>
       <c r="B745">
-        <v>-6.2460000000000002E-2</v>
+        <v>-7.3150000000000007E-2</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.25">
@@ -6284,7 +6284,7 @@
         <v>-35.469290000000001</v>
       </c>
       <c r="B746">
-        <v>-6.2740000000000004E-2</v>
+        <v>-7.3480000000000004E-2</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>-35.62527</v>
       </c>
       <c r="B747">
-        <v>-6.2990000000000004E-2</v>
+        <v>-7.3789999999999994E-2</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.25">
@@ -6300,7 +6300,7 @@
         <v>-35.781260000000003</v>
       </c>
       <c r="B748">
-        <v>-6.3250000000000001E-2</v>
+        <v>-7.4139999999999998E-2</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.25">
@@ -6308,7 +6308,7 @@
         <v>-35.938600000000001</v>
       </c>
       <c r="B749">
-        <v>-6.3519999999999993E-2</v>
+        <v>-7.4459999999999998E-2</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
@@ -6316,7 +6316,7 @@
         <v>-36.094580000000001</v>
       </c>
       <c r="B750">
-        <v>-6.3810000000000006E-2</v>
+        <v>-7.4779999999999999E-2</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.25">
@@ -6324,7 +6324,7 @@
         <v>-36.25056</v>
       </c>
       <c r="B751">
-        <v>-6.411E-2</v>
+        <v>-7.5120000000000006E-2</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
@@ -6332,7 +6332,7 @@
         <v>-36.406550000000003</v>
       </c>
       <c r="B752">
-        <v>-6.4390000000000003E-2</v>
+        <v>-7.5429999999999997E-2</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.25">
@@ -6340,7 +6340,7 @@
         <v>-36.562530000000002</v>
       </c>
       <c r="B753">
-        <v>-6.4680000000000001E-2</v>
+        <v>-7.5759999999999994E-2</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.25">
@@ -6348,7 +6348,7 @@
         <v>-36.71987</v>
       </c>
       <c r="B754">
-        <v>-6.4920000000000005E-2</v>
+        <v>-7.6090000000000005E-2</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.25">
@@ -6356,7 +6356,7 @@
         <v>-36.87585</v>
       </c>
       <c r="B755">
-        <v>-6.5210000000000004E-2</v>
+        <v>-7.6429999999999998E-2</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.25">
@@ -6364,7 +6364,7 @@
         <v>-37.031840000000003</v>
       </c>
       <c r="B756">
-        <v>-6.5540000000000001E-2</v>
+        <v>-7.6740000000000003E-2</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
@@ -6372,7 +6372,7 @@
         <v>-37.187820000000002</v>
       </c>
       <c r="B757">
-        <v>-6.5799999999999997E-2</v>
+        <v>-7.707E-2</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.25">
@@ -6380,7 +6380,7 @@
         <v>-37.343800000000002</v>
       </c>
       <c r="B758">
-        <v>-6.6040000000000001E-2</v>
+        <v>-7.7369999999999994E-2</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.25">
@@ -6388,7 +6388,7 @@
         <v>-37.501139999999999</v>
       </c>
       <c r="B759">
-        <v>-6.6339999999999996E-2</v>
+        <v>-7.7710000000000001E-2</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.25">
@@ -6396,7 +6396,7 @@
         <v>-37.657130000000002</v>
       </c>
       <c r="B760">
-        <v>-6.6650000000000001E-2</v>
+        <v>-7.8030000000000002E-2</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -6404,7 +6404,7 @@
         <v>-37.813110000000002</v>
       </c>
       <c r="B761">
-        <v>-6.6930000000000003E-2</v>
+        <v>-7.8390000000000001E-2</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
         <v>-37.969090000000001</v>
       </c>
       <c r="B762">
-        <v>-6.7150000000000001E-2</v>
+        <v>-7.8700000000000006E-2</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.25">
@@ -6420,7 +6420,7 @@
         <v>-38.125079999999997</v>
       </c>
       <c r="B763">
-        <v>-6.7449999999999996E-2</v>
+        <v>-7.9020000000000007E-2</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
@@ -6428,7 +6428,7 @@
         <v>-38.282420000000002</v>
       </c>
       <c r="B764">
-        <v>-6.7720000000000002E-2</v>
+        <v>-7.9350000000000004E-2</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.25">
@@ -6436,7 +6436,7 @@
         <v>-38.438400000000001</v>
       </c>
       <c r="B765">
-        <v>-6.8000000000000005E-2</v>
+        <v>-7.9659999999999995E-2</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.25">
@@ -6444,7 +6444,7 @@
         <v>-38.594389999999997</v>
       </c>
       <c r="B766">
-        <v>-6.8309999999999996E-2</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.25">
@@ -6452,7 +6452,7 @@
         <v>-38.750369999999997</v>
       </c>
       <c r="B767">
-        <v>-6.8559999999999996E-2</v>
+        <v>-8.0329999999999999E-2</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
@@ -6460,7 +6460,7 @@
         <v>-38.906350000000003</v>
       </c>
       <c r="B768">
-        <v>-6.8839999999999998E-2</v>
+        <v>-8.0629999999999993E-2</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.25">
@@ -6468,7 +6468,7 @@
         <v>-39.063690000000001</v>
       </c>
       <c r="B769">
-        <v>-6.9120000000000001E-2</v>
+        <v>-8.1009999999999999E-2</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.25">
@@ -6476,7 +6476,7 @@
         <v>-39.219679999999997</v>
       </c>
       <c r="B770">
-        <v>-6.9430000000000006E-2</v>
+        <v>-8.1320000000000003E-2</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.25">
@@ -6484,7 +6484,7 @@
         <v>-39.375660000000003</v>
       </c>
       <c r="B771">
-        <v>-6.9639999999999994E-2</v>
+        <v>-8.1640000000000004E-2</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.25">
@@ -6492,7 +6492,7 @@
         <v>-39.531640000000003</v>
       </c>
       <c r="B772">
-        <v>-6.9949999999999998E-2</v>
+        <v>-8.1989999999999993E-2</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.25">
@@ -6500,7 +6500,7 @@
         <v>-39.687629999999999</v>
       </c>
       <c r="B773">
-        <v>-7.0260000000000003E-2</v>
+        <v>-8.2299999999999998E-2</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.25">
@@ -6508,7 +6508,7 @@
         <v>-39.844970000000004</v>
       </c>
       <c r="B774">
-        <v>-7.0510000000000003E-2</v>
+        <v>-8.2629999999999995E-2</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.25">
@@ -6516,7 +6516,7 @@
         <v>-40.000950000000003</v>
       </c>
       <c r="B775">
-        <v>-7.0800000000000002E-2</v>
+        <v>-8.2919999999999994E-2</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.25">
@@ -6524,7 +6524,7 @@
         <v>-39.844970000000004</v>
       </c>
       <c r="B776">
-        <v>-7.0540000000000005E-2</v>
+        <v>-8.2629999999999995E-2</v>
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.25">
@@ -6532,7 +6532,7 @@
         <v>-39.687629999999999</v>
       </c>
       <c r="B777">
-        <v>-7.0309999999999997E-2</v>
+        <v>-8.2339999999999997E-2</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
@@ -6540,7 +6540,7 @@
         <v>-39.531640000000003</v>
       </c>
       <c r="B778">
-        <v>-7.0019999999999999E-2</v>
+        <v>-8.2030000000000006E-2</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.25">
@@ -6548,7 +6548,7 @@
         <v>-39.375660000000003</v>
       </c>
       <c r="B779">
-        <v>-6.9750000000000006E-2</v>
+        <v>-8.1680000000000003E-2</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.25">
@@ -6556,7 +6556,7 @@
         <v>-39.219679999999997</v>
       </c>
       <c r="B780">
-        <v>-6.9409999999999999E-2</v>
+        <v>-8.1339999999999996E-2</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.25">
@@ -6564,7 +6564,7 @@
         <v>-39.063690000000001</v>
       </c>
       <c r="B781">
-        <v>-6.9159999999999999E-2</v>
+        <v>-8.1079999999999999E-2</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.25">
@@ -6572,7 +6572,7 @@
         <v>-38.906350000000003</v>
       </c>
       <c r="B782">
-        <v>-6.8879999999999997E-2</v>
+        <v>-8.0710000000000004E-2</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>-38.750369999999997</v>
       </c>
       <c r="B783">
-        <v>-6.8570000000000006E-2</v>
+        <v>-8.0369999999999997E-2</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.25">
@@ -6588,7 +6588,7 @@
         <v>-38.594389999999997</v>
       </c>
       <c r="B784">
-        <v>-6.8320000000000006E-2</v>
+        <v>-8.0070000000000002E-2</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.25">
@@ -6596,7 +6596,7 @@
         <v>-38.438400000000001</v>
       </c>
       <c r="B785">
-        <v>-6.8049999999999999E-2</v>
+        <v>-7.9750000000000001E-2</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.25">
@@ -6604,7 +6604,7 @@
         <v>-38.282420000000002</v>
       </c>
       <c r="B786">
-        <v>-6.7820000000000005E-2</v>
+        <v>-7.9390000000000002E-2</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
@@ -6612,7 +6612,7 @@
         <v>-38.125079999999997</v>
       </c>
       <c r="B787">
-        <v>-6.7470000000000002E-2</v>
+        <v>-7.9070000000000001E-2</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.25">
@@ -6620,7 +6620,7 @@
         <v>-37.969090000000001</v>
       </c>
       <c r="B788">
-        <v>-6.7210000000000006E-2</v>
+        <v>-7.8740000000000004E-2</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.25">
@@ -6628,7 +6628,7 @@
         <v>-37.813110000000002</v>
       </c>
       <c r="B789">
-        <v>-6.6960000000000006E-2</v>
+        <v>-7.8399999999999997E-2</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.25">
@@ -6636,7 +6636,7 @@
         <v>-37.657130000000002</v>
       </c>
       <c r="B790">
-        <v>-6.6640000000000005E-2</v>
+        <v>-7.8130000000000005E-2</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.25">
@@ -6644,7 +6644,7 @@
         <v>-37.501139999999999</v>
       </c>
       <c r="B791">
-        <v>-6.6350000000000006E-2</v>
+        <v>-7.7770000000000006E-2</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.25">
@@ -6652,7 +6652,7 @@
         <v>-37.343800000000002</v>
       </c>
       <c r="B792">
-        <v>-6.6070000000000004E-2</v>
+        <v>-7.7469999999999997E-2</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.25">
@@ -6660,7 +6660,7 @@
         <v>-37.187820000000002</v>
       </c>
       <c r="B793">
-        <v>-6.5790000000000001E-2</v>
+        <v>-7.7100000000000002E-2</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.25">
@@ -6668,7 +6668,7 @@
         <v>-37.031840000000003</v>
       </c>
       <c r="B794">
-        <v>-6.5559999999999993E-2</v>
+        <v>-7.6799999999999993E-2</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.25">
@@ -6676,7 +6676,7 @@
         <v>-36.87585</v>
       </c>
       <c r="B795">
-        <v>-6.5259999999999999E-2</v>
+        <v>-7.646E-2</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.25">
@@ -6684,7 +6684,7 @@
         <v>-36.71987</v>
       </c>
       <c r="B796">
-        <v>-6.5019999999999994E-2</v>
+        <v>-7.6160000000000005E-2</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.25">
@@ -6692,7 +6692,7 @@
         <v>-36.562530000000002</v>
       </c>
       <c r="B797">
-        <v>-6.4680000000000001E-2</v>
+        <v>-7.5819999999999999E-2</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.25">
@@ -6700,7 +6700,7 @@
         <v>-36.406550000000003</v>
       </c>
       <c r="B798">
-        <v>-6.4409999999999995E-2</v>
+        <v>-7.5490000000000002E-2</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.25">
@@ -6708,7 +6708,7 @@
         <v>-36.25056</v>
       </c>
       <c r="B799">
-        <v>-6.4170000000000005E-2</v>
+        <v>-7.5160000000000005E-2</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.25">
@@ -6716,7 +6716,7 @@
         <v>-36.094580000000001</v>
       </c>
       <c r="B800">
-        <v>-6.3869999999999996E-2</v>
+        <v>-7.4840000000000004E-2</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.25">
@@ -6724,7 +6724,7 @@
         <v>-35.938600000000001</v>
       </c>
       <c r="B801">
-        <v>-6.3600000000000004E-2</v>
+        <v>-7.4529999999999999E-2</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.25">
@@ -6732,7 +6732,7 @@
         <v>-35.781260000000003</v>
       </c>
       <c r="B802">
-        <v>-6.3329999999999997E-2</v>
+        <v>-7.4190000000000006E-2</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.25">
@@ -6740,7 +6740,7 @@
         <v>-35.62527</v>
       </c>
       <c r="B803">
-        <v>-6.3020000000000007E-2</v>
+        <v>-7.3830000000000007E-2</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.25">
@@ -6748,7 +6748,7 @@
         <v>-35.469290000000001</v>
       </c>
       <c r="B804">
-        <v>-6.2789999999999999E-2</v>
+        <v>-7.3550000000000004E-2</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.25">
@@ -6756,7 +6756,7 @@
         <v>-35.313299999999998</v>
       </c>
       <c r="B805">
-        <v>-6.2460000000000002E-2</v>
+        <v>-7.3219999999999993E-2</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.25">
@@ -6764,7 +6764,7 @@
         <v>-35.157319999999999</v>
       </c>
       <c r="B806">
-        <v>-6.2199999999999998E-2</v>
+        <v>-7.288E-2</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.25">
@@ -6772,7 +6772,7 @@
         <v>-34.999980000000001</v>
       </c>
       <c r="B807">
-        <v>-6.1949999999999998E-2</v>
+        <v>-7.2559999999999999E-2</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.25">
@@ -6780,7 +6780,7 @@
         <v>-34.844000000000001</v>
       </c>
       <c r="B808">
-        <v>-6.164E-2</v>
+        <v>-7.22E-2</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.25">
@@ -6788,7 +6788,7 @@
         <v>-34.688009999999998</v>
       </c>
       <c r="B809">
-        <v>-6.132E-2</v>
+        <v>-7.1900000000000006E-2</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.25">
@@ -6796,7 +6796,7 @@
         <v>-34.532029999999999</v>
       </c>
       <c r="B810">
-        <v>-6.1120000000000001E-2</v>
+        <v>-7.1580000000000005E-2</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.25">
@@ -6804,7 +6804,7 @@
         <v>-34.376049999999999</v>
       </c>
       <c r="B811">
-        <v>-6.0810000000000003E-2</v>
+        <v>-7.1260000000000004E-2</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.25">
@@ -6812,7 +6812,7 @@
         <v>-34.218710000000002</v>
       </c>
       <c r="B812">
-        <v>-6.0569999999999999E-2</v>
+        <v>-7.0940000000000003E-2</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.25">
@@ -6820,7 +6820,7 @@
         <v>-34.062730000000002</v>
       </c>
       <c r="B813">
-        <v>-6.0269999999999997E-2</v>
+        <v>-7.0620000000000002E-2</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.25">
@@ -6828,7 +6828,7 @@
         <v>-33.906739999999999</v>
       </c>
       <c r="B814">
-        <v>-5.9959999999999999E-2</v>
+        <v>-7.0300000000000001E-2</v>
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.25">
@@ -6836,7 +6836,7 @@
         <v>-33.75076</v>
       </c>
       <c r="B815">
-        <v>-5.9720000000000002E-2</v>
+        <v>-6.9940000000000002E-2</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.25">
@@ -6844,7 +6844,7 @@
         <v>-33.59478</v>
       </c>
       <c r="B816">
-        <v>-5.9429999999999997E-2</v>
+        <v>-6.9620000000000001E-2</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.25">
@@ -6852,7 +6852,7 @@
         <v>-33.437440000000002</v>
       </c>
       <c r="B817">
-        <v>-5.9130000000000002E-2</v>
+        <v>-6.9320000000000007E-2</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
@@ -6860,7 +6860,7 @@
         <v>-33.28145</v>
       </c>
       <c r="B818">
-        <v>-5.8880000000000002E-2</v>
+        <v>-6.8970000000000004E-2</v>
       </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.25">
@@ -6868,7 +6868,7 @@
         <v>-33.12547</v>
       </c>
       <c r="B819">
-        <v>-5.8569999999999997E-2</v>
+        <v>-6.8650000000000003E-2</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.25">
@@ -6876,7 +6876,7 @@
         <v>-32.96949</v>
       </c>
       <c r="B820">
-        <v>-5.833E-2</v>
+        <v>-6.8309999999999996E-2</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.25">
@@ -6884,7 +6884,7 @@
         <v>-32.813499999999998</v>
       </c>
       <c r="B821">
-        <v>-5.806E-2</v>
+        <v>-6.8019999999999997E-2</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
@@ -6892,7 +6892,7 @@
         <v>-32.65616</v>
       </c>
       <c r="B822">
-        <v>-5.7759999999999999E-2</v>
+        <v>-6.7680000000000004E-2</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.25">
@@ -6900,7 +6900,7 @@
         <v>-32.50018</v>
       </c>
       <c r="B823">
-        <v>-5.747E-2</v>
+        <v>-6.7369999999999999E-2</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.25">
@@ -6908,7 +6908,7 @@
         <v>-32.344200000000001</v>
       </c>
       <c r="B824">
-        <v>-5.7200000000000001E-2</v>
+        <v>-6.7040000000000002E-2</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.25">
@@ -6916,7 +6916,7 @@
         <v>-32.188209999999998</v>
       </c>
       <c r="B825">
-        <v>-5.6899999999999999E-2</v>
+        <v>-6.6710000000000005E-2</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.25">
@@ -6924,7 +6924,7 @@
         <v>-32.032229999999998</v>
       </c>
       <c r="B826">
-        <v>-5.6640000000000003E-2</v>
+        <v>-6.6350000000000006E-2</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.25">
@@ -6932,7 +6932,7 @@
         <v>-31.874890000000001</v>
       </c>
       <c r="B827">
-        <v>-5.638E-2</v>
+        <v>-6.6070000000000004E-2</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
@@ -6940,7 +6940,7 @@
         <v>-31.718900000000001</v>
       </c>
       <c r="B828">
-        <v>-5.6059999999999999E-2</v>
+        <v>-6.5720000000000001E-2</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.25">
@@ -6948,7 +6948,7 @@
         <v>-31.562919999999998</v>
       </c>
       <c r="B829">
-        <v>-5.5809999999999998E-2</v>
+        <v>-6.5430000000000002E-2</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
@@ -6956,7 +6956,7 @@
         <v>-31.406939999999999</v>
       </c>
       <c r="B830">
-        <v>-5.5530000000000003E-2</v>
+        <v>-6.5070000000000003E-2</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
@@ -6964,7 +6964,7 @@
         <v>-31.25095</v>
       </c>
       <c r="B831">
-        <v>-5.5280000000000003E-2</v>
+        <v>-6.4729999999999996E-2</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.25">
@@ -6972,7 +6972,7 @@
         <v>-31.093610000000002</v>
       </c>
       <c r="B832">
-        <v>-5.4989999999999997E-2</v>
+        <v>-6.4399999999999999E-2</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.25">
@@ -6980,7 +6980,7 @@
         <v>-30.937629999999999</v>
       </c>
       <c r="B833">
-        <v>-5.4730000000000001E-2</v>
+        <v>-6.4100000000000004E-2</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.25">
@@ -6988,7 +6988,7 @@
         <v>-30.781649999999999</v>
       </c>
       <c r="B834">
-        <v>-5.441E-2</v>
+        <v>-6.3769999999999993E-2</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.25">
@@ -6996,7 +6996,7 @@
         <v>-30.62566</v>
       </c>
       <c r="B835">
-        <v>-5.4170000000000003E-2</v>
+        <v>-6.3450000000000006E-2</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.25">
@@ -7004,7 +7004,7 @@
         <v>-30.46968</v>
       </c>
       <c r="B836">
-        <v>-5.3900000000000003E-2</v>
+        <v>-6.3109999999999999E-2</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.25">
@@ -7012,7 +7012,7 @@
         <v>-30.312339999999999</v>
       </c>
       <c r="B837">
-        <v>-5.3609999999999998E-2</v>
+        <v>-6.2799999999999995E-2</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.25">
@@ -7020,7 +7020,7 @@
         <v>-30.156359999999999</v>
       </c>
       <c r="B838">
-        <v>-5.3310000000000003E-2</v>
+        <v>-6.2489999999999997E-2</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.25">
@@ -7028,7 +7028,7 @@
         <v>-30.00037</v>
       </c>
       <c r="B839">
-        <v>-5.3039999999999997E-2</v>
+        <v>-6.2140000000000001E-2</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.25">
@@ -7036,7 +7036,7 @@
         <v>-29.844390000000001</v>
       </c>
       <c r="B840">
-        <v>-5.2780000000000001E-2</v>
+        <v>-6.1789999999999998E-2</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.25">
@@ -7044,7 +7044,7 @@
         <v>-29.688410000000001</v>
       </c>
       <c r="B841">
-        <v>-5.246E-2</v>
+        <v>-6.1550000000000001E-2</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.25">
@@ -7052,7 +7052,7 @@
         <v>-29.53107</v>
       </c>
       <c r="B842">
-        <v>-5.2200000000000003E-2</v>
+        <v>-6.1159999999999999E-2</v>
       </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.25">
@@ -7060,7 +7060,7 @@
         <v>-29.375080000000001</v>
       </c>
       <c r="B843">
-        <v>-5.1920000000000001E-2</v>
+        <v>-6.0839999999999998E-2</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.25">
@@ -7068,7 +7068,7 @@
         <v>-29.219100000000001</v>
       </c>
       <c r="B844">
-        <v>-5.1659999999999998E-2</v>
+        <v>-6.053E-2</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>-29.063120000000001</v>
       </c>
       <c r="B845">
-        <v>-5.1339999999999997E-2</v>
+        <v>-6.0199999999999997E-2</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7084,7 @@
         <v>-28.907129999999999</v>
       </c>
       <c r="B846">
-        <v>-5.11E-2</v>
+        <v>-5.9900000000000002E-2</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>-28.749790000000001</v>
       </c>
       <c r="B847">
-        <v>-5.0810000000000001E-2</v>
+        <v>-5.9560000000000002E-2</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>-28.593810000000001</v>
       </c>
       <c r="B848">
-        <v>-5.0520000000000002E-2</v>
+        <v>-5.9200000000000003E-2</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
         <v>-28.437830000000002</v>
       </c>
       <c r="B849">
-        <v>-5.0250000000000003E-2</v>
+        <v>-5.8909999999999997E-2</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>-28.281839999999999</v>
       </c>
       <c r="B850">
-        <v>-4.999E-2</v>
+        <v>-5.858E-2</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>-28.125859999999999</v>
       </c>
       <c r="B851">
-        <v>-4.9700000000000001E-2</v>
+        <v>-5.824E-2</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7132,7 @@
         <v>-27.968520000000002</v>
       </c>
       <c r="B852">
-        <v>-4.9439999999999998E-2</v>
+        <v>-5.7910000000000003E-2</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>-27.812529999999999</v>
       </c>
       <c r="B853">
-        <v>-4.9140000000000003E-2</v>
+        <v>-5.7570000000000003E-2</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7148,7 @@
         <v>-27.656549999999999</v>
       </c>
       <c r="B854">
-        <v>-4.8849999999999998E-2</v>
+        <v>-5.7270000000000001E-2</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>-27.50057</v>
       </c>
       <c r="B855">
-        <v>-4.8619999999999997E-2</v>
+        <v>-5.6930000000000001E-2</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
@@ -7164,7 +7164,7 @@
         <v>-27.34459</v>
       </c>
       <c r="B856">
-        <v>-4.829E-2</v>
+        <v>-5.6599999999999998E-2</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7172,7 @@
         <v>-27.187239999999999</v>
       </c>
       <c r="B857">
-        <v>-4.8079999999999998E-2</v>
+        <v>-5.629E-2</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>-27.03126</v>
       </c>
       <c r="B858">
-        <v>-4.7750000000000001E-2</v>
+        <v>-5.5980000000000002E-2</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7188,7 @@
         <v>-26.87528</v>
       </c>
       <c r="B859">
-        <v>-4.7469999999999998E-2</v>
+        <v>-5.5660000000000001E-2</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
         <v>-26.719290000000001</v>
       </c>
       <c r="B860">
-        <v>-4.7219999999999998E-2</v>
+        <v>-5.5350000000000003E-2</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7204,7 @@
         <v>-26.563310000000001</v>
       </c>
       <c r="B861">
-        <v>-4.6929999999999999E-2</v>
+        <v>-5.5019999999999999E-2</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7212,7 @@
         <v>-26.40597</v>
       </c>
       <c r="B862">
-        <v>-4.6690000000000002E-2</v>
+        <v>-5.4670000000000003E-2</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>-26.24999</v>
       </c>
       <c r="B863">
-        <v>-4.632E-2</v>
+        <v>-5.4370000000000002E-2</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>-26.094000000000001</v>
       </c>
       <c r="B864">
-        <v>-4.6089999999999999E-2</v>
+        <v>-5.4059999999999997E-2</v>
       </c>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7236,7 @@
         <v>-25.938020000000002</v>
       </c>
       <c r="B865">
-        <v>-4.582E-2</v>
+        <v>-5.3670000000000002E-2</v>
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7244,7 @@
         <v>-25.782039999999999</v>
       </c>
       <c r="B866">
-        <v>-4.5560000000000003E-2</v>
+        <v>-5.339E-2</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7252,7 @@
         <v>-25.624700000000001</v>
       </c>
       <c r="B867">
-        <v>-4.5310000000000003E-2</v>
+        <v>-5.305E-2</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7260,7 @@
         <v>-25.468710000000002</v>
       </c>
       <c r="B868">
-        <v>-4.4990000000000002E-2</v>
+        <v>-5.271E-2</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>-25.312729999999998</v>
       </c>
       <c r="B869">
-        <v>-4.4740000000000002E-2</v>
+        <v>-5.2400000000000002E-2</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7276,7 @@
         <v>-25.156749999999999</v>
       </c>
       <c r="B870">
-        <v>-4.4450000000000003E-2</v>
+        <v>-5.2069999999999998E-2</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7284,7 @@
         <v>-25.00076</v>
       </c>
       <c r="B871">
-        <v>-4.419E-2</v>
+        <v>-5.1749999999999997E-2</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>-24.843419999999998</v>
       </c>
       <c r="B872">
-        <v>-4.3920000000000001E-2</v>
+        <v>-5.142E-2</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>-24.687439999999999</v>
       </c>
       <c r="B873">
-        <v>-4.3610000000000003E-2</v>
+        <v>-5.1110000000000003E-2</v>
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>-24.531459999999999</v>
       </c>
       <c r="B874">
-        <v>-4.335E-2</v>
+        <v>-5.0779999999999999E-2</v>
       </c>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7316,7 @@
         <v>-24.37547</v>
       </c>
       <c r="B875">
-        <v>-4.3090000000000003E-2</v>
+        <v>-5.0430000000000003E-2</v>
       </c>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7324,7 @@
         <v>-24.21949</v>
       </c>
       <c r="B876">
-        <v>-4.2770000000000002E-2</v>
+        <v>-5.0139999999999997E-2</v>
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>-24.062149999999999</v>
       </c>
       <c r="B877">
-        <v>-4.2509999999999999E-2</v>
+        <v>-4.9820000000000003E-2</v>
       </c>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7340,7 @@
         <v>-23.906169999999999</v>
       </c>
       <c r="B878">
-        <v>-4.2250000000000003E-2</v>
+        <v>-4.9459999999999997E-2</v>
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>-23.75018</v>
       </c>
       <c r="B879">
-        <v>-4.1950000000000001E-2</v>
+        <v>-4.9149999999999999E-2</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7356,7 @@
         <v>-23.594200000000001</v>
       </c>
       <c r="B880">
-        <v>-4.1660000000000003E-2</v>
+        <v>-4.8820000000000002E-2</v>
       </c>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7364,7 @@
         <v>-23.438220000000001</v>
       </c>
       <c r="B881">
-        <v>-4.138E-2</v>
+        <v>-4.8500000000000001E-2</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7372,7 @@
         <v>-23.28088</v>
       </c>
       <c r="B882">
-        <v>-4.1099999999999998E-2</v>
+        <v>-4.8169999999999998E-2</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>-23.124890000000001</v>
       </c>
       <c r="B883">
-        <v>-4.0829999999999998E-2</v>
+        <v>-4.786E-2</v>
       </c>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>-22.968910000000001</v>
       </c>
       <c r="B884">
-        <v>-4.0570000000000002E-2</v>
+        <v>-4.7539999999999999E-2</v>
       </c>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7396,7 @@
         <v>-22.812930000000001</v>
       </c>
       <c r="B885">
-        <v>-4.0320000000000002E-2</v>
+        <v>-4.7199999999999999E-2</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7404,7 @@
         <v>-22.656939999999999</v>
       </c>
       <c r="B886">
-        <v>-4.0030000000000003E-2</v>
+        <v>-4.6870000000000002E-2</v>
       </c>
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>-22.499600000000001</v>
       </c>
       <c r="B887">
-        <v>-3.9730000000000001E-2</v>
+        <v>-4.657E-2</v>
       </c>
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>-22.343620000000001</v>
       </c>
       <c r="B888">
-        <v>-3.9469999999999998E-2</v>
+        <v>-4.6219999999999997E-2</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7428,7 @@
         <v>-22.187639999999998</v>
       </c>
       <c r="B889">
-        <v>-3.9210000000000002E-2</v>
+        <v>-4.5929999999999999E-2</v>
       </c>
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7436,7 @@
         <v>-22.031649999999999</v>
       </c>
       <c r="B890">
-        <v>-3.8929999999999999E-2</v>
+        <v>-4.5609999999999998E-2</v>
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.25">
@@ -7444,7 +7444,7 @@
         <v>-21.87567</v>
       </c>
       <c r="B891">
-        <v>-3.8629999999999998E-2</v>
+        <v>-4.5280000000000001E-2</v>
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>-21.718330000000002</v>
       </c>
       <c r="B892">
-        <v>-3.8330000000000003E-2</v>
+        <v>-4.4940000000000001E-2</v>
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.25">
@@ -7460,7 +7460,7 @@
         <v>-21.562339999999999</v>
       </c>
       <c r="B893">
-        <v>-3.8059999999999997E-2</v>
+        <v>-4.4600000000000001E-2</v>
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>-21.406359999999999</v>
       </c>
       <c r="B894">
-        <v>-3.7789999999999997E-2</v>
+        <v>-4.4310000000000002E-2</v>
       </c>
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
         <v>-21.25038</v>
       </c>
       <c r="B895">
-        <v>-3.7530000000000001E-2</v>
+        <v>-4.3990000000000001E-2</v>
       </c>
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7484,7 @@
         <v>-21.094390000000001</v>
       </c>
       <c r="B896">
-        <v>-3.7229999999999999E-2</v>
+        <v>-4.3650000000000001E-2</v>
       </c>
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7492,7 @@
         <v>-20.937049999999999</v>
       </c>
       <c r="B897">
-        <v>-3.6949999999999997E-2</v>
+        <v>-4.333E-2</v>
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>-20.78107</v>
       </c>
       <c r="B898">
-        <v>-3.6650000000000002E-2</v>
+        <v>-4.299E-2</v>
       </c>
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>-20.62509</v>
       </c>
       <c r="B899">
-        <v>-3.6409999999999998E-2</v>
+        <v>-4.2720000000000001E-2</v>
       </c>
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>-20.469100000000001</v>
       </c>
       <c r="B900">
-        <v>-3.6150000000000002E-2</v>
+        <v>-4.233E-2</v>
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7524,7 @@
         <v>-20.313120000000001</v>
       </c>
       <c r="B901">
-        <v>-3.5860000000000003E-2</v>
+        <v>-4.199E-2</v>
       </c>
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7532,7 @@
         <v>-20.15578</v>
       </c>
       <c r="B902">
-        <v>-3.5560000000000001E-2</v>
+        <v>-4.1709999999999997E-2</v>
       </c>
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>-19.9998</v>
       </c>
       <c r="B903">
-        <v>-3.5270000000000003E-2</v>
+        <v>-4.1390000000000003E-2</v>
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
         <v>-19.843810000000001</v>
       </c>
       <c r="B904">
-        <v>-3.5040000000000002E-2</v>
+        <v>-4.1059999999999999E-2</v>
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.25">
@@ -7556,7 +7556,7 @@
         <v>-19.687830000000002</v>
       </c>
       <c r="B905">
-        <v>-3.4790000000000001E-2</v>
+        <v>-4.0719999999999999E-2</v>
       </c>
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
         <v>-19.531849999999999</v>
       </c>
       <c r="B906">
-        <v>-3.4470000000000001E-2</v>
+        <v>-4.0390000000000002E-2</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>-19.374510000000001</v>
       </c>
       <c r="B907">
-        <v>-3.422E-2</v>
+        <v>-4.0099999999999997E-2</v>
       </c>
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>-19.218520000000002</v>
       </c>
       <c r="B908">
-        <v>-3.3950000000000001E-2</v>
+        <v>-3.9750000000000001E-2</v>
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>-19.062539999999998</v>
       </c>
       <c r="B909">
-        <v>-3.3649999999999999E-2</v>
+        <v>-3.943E-2</v>
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7596,7 @@
         <v>-18.906559999999999</v>
       </c>
       <c r="B910">
-        <v>-3.338E-2</v>
+        <v>-3.9129999999999998E-2</v>
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7604,7 @@
         <v>-18.75057</v>
       </c>
       <c r="B911">
-        <v>-3.3090000000000001E-2</v>
+        <v>-3.8809999999999997E-2</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.25">
@@ -7612,7 +7612,7 @@
         <v>-18.593229999999998</v>
       </c>
       <c r="B912">
-        <v>-3.2820000000000002E-2</v>
+        <v>-3.8420000000000003E-2</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>-18.437249999999999</v>
       </c>
       <c r="B913">
-        <v>-3.2530000000000003E-2</v>
+        <v>-3.8109999999999998E-2</v>
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7628,7 @@
         <v>-18.281269999999999</v>
       </c>
       <c r="B914">
-        <v>-3.2210000000000003E-2</v>
+        <v>-3.7830000000000003E-2</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7636,7 @@
         <v>-18.12528</v>
       </c>
       <c r="B915">
-        <v>-3.1969999999999998E-2</v>
+        <v>-3.7470000000000003E-2</v>
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7644,7 @@
         <v>-17.9693</v>
       </c>
       <c r="B916">
-        <v>-3.1759999999999997E-2</v>
+        <v>-3.7159999999999999E-2</v>
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
         <v>-17.811959999999999</v>
       </c>
       <c r="B917">
-        <v>-3.1440000000000003E-2</v>
+        <v>-3.6859999999999997E-2</v>
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7660,7 @@
         <v>-17.65598</v>
       </c>
       <c r="B918">
-        <v>-3.1150000000000001E-2</v>
+        <v>-3.653E-2</v>
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>-17.49999</v>
       </c>
       <c r="B919">
-        <v>-3.09E-2</v>
+        <v>-3.619E-2</v>
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7676,7 @@
         <v>-17.344010000000001</v>
       </c>
       <c r="B920">
-        <v>-3.0609999999999998E-2</v>
+        <v>-3.5839999999999997E-2</v>
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>-17.188020000000002</v>
       </c>
       <c r="B921">
-        <v>-3.0380000000000001E-2</v>
+        <v>-3.5529999999999999E-2</v>
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.25">
@@ -7692,7 +7692,7 @@
         <v>-17.03069</v>
       </c>
       <c r="B922">
-        <v>-3.0099999999999998E-2</v>
+        <v>-3.5209999999999998E-2</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>-16.874700000000001</v>
       </c>
       <c r="B923">
-        <v>-2.9770000000000001E-2</v>
+        <v>-3.492E-2</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.25">
@@ -7708,7 +7708,7 @@
         <v>-16.718720000000001</v>
       </c>
       <c r="B924">
-        <v>-2.9520000000000001E-2</v>
+        <v>-3.4590000000000003E-2</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.25">
@@ -7716,7 +7716,7 @@
         <v>-16.562729999999998</v>
       </c>
       <c r="B925">
-        <v>-2.921E-2</v>
+        <v>-3.4229999999999997E-2</v>
       </c>
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.25">
@@ -7724,7 +7724,7 @@
         <v>-16.406749999999999</v>
       </c>
       <c r="B926">
-        <v>-2.8989999999999998E-2</v>
+        <v>-3.3919999999999999E-2</v>
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.25">
@@ -7732,7 +7732,7 @@
         <v>-16.249410000000001</v>
       </c>
       <c r="B927">
-        <v>-2.87E-2</v>
+        <v>-3.363E-2</v>
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.25">
@@ -7740,7 +7740,7 @@
         <v>-16.093430000000001</v>
       </c>
       <c r="B928">
-        <v>-2.8420000000000001E-2</v>
+        <v>-3.3279999999999997E-2</v>
       </c>
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.25">
@@ -7748,7 +7748,7 @@
         <v>-15.93744</v>
       </c>
       <c r="B929">
-        <v>-2.8139999999999998E-2</v>
+        <v>-3.2980000000000002E-2</v>
       </c>
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.25">
@@ -7756,7 +7756,7 @@
         <v>-15.781459999999999</v>
       </c>
       <c r="B930">
-        <v>-2.785E-2</v>
+        <v>-3.2660000000000002E-2</v>
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.25">
@@ -7764,7 +7764,7 @@
         <v>-15.62548</v>
       </c>
       <c r="B931">
-        <v>-2.7570000000000001E-2</v>
+        <v>-3.2300000000000002E-2</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.25">
@@ -7772,7 +7772,7 @@
         <v>-15.46814</v>
       </c>
       <c r="B932">
-        <v>-2.7320000000000001E-2</v>
+        <v>-3.1989999999999998E-2</v>
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.25">
@@ -7780,7 +7780,7 @@
         <v>-15.312150000000001</v>
       </c>
       <c r="B933">
-        <v>-2.7060000000000001E-2</v>
+        <v>-3.1669999999999997E-2</v>
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.25">
@@ -7788,7 +7788,7 @@
         <v>-15.156169999999999</v>
       </c>
       <c r="B934">
-        <v>-2.6749999999999999E-2</v>
+        <v>-3.1300000000000001E-2</v>
       </c>
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.25">
@@ -7796,7 +7796,7 @@
         <v>-15.00019</v>
       </c>
       <c r="B935">
-        <v>-2.647E-2</v>
+        <v>-3.1019999999999999E-2</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
         <v>-14.844200000000001</v>
       </c>
       <c r="B936">
-        <v>-2.6169999999999999E-2</v>
+        <v>-3.0720000000000001E-2</v>
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.25">
@@ -7812,7 +7812,7 @@
         <v>-14.686859999999999</v>
       </c>
       <c r="B937">
-        <v>-2.5940000000000001E-2</v>
+        <v>-3.0360000000000002E-2</v>
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.25">
@@ -7820,7 +7820,7 @@
         <v>-14.53088</v>
       </c>
       <c r="B938">
-        <v>-2.5669999999999998E-2</v>
+        <v>-3.006E-2</v>
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.25">
@@ -7828,7 +7828,7 @@
         <v>-14.3749</v>
       </c>
       <c r="B939">
-        <v>-2.5399999999999999E-2</v>
+        <v>-2.9760000000000002E-2</v>
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.25">
@@ -7836,7 +7836,7 @@
         <v>-14.218909999999999</v>
       </c>
       <c r="B940">
-        <v>-2.5069999999999999E-2</v>
+        <v>-2.938E-2</v>
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.25">
@@ -7844,7 +7844,7 @@
         <v>-14.06293</v>
       </c>
       <c r="B941">
-        <v>-2.478E-2</v>
+        <v>-2.9049999999999999E-2</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.25">
@@ -7852,7 +7852,7 @@
         <v>-13.90559</v>
       </c>
       <c r="B942">
-        <v>-2.452E-2</v>
+        <v>-2.8709999999999999E-2</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.25">
@@ -7860,7 +7860,7 @@
         <v>-13.749610000000001</v>
       </c>
       <c r="B943">
-        <v>-2.4230000000000002E-2</v>
+        <v>-2.8420000000000001E-2</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
@@ -7868,7 +7868,7 @@
         <v>-13.59362</v>
       </c>
       <c r="B944">
-        <v>-2.3970000000000002E-2</v>
+        <v>-2.8139999999999998E-2</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.25">
@@ -7876,7 +7876,7 @@
         <v>-13.43764</v>
       </c>
       <c r="B945">
-        <v>-2.368E-2</v>
+        <v>-2.7779999999999999E-2</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>-13.28166</v>
       </c>
       <c r="B946">
-        <v>-2.3439999999999999E-2</v>
+        <v>-2.7470000000000001E-2</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
@@ -7892,7 +7892,7 @@
         <v>-13.124320000000001</v>
       </c>
       <c r="B947">
-        <v>-2.315E-2</v>
+        <v>-2.7150000000000001E-2</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.25">
@@ -7900,7 +7900,7 @@
         <v>-12.96833</v>
       </c>
       <c r="B948">
-        <v>-2.2849999999999999E-2</v>
+        <v>-2.6780000000000002E-2</v>
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.25">
@@ -7908,7 +7908,7 @@
         <v>-12.81235</v>
       </c>
       <c r="B949">
-        <v>-2.2599999999999999E-2</v>
+        <v>-2.647E-2</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.25">
@@ -7916,7 +7916,7 @@
         <v>-12.656370000000001</v>
       </c>
       <c r="B950">
-        <v>-2.2290000000000001E-2</v>
+        <v>-2.6179999999999998E-2</v>
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.25">
@@ -7924,7 +7924,7 @@
         <v>-12.50038</v>
       </c>
       <c r="B951">
-        <v>-2.206E-2</v>
+        <v>-2.5839999999999998E-2</v>
       </c>
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.25">
@@ -7932,7 +7932,7 @@
         <v>-12.34304</v>
       </c>
       <c r="B952">
-        <v>-2.172E-2</v>
+        <v>-2.5510000000000001E-2</v>
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.25">
@@ -7940,7 +7940,7 @@
         <v>-12.187060000000001</v>
       </c>
       <c r="B953">
-        <v>-2.145E-2</v>
+        <v>-2.521E-2</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.25">
@@ -7948,7 +7948,7 @@
         <v>-12.03107</v>
       </c>
       <c r="B954">
-        <v>-2.112E-2</v>
+        <v>-2.486E-2</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.25">
@@ -7956,7 +7956,7 @@
         <v>-11.87509</v>
       </c>
       <c r="B955">
-        <v>-2.069E-2</v>
+        <v>-2.452E-2</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.25">
@@ -7964,7 +7964,7 @@
         <v>-11.719110000000001</v>
       </c>
       <c r="B956">
-        <v>-2.0250000000000001E-2</v>
+        <v>-2.418E-2</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.25">
@@ -7972,7 +7972,7 @@
         <v>-11.561769999999999</v>
       </c>
       <c r="B957">
-        <v>-1.9699999999999999E-2</v>
+        <v>-2.3869999999999999E-2</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.25">
@@ -7980,7 +7980,7 @@
         <v>-11.40578</v>
       </c>
       <c r="B958">
-        <v>-1.9040000000000001E-2</v>
+        <v>-2.3529999999999999E-2</v>
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.25">
@@ -7988,7 +7988,7 @@
         <v>-11.2498</v>
       </c>
       <c r="B959">
-        <v>-1.839E-2</v>
+        <v>-2.325E-2</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.25">
@@ -7996,7 +7996,7 @@
         <v>-11.093819999999999</v>
       </c>
       <c r="B960">
-        <v>-1.7690000000000001E-2</v>
+        <v>-2.2929999999999999E-2</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.25">
@@ -8004,7 +8004,7 @@
         <v>-10.93783</v>
       </c>
       <c r="B961">
-        <v>-1.7069999999999998E-2</v>
+        <v>-2.2589999999999999E-2</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.25">
@@ -8012,7 +8012,7 @@
         <v>-10.78049</v>
       </c>
       <c r="B962">
-        <v>-1.6400000000000001E-2</v>
+        <v>-2.23E-2</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.25">
@@ -8020,7 +8020,7 @@
         <v>-10.624510000000001</v>
       </c>
       <c r="B963">
-        <v>-1.5650000000000001E-2</v>
+        <v>-2.1940000000000001E-2</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.25">
@@ -8028,7 +8028,7 @@
         <v>-10.468529999999999</v>
       </c>
       <c r="B964">
-        <v>-1.487E-2</v>
+        <v>-2.162E-2</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.25">
@@ -8036,7 +8036,7 @@
         <v>-10.31254</v>
       </c>
       <c r="B965">
-        <v>-1.396E-2</v>
+        <v>-2.1309999999999999E-2</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.25">
@@ -8044,7 +8044,7 @@
         <v>-10.156560000000001</v>
       </c>
       <c r="B966">
-        <v>-1.294E-2</v>
+        <v>-2.103E-2</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.25">
@@ -8052,7 +8052,7 @@
         <v>-9.9992199999999993</v>
       </c>
       <c r="B967">
-        <v>-1.17E-2</v>
+        <v>-2.0670000000000001E-2</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.25">
@@ -8060,7 +8060,7 @@
         <v>-9.8432399999999998</v>
       </c>
       <c r="B968">
-        <v>-1.013E-2</v>
+        <v>-2.035E-2</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.25">
@@ -8068,7 +8068,7 @@
         <v>-9.6872500000000006</v>
       </c>
       <c r="B969">
-        <v>-6.79E-3</v>
+        <v>-2.002E-2</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.25">
@@ -8076,7 +8076,7 @@
         <v>-9.5312699999999992</v>
       </c>
       <c r="B970" s="1">
-        <v>-7.4410199999999996E-4</v>
+        <v>-1.9730000000000001E-2</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.25">
@@ -8084,7 +8084,7 @@
         <v>-9.3752899999999997</v>
       </c>
       <c r="B971" s="1">
-        <v>-1.13158E-4</v>
+        <v>-1.934E-2</v>
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>-9.2179500000000001</v>
       </c>
       <c r="B972" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>-1.9060000000000001E-2</v>
       </c>
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.25">
@@ -8100,7 +8100,7 @@
         <v>-9.0619599999999991</v>
       </c>
       <c r="B973" s="1">
-        <v>6.5151800000000002E-5</v>
+        <v>-1.873E-2</v>
       </c>
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.25">
@@ -8108,7 +8108,7 @@
         <v>-8.9059799999999996</v>
       </c>
       <c r="B974" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-1.84E-2</v>
       </c>
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.25">
@@ -8116,7 +8116,7 @@
         <v>-8.75</v>
       </c>
       <c r="B975" s="1">
-        <v>1.71452E-5</v>
+        <v>-1.8079999999999999E-2</v>
       </c>
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.25">
@@ -8124,7 +8124,7 @@
         <v>-8.5940100000000008</v>
       </c>
       <c r="B976" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>-1.7770000000000001E-2</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.25">
@@ -8132,7 +8132,7 @@
         <v>-8.4366699999999994</v>
       </c>
       <c r="B977" s="1">
-        <v>-3.42904E-6</v>
+        <v>-1.7420000000000001E-2</v>
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.25">
@@ -8140,7 +8140,7 @@
         <v>-8.2806899999999999</v>
       </c>
       <c r="B978" s="1">
-        <v>-3.42904E-6</v>
+        <v>-1.7149999999999999E-2</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>-8.1247100000000003</v>
       </c>
       <c r="B979" s="1">
-        <v>1.71452E-5</v>
+        <v>-1.6789999999999999E-2</v>
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.25">
@@ -8156,7 +8156,7 @@
         <v>-7.9687200000000002</v>
       </c>
       <c r="B980" s="1">
-        <v>-3.42904E-6</v>
+        <v>-1.643E-2</v>
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.25">
@@ -8164,7 +8164,7 @@
         <v>-7.8127399999999998</v>
       </c>
       <c r="B981" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>-1.6160000000000001E-2</v>
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.25">
@@ -8172,7 +8172,7 @@
         <v>-7.6554000000000002</v>
       </c>
       <c r="B982" s="1">
-        <v>-3.42904E-6</v>
+        <v>-1.5820000000000001E-2</v>
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.25">
@@ -8180,7 +8180,7 @@
         <v>-7.4994199999999998</v>
       </c>
       <c r="B983" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-1.5480000000000001E-2</v>
       </c>
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.25">
@@ -8188,7 +8188,7 @@
         <v>-7.3434299999999997</v>
       </c>
       <c r="B984" s="1">
-        <v>2.7432300000000002E-5</v>
+        <v>-1.52E-2</v>
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.25">
@@ -8196,7 +8196,7 @@
         <v>-7.1874500000000001</v>
       </c>
       <c r="B985">
-        <v>0</v>
+        <v>-1.485E-2</v>
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.25">
@@ -8204,7 +8204,7 @@
         <v>-7.0314699999999997</v>
       </c>
       <c r="B986" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-1.448E-2</v>
       </c>
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.25">
@@ -8212,7 +8212,7 @@
         <v>-6.8741300000000001</v>
       </c>
       <c r="B987" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>-1.422E-2</v>
       </c>
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.25">
@@ -8220,7 +8220,7 @@
         <v>-6.71814</v>
       </c>
       <c r="B988" s="1">
-        <v>4.1148500000000001E-5</v>
+        <v>-1.389E-2</v>
       </c>
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.25">
@@ -8228,7 +8228,7 @@
         <v>-6.5621600000000004</v>
       </c>
       <c r="B989" s="1">
-        <v>1.02871E-5</v>
+        <v>-1.355E-2</v>
       </c>
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.25">
@@ -8236,7 +8236,7 @@
         <v>-6.4061700000000004</v>
       </c>
       <c r="B990">
-        <v>0</v>
+        <v>-1.3259999999999999E-2</v>
       </c>
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.25">
@@ -8244,7 +8244,7 @@
         <v>-6.2501899999999999</v>
       </c>
       <c r="B991" s="1">
-        <v>1.02871E-5</v>
+        <v>-1.289E-2</v>
       </c>
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>-6.0928500000000003</v>
       </c>
       <c r="B992" s="1">
-        <v>-1.02871E-5</v>
+        <v>-1.255E-2</v>
       </c>
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.25">
@@ -8260,7 +8260,7 @@
         <v>-5.9368699999999999</v>
       </c>
       <c r="B993" s="1">
-        <v>2.0574300000000001E-5</v>
+        <v>-1.227E-2</v>
       </c>
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.25">
@@ -8268,7 +8268,7 @@
         <v>-5.7808799999999998</v>
       </c>
       <c r="B994" s="1">
-        <v>3.7719499999999997E-5</v>
+        <v>-1.1939999999999999E-2</v>
       </c>
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.25">
@@ -8276,7 +8276,7 @@
         <v>-5.6249000000000002</v>
       </c>
       <c r="B995" s="1">
-        <v>-3.42904E-6</v>
+        <v>-1.1599999999999999E-2</v>
       </c>
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.25">
@@ -8284,7 +8284,7 @@
         <v>-5.4689199999999998</v>
       </c>
       <c r="B996" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>-1.125E-2</v>
       </c>
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.25">
@@ -8292,7 +8292,7 @@
         <v>-5.3115800000000002</v>
       </c>
       <c r="B997" s="1">
-        <v>-6.8580799999999999E-6</v>
+        <v>-1.094E-2</v>
       </c>
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.25">
@@ -8300,7 +8300,7 @@
         <v>-5.1555900000000001</v>
       </c>
       <c r="B998" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>-1.064E-2</v>
       </c>
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.25">
@@ -8308,7 +8308,7 @@
         <v>-4.9996099999999997</v>
       </c>
       <c r="B999" s="1">
-        <v>-2.4003300000000001E-5</v>
+        <v>-1.023E-2</v>
       </c>
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.25">
@@ -8316,7 +8316,7 @@
         <v>-4.8436300000000001</v>
       </c>
       <c r="B1000" s="1">
-        <v>6.8580799999999999E-6</v>
+        <v>-9.9000000000000008E-3</v>
       </c>
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.25">
@@ -8324,7 +8324,7 @@
         <v>-4.68764</v>
       </c>
       <c r="B1001" s="1">
-        <v>5.4864699999999997E-5</v>
+        <v>-9.5099999999999994E-3</v>
       </c>
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.25">
@@ -8332,7 +8332,7 @@
         <v>-4.5303000000000004</v>
       </c>
       <c r="B1002" s="1">
-        <v>-1.02871E-5</v>
+        <v>-9.0799999999999995E-3</v>
       </c>
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.25">
@@ -8340,7 +8340,7 @@
         <v>-4.37432</v>
       </c>
       <c r="B1003" s="1">
-        <v>-1.02871E-5</v>
+        <v>-8.6E-3</v>
       </c>
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.25">
@@ -8348,7 +8348,7 @@
         <v>-4.2183400000000004</v>
       </c>
       <c r="B1004" s="1">
-        <v>-1.02871E-5</v>
+        <v>-8.1399999999999997E-3</v>
       </c>
     </row>
     <row r="1005" spans="1:2" x14ac:dyDescent="0.25">
@@ -8356,7 +8356,7 @@
         <v>-4.0623500000000003</v>
       </c>
       <c r="B1005" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-7.6499999999999997E-3</v>
       </c>
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.25">
@@ -8364,7 +8364,7 @@
         <v>-3.9063699999999999</v>
       </c>
       <c r="B1006" s="1">
-        <v>3.42904E-5</v>
+        <v>-7.1300000000000001E-3</v>
       </c>
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.25">
@@ -8372,7 +8372,7 @@
         <v>-3.7490299999999999</v>
       </c>
       <c r="B1007" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-6.6600000000000001E-3</v>
       </c>
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.25">
@@ -8380,7 +8380,7 @@
         <v>-3.5930499999999999</v>
       </c>
       <c r="B1008" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>-6.2199999999999998E-3</v>
       </c>
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.25">
@@ -8388,7 +8388,7 @@
         <v>-3.4370599999999998</v>
       </c>
       <c r="B1009" s="1">
-        <v>1.71452E-5</v>
+        <v>-5.7999999999999996E-3</v>
       </c>
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.25">
@@ -8396,7 +8396,7 @@
         <v>-3.2810800000000002</v>
       </c>
       <c r="B1010" s="1">
-        <v>3.42904E-5</v>
+        <v>-5.3800000000000002E-3</v>
       </c>
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.25">
@@ -8404,7 +8404,7 @@
         <v>-3.1251000000000002</v>
       </c>
       <c r="B1011" s="1">
-        <v>-2.0574300000000001E-5</v>
+        <v>-4.9399999999999999E-3</v>
       </c>
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.25">
@@ -8412,7 +8412,7 @@
         <v>-2.9677600000000002</v>
       </c>
       <c r="B1012" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-4.5500000000000002E-3</v>
       </c>
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.25">
@@ -8420,7 +8420,7 @@
         <v>-2.8117700000000001</v>
       </c>
       <c r="B1013" s="1">
-        <v>-3.42904E-5</v>
+        <v>-4.1999999999999997E-3</v>
       </c>
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.25">
@@ -8428,7 +8428,7 @@
         <v>-2.6557900000000001</v>
       </c>
       <c r="B1014" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>-3.82E-3</v>
       </c>
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.25">
@@ -8436,7 +8436,7 @@
         <v>-2.4998100000000001</v>
       </c>
       <c r="B1015" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>-3.46E-3</v>
       </c>
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.25">
@@ -8444,7 +8444,7 @@
         <v>-2.34382</v>
       </c>
       <c r="B1016" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>-3.0699999999999998E-3</v>
       </c>
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.25">
@@ -8452,7 +8452,7 @@
         <v>-2.18648</v>
       </c>
       <c r="B1017" s="1">
-        <v>8.2297000000000002E-5</v>
+        <v>-2.7399999999999998E-3</v>
       </c>
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.25">
@@ -8460,7 +8460,7 @@
         <v>-2.0305</v>
       </c>
       <c r="B1018" s="1">
-        <v>-3.42904E-6</v>
+        <v>-2.4099999999999998E-3</v>
       </c>
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.25">
@@ -8468,7 +8468,7 @@
         <v>-1.87452</v>
       </c>
       <c r="B1019" s="1">
-        <v>4.8006600000000002E-5</v>
+        <v>-2.0899999999999998E-3</v>
       </c>
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.25">
@@ -8476,7 +8476,7 @@
         <v>-1.7185299999999999</v>
       </c>
       <c r="B1020" s="1">
-        <v>1.02871E-5</v>
+        <v>-1.72E-3</v>
       </c>
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.25">
@@ -8484,15 +8484,15 @@
         <v>-1.5625500000000001</v>
       </c>
       <c r="B1021" s="1">
-        <v>4.4577499999999998E-5</v>
+        <v>-1.39E-3</v>
       </c>
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1022">
         <v>-1.4052100000000001</v>
       </c>
-      <c r="B1022">
-        <v>0</v>
+      <c r="B1022" s="1">
+        <v>-9.8413499999999991E-4</v>
       </c>
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
         <v>-1.24922</v>
       </c>
       <c r="B1023" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>-6.72092E-4</v>
       </c>
     </row>
     <row r="1024" spans="1:2" x14ac:dyDescent="0.25">
@@ -8508,7 +8508,7 @@
         <v>-1.09324</v>
       </c>
       <c r="B1024" s="1">
-        <v>3.0861400000000002E-5</v>
+        <v>-3.4633299999999999E-4</v>
       </c>
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.25">
@@ -8516,7 +8516,7 @@
         <v>-0.93725999999999998</v>
       </c>
       <c r="B1025" s="1">
-        <v>2.4003300000000001E-5</v>
+        <v>-1.5430700000000001E-4</v>
       </c>
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.25">
@@ -8524,7 +8524,7 @@
         <v>-0.78127000000000002</v>
       </c>
       <c r="B1026" s="1">
-        <v>1.3716199999999999E-5</v>
+        <v>-1.063E-4</v>
       </c>
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.25">
@@ -8532,7 +8532,7 @@
         <v>-0.62392999999999998</v>
       </c>
       <c r="B1027" s="1">
-        <v>5.8293700000000001E-5</v>
+        <v>-6.8580799999999999E-5</v>
       </c>
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.25">
@@ -8540,7 +8540,7 @@
         <v>-0.46794999999999998</v>
       </c>
       <c r="B1028" s="1">
-        <v>3.42904E-5</v>
+        <v>-3.7719499999999997E-5</v>
       </c>
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.25">
@@ -8548,7 +8548,7 @@
         <v>-0.31197000000000003</v>
       </c>
       <c r="B1029" s="1">
-        <v>5.1435599999999999E-5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Fig.S9(a).xlsx
+++ b/Fig.S9(a).xlsx
@@ -475,7 +475,7 @@
       <c r="A20">
         <v>2.0305</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>0</v>
       </c>
     </row>
@@ -523,7 +523,7 @@
       <c r="A26">
         <v>2.9677600000000002</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <v>0</v>
       </c>
     </row>
@@ -883,7 +883,7 @@
       <c r="A71">
         <v>9.9992199999999993</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>0</v>
       </c>
     </row>
@@ -931,7 +931,7 @@
       <c r="A77">
         <v>10.93783</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77">
         <v>0</v>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       <c r="A93">
         <v>13.43764</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93">
         <v>0</v>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="A108">
         <v>15.781459999999999</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108">
         <v>1.09E-3</v>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       <c r="A110">
         <v>16.093430000000001</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110">
         <v>1.004E-2</v>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       <c r="A111">
         <v>16.249410000000001</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111">
         <v>1.553E-2</v>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       <c r="A112">
         <v>16.406749999999999</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112">
         <v>2.103E-2</v>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       <c r="A113">
         <v>16.562729999999998</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113">
         <v>2.5149999999999999E-2</v>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       <c r="A115">
         <v>16.874700000000001</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115">
         <v>3.0720000000000001E-2</v>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       <c r="A116">
         <v>17.03069</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116">
         <v>3.2370000000000003E-2</v>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       <c r="A117">
         <v>17.188020000000002</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117">
         <v>3.4090000000000002E-2</v>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       <c r="A118">
         <v>17.344010000000001</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118">
         <v>3.5200000000000002E-2</v>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       <c r="A119">
         <v>17.49999</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119">
         <v>3.5959999999999999E-2</v>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       <c r="A120">
         <v>17.65598</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120">
         <v>3.6450000000000003E-2</v>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       <c r="A121">
         <v>17.811959999999999</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121">
         <v>3.6839999999999998E-2</v>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="A122">
         <v>17.9693</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122">
         <v>3.7150000000000002E-2</v>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       <c r="A123">
         <v>18.12528</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123">
         <v>3.7420000000000002E-2</v>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       <c r="A124">
         <v>18.281269999999999</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124">
         <v>3.7780000000000001E-2</v>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       <c r="A125">
         <v>18.437249999999999</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125">
         <v>3.8129999999999997E-2</v>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       <c r="A126">
         <v>18.593229999999998</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126">
         <v>3.8460000000000001E-2</v>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       <c r="A128">
         <v>18.906559999999999</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128">
         <v>3.9070000000000001E-2</v>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="A129">
         <v>19.062539999999998</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129">
         <v>3.9469999999999998E-2</v>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       <c r="A130">
         <v>19.218520000000002</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130">
         <v>3.9730000000000001E-2</v>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       <c r="A131">
         <v>19.374510000000001</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131">
         <v>4.0090000000000001E-2</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       <c r="A133">
         <v>19.687830000000002</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133">
         <v>4.0730000000000002E-2</v>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="A134">
         <v>19.843810000000001</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134">
         <v>4.1050000000000003E-2</v>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       <c r="A135">
         <v>19.9998</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135">
         <v>4.1360000000000001E-2</v>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       <c r="A136">
         <v>20.15578</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136">
         <v>4.1709999999999997E-2</v>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       <c r="A137">
         <v>20.313120000000001</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137">
         <v>4.2040000000000001E-2</v>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       <c r="A138">
         <v>20.469100000000001</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138">
         <v>4.233E-2</v>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       <c r="A139">
         <v>20.62509</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139">
         <v>4.2630000000000001E-2</v>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       <c r="A140">
         <v>20.78107</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140">
         <v>4.2930000000000003E-2</v>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       <c r="A141">
         <v>20.937049999999999</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141">
         <v>4.3310000000000001E-2</v>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       <c r="A142">
         <v>21.094390000000001</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142">
         <v>4.3589999999999997E-2</v>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       <c r="A458">
         <v>9.5312699999999992</v>
       </c>
-      <c r="B458" s="1">
+      <c r="B458">
         <v>1.9740000000000001E-2</v>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       <c r="A459">
         <v>9.3752899999999997</v>
       </c>
-      <c r="B459" s="1">
+      <c r="B459">
         <v>1.9429999999999999E-2</v>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       <c r="A460">
         <v>9.2179500000000001</v>
       </c>
-      <c r="B460" s="1">
+      <c r="B460">
         <v>1.9120000000000002E-2</v>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       <c r="A461">
         <v>9.0619599999999991</v>
       </c>
-      <c r="B461" s="1">
+      <c r="B461">
         <v>1.8800000000000001E-2</v>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       <c r="A462">
         <v>8.9059799999999996</v>
       </c>
-      <c r="B462" s="1">
+      <c r="B462">
         <v>1.8489999999999999E-2</v>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       <c r="A463">
         <v>8.75</v>
       </c>
-      <c r="B463" s="1">
+      <c r="B463">
         <v>1.8100000000000002E-2</v>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       <c r="A464">
         <v>8.5940100000000008</v>
       </c>
-      <c r="B464" s="1">
+      <c r="B464">
         <v>1.7809999999999999E-2</v>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       <c r="A465">
         <v>8.4366699999999994</v>
       </c>
-      <c r="B465" s="1">
+      <c r="B465">
         <v>1.7489999999999999E-2</v>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       <c r="A466">
         <v>8.2806899999999999</v>
       </c>
-      <c r="B466" s="1">
+      <c r="B466">
         <v>1.7129999999999999E-2</v>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       <c r="A467">
         <v>8.1247100000000003</v>
       </c>
-      <c r="B467" s="1">
+      <c r="B467">
         <v>1.6809999999999999E-2</v>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       <c r="A469">
         <v>7.8127399999999998</v>
       </c>
-      <c r="B469" s="1">
+      <c r="B469">
         <v>1.6160000000000001E-2</v>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       <c r="A470">
         <v>7.6554000000000002</v>
       </c>
-      <c r="B470" s="1">
+      <c r="B470">
         <v>1.585E-2</v>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       <c r="A471">
         <v>7.4994199999999998</v>
       </c>
-      <c r="B471" s="1">
+      <c r="B471">
         <v>1.5559999999999999E-2</v>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       <c r="A472">
         <v>7.3434299999999997</v>
       </c>
-      <c r="B472" s="1">
+      <c r="B472">
         <v>1.5180000000000001E-2</v>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       <c r="A473">
         <v>7.1874500000000001</v>
       </c>
-      <c r="B473" s="1">
+      <c r="B473">
         <v>1.489E-2</v>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       <c r="A474">
         <v>7.0314699999999997</v>
       </c>
-      <c r="B474" s="1">
+      <c r="B474">
         <v>1.4579999999999999E-2</v>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       <c r="A475">
         <v>6.8741300000000001</v>
       </c>
-      <c r="B475" s="1">
+      <c r="B475">
         <v>1.4239999999999999E-2</v>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       <c r="A476">
         <v>6.71814</v>
       </c>
-      <c r="B476" s="1">
+      <c r="B476">
         <v>1.3950000000000001E-2</v>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       <c r="A477">
         <v>6.5621600000000004</v>
       </c>
-      <c r="B477" s="1">
+      <c r="B477">
         <v>1.359E-2</v>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       <c r="A478">
         <v>6.4061700000000004</v>
       </c>
-      <c r="B478" s="1">
+      <c r="B478">
         <v>1.3270000000000001E-2</v>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       <c r="A479">
         <v>6.2501899999999999</v>
       </c>
-      <c r="B479" s="1">
+      <c r="B479">
         <v>1.294E-2</v>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       <c r="A480">
         <v>6.0928500000000003</v>
       </c>
-      <c r="B480" s="1">
+      <c r="B480">
         <v>1.2659999999999999E-2</v>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       <c r="A481">
         <v>5.9368699999999999</v>
       </c>
-      <c r="B481" s="1">
+      <c r="B481">
         <v>1.225E-2</v>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       <c r="A482">
         <v>5.7808799999999998</v>
       </c>
-      <c r="B482" s="1">
+      <c r="B482">
         <v>1.2019999999999999E-2</v>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       <c r="A483">
         <v>5.6249000000000002</v>
       </c>
-      <c r="B483" s="1">
+      <c r="B483">
         <v>1.167E-2</v>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       <c r="A484">
         <v>5.4689199999999998</v>
       </c>
-      <c r="B484" s="1">
+      <c r="B484">
         <v>1.1310000000000001E-2</v>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       <c r="A485">
         <v>5.3115800000000002</v>
       </c>
-      <c r="B485" s="1">
+      <c r="B485">
         <v>1.103E-2</v>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       <c r="A486">
         <v>5.1555900000000001</v>
       </c>
-      <c r="B486" s="1">
+      <c r="B486">
         <v>1.064E-2</v>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       <c r="A487">
         <v>4.9996099999999997</v>
       </c>
-      <c r="B487" s="1">
+      <c r="B487">
         <v>1.0290000000000001E-2</v>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       <c r="A488">
         <v>4.8436300000000001</v>
       </c>
-      <c r="B488" s="1">
+      <c r="B488">
         <v>9.8399999999999998E-3</v>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       <c r="A489">
         <v>4.68764</v>
       </c>
-      <c r="B489" s="1">
+      <c r="B489">
         <v>9.4500000000000001E-3</v>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       <c r="A490">
         <v>4.5303000000000004</v>
       </c>
-      <c r="B490" s="1">
+      <c r="B490">
         <v>8.9499999999999996E-3</v>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       <c r="A491">
         <v>4.37432</v>
       </c>
-      <c r="B491" s="1">
+      <c r="B491">
         <v>8.4899999999999993E-3</v>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       <c r="A492">
         <v>4.2183400000000004</v>
       </c>
-      <c r="B492" s="1">
+      <c r="B492">
         <v>7.9699999999999997E-3</v>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       <c r="A493">
         <v>4.0623500000000003</v>
       </c>
-      <c r="B493" s="1">
+      <c r="B493">
         <v>7.43E-3</v>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       <c r="A494">
         <v>3.9063699999999999</v>
       </c>
-      <c r="B494" s="1">
+      <c r="B494">
         <v>6.9199999999999999E-3</v>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       <c r="A495">
         <v>3.7490299999999999</v>
       </c>
-      <c r="B495" s="1">
+      <c r="B495">
         <v>6.4900000000000001E-3</v>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       <c r="A496">
         <v>3.5930499999999999</v>
       </c>
-      <c r="B496" s="1">
+      <c r="B496">
         <v>6.0400000000000002E-3</v>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       <c r="A497">
         <v>3.4370599999999998</v>
       </c>
-      <c r="B497" s="1">
+      <c r="B497">
         <v>5.6299999999999996E-3</v>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       <c r="A498">
         <v>3.2810800000000002</v>
       </c>
-      <c r="B498" s="1">
+      <c r="B498">
         <v>5.2100000000000002E-3</v>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       <c r="A499">
         <v>3.1251000000000002</v>
       </c>
-      <c r="B499" s="1">
+      <c r="B499">
         <v>4.8399999999999997E-3</v>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       <c r="A500">
         <v>2.9677600000000002</v>
       </c>
-      <c r="B500" s="1">
+      <c r="B500">
         <v>4.4200000000000003E-3</v>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       <c r="A501">
         <v>2.8117700000000001</v>
       </c>
-      <c r="B501" s="1">
+      <c r="B501">
         <v>3.9899999999999996E-3</v>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       <c r="A502">
         <v>2.6557900000000001</v>
       </c>
-      <c r="B502" s="1">
+      <c r="B502">
         <v>3.6900000000000001E-3</v>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       <c r="A503">
         <v>2.4998100000000001</v>
       </c>
-      <c r="B503" s="1">
+      <c r="B503">
         <v>3.2699999999999999E-3</v>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       <c r="A504">
         <v>2.34382</v>
       </c>
-      <c r="B504" s="1">
+      <c r="B504">
         <v>2.9099999999999998E-3</v>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       <c r="A505">
         <v>2.18648</v>
       </c>
-      <c r="B505" s="1">
+      <c r="B505">
         <v>2.5699999999999998E-3</v>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       <c r="A506">
         <v>2.0305</v>
       </c>
-      <c r="B506" s="1">
+      <c r="B506">
         <v>2.1800000000000001E-3</v>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       <c r="A507">
         <v>1.87452</v>
       </c>
-      <c r="B507" s="1">
+      <c r="B507">
         <v>1.7899999999999999E-3</v>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       <c r="A508">
         <v>1.7185299999999999</v>
       </c>
-      <c r="B508" s="1">
+      <c r="B508">
         <v>1.4599999999999999E-3</v>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       <c r="A509">
         <v>1.5625500000000001</v>
       </c>
-      <c r="B509" s="1">
+      <c r="B509">
         <v>1.0200000000000001E-3</v>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       <c r="A532">
         <v>-2.0305</v>
       </c>
-      <c r="B532" s="1">
+      <c r="B532">
         <v>0</v>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       <c r="A548">
         <v>-4.5303000000000004</v>
       </c>
-      <c r="B548" s="1">
+      <c r="B548">
         <v>0</v>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       <c r="A554">
         <v>-5.4689199999999998</v>
       </c>
-      <c r="B554" s="1">
+      <c r="B554">
         <v>0</v>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       <c r="A566">
         <v>-7.3434299999999997</v>
       </c>
-      <c r="B566" s="1">
+      <c r="B566">
         <v>0</v>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       <c r="A579">
         <v>-9.3752899999999997</v>
       </c>
-      <c r="B579" s="1">
+      <c r="B579">
         <v>0</v>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       <c r="A584">
         <v>-10.156560000000001</v>
       </c>
-      <c r="B584" s="1">
+      <c r="B584">
         <v>0</v>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       <c r="A615">
         <v>-15.00019</v>
       </c>
-      <c r="B615" s="1">
+      <c r="B615">
         <v>-5.9899999999999997E-3</v>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       <c r="A616">
         <v>-15.156169999999999</v>
       </c>
-      <c r="B616" s="1">
+      <c r="B616">
         <v>-1.558E-2</v>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       <c r="A617">
         <v>-15.312150000000001</v>
       </c>
-      <c r="B617" s="1">
+      <c r="B617">
         <v>-2.3970000000000002E-2</v>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       <c r="A618">
         <v>-15.46814</v>
       </c>
-      <c r="B618" s="1">
+      <c r="B618">
         <v>-2.8330000000000001E-2</v>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       <c r="A619">
         <v>-15.62548</v>
       </c>
-      <c r="B619" s="1">
+      <c r="B619">
         <v>-3.0290000000000001E-2</v>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       <c r="A620">
         <v>-15.781459999999999</v>
       </c>
-      <c r="B620" s="1">
+      <c r="B620">
         <v>-3.168E-2</v>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       <c r="A621">
         <v>-15.93744</v>
       </c>
-      <c r="B621" s="1">
+      <c r="B621">
         <v>-3.2210000000000003E-2</v>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       <c r="A622">
         <v>-16.093430000000001</v>
       </c>
-      <c r="B622" s="1">
+      <c r="B622">
         <v>-3.2989999999999998E-2</v>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       <c r="A623">
         <v>-16.249410000000001</v>
       </c>
-      <c r="B623" s="1">
+      <c r="B623">
         <v>-3.3579999999999999E-2</v>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       <c r="A624">
         <v>-16.406749999999999</v>
       </c>
-      <c r="B624" s="1">
+      <c r="B624">
         <v>-3.3910000000000003E-2</v>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       <c r="A625">
         <v>-16.562729999999998</v>
       </c>
-      <c r="B625" s="1">
+      <c r="B625">
         <v>-3.4209999999999997E-2</v>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       <c r="A626">
         <v>-16.718720000000001</v>
       </c>
-      <c r="B626" s="1">
+      <c r="B626">
         <v>-3.4540000000000001E-2</v>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       <c r="A627">
         <v>-16.874700000000001</v>
       </c>
-      <c r="B627" s="1">
+      <c r="B627">
         <v>-3.4790000000000001E-2</v>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       <c r="A628">
         <v>-17.03069</v>
       </c>
-      <c r="B628" s="1">
+      <c r="B628">
         <v>-3.5130000000000002E-2</v>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       <c r="A629">
         <v>-17.188020000000002</v>
       </c>
-      <c r="B629" s="1">
+      <c r="B629">
         <v>-3.551E-2</v>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       <c r="A630">
         <v>-17.344010000000001</v>
       </c>
-      <c r="B630" s="1">
+      <c r="B630">
         <v>-3.5819999999999998E-2</v>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       <c r="A631">
         <v>-17.49999</v>
       </c>
-      <c r="B631" s="1">
+      <c r="B631">
         <v>-3.6150000000000002E-2</v>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       <c r="A632">
         <v>-17.65598</v>
       </c>
-      <c r="B632" s="1">
+      <c r="B632">
         <v>-3.6459999999999999E-2</v>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       <c r="A633">
         <v>-17.811959999999999</v>
       </c>
-      <c r="B633" s="1">
+      <c r="B633">
         <v>-3.6799999999999999E-2</v>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       <c r="A634">
         <v>-17.9693</v>
       </c>
-      <c r="B634" s="1">
+      <c r="B634">
         <v>-3.7179999999999998E-2</v>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       <c r="A635">
         <v>-18.12528</v>
       </c>
-      <c r="B635" s="1">
+      <c r="B635">
         <v>-3.7400000000000003E-2</v>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       <c r="A636">
         <v>-18.281269999999999</v>
       </c>
-      <c r="B636" s="1">
+      <c r="B636">
         <v>-3.7769999999999998E-2</v>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       <c r="A637">
         <v>-18.437249999999999</v>
       </c>
-      <c r="B637" s="1">
+      <c r="B637">
         <v>-3.8059999999999997E-2</v>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       <c r="A638">
         <v>-18.593229999999998</v>
       </c>
-      <c r="B638" s="1">
+      <c r="B638">
         <v>-3.8449999999999998E-2</v>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       <c r="A639">
         <v>-18.75057</v>
       </c>
-      <c r="B639" s="1">
+      <c r="B639">
         <v>-3.8760000000000003E-2</v>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
       <c r="A640">
         <v>-18.906559999999999</v>
       </c>
-      <c r="B640" s="1">
+      <c r="B640">
         <v>-3.909E-2</v>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       <c r="A641">
         <v>-19.062539999999998</v>
       </c>
-      <c r="B641" s="1">
+      <c r="B641">
         <v>-3.9370000000000002E-2</v>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       <c r="A642">
         <v>-19.218520000000002</v>
       </c>
-      <c r="B642" s="1">
+      <c r="B642">
         <v>-3.9730000000000001E-2</v>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       <c r="A643">
         <v>-19.374510000000001</v>
       </c>
-      <c r="B643" s="1">
+      <c r="B643">
         <v>-4.0030000000000003E-2</v>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       <c r="A644">
         <v>-19.531849999999999</v>
       </c>
-      <c r="B644" s="1">
+      <c r="B644">
         <v>-4.0349999999999997E-2</v>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       <c r="A645">
         <v>-19.687830000000002</v>
       </c>
-      <c r="B645" s="1">
+      <c r="B645">
         <v>-4.07E-2</v>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       <c r="A970">
         <v>-9.5312699999999992</v>
       </c>
-      <c r="B970" s="1">
+      <c r="B970">
         <v>-1.9730000000000001E-2</v>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       <c r="A971">
         <v>-9.3752899999999997</v>
       </c>
-      <c r="B971" s="1">
+      <c r="B971">
         <v>-1.934E-2</v>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       <c r="A972">
         <v>-9.2179500000000001</v>
       </c>
-      <c r="B972" s="1">
+      <c r="B972">
         <v>-1.9060000000000001E-2</v>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       <c r="A973">
         <v>-9.0619599999999991</v>
       </c>
-      <c r="B973" s="1">
+      <c r="B973">
         <v>-1.873E-2</v>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       <c r="A974">
         <v>-8.9059799999999996</v>
       </c>
-      <c r="B974" s="1">
+      <c r="B974">
         <v>-1.84E-2</v>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       <c r="A975">
         <v>-8.75</v>
       </c>
-      <c r="B975" s="1">
+      <c r="B975">
         <v>-1.8079999999999999E-2</v>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       <c r="A976">
         <v>-8.5940100000000008</v>
       </c>
-      <c r="B976" s="1">
+      <c r="B976">
         <v>-1.7770000000000001E-2</v>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       <c r="A977">
         <v>-8.4366699999999994</v>
       </c>
-      <c r="B977" s="1">
+      <c r="B977">
         <v>-1.7420000000000001E-2</v>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       <c r="A978">
         <v>-8.2806899999999999</v>
       </c>
-      <c r="B978" s="1">
+      <c r="B978">
         <v>-1.7149999999999999E-2</v>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       <c r="A979">
         <v>-8.1247100000000003</v>
       </c>
-      <c r="B979" s="1">
+      <c r="B979">
         <v>-1.6789999999999999E-2</v>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       <c r="A980">
         <v>-7.9687200000000002</v>
       </c>
-      <c r="B980" s="1">
+      <c r="B980">
         <v>-1.643E-2</v>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="A981">
         <v>-7.8127399999999998</v>
       </c>
-      <c r="B981" s="1">
+      <c r="B981">
         <v>-1.6160000000000001E-2</v>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       <c r="A982">
         <v>-7.6554000000000002</v>
       </c>
-      <c r="B982" s="1">
+      <c r="B982">
         <v>-1.5820000000000001E-2</v>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       <c r="A983">
         <v>-7.4994199999999998</v>
       </c>
-      <c r="B983" s="1">
+      <c r="B983">
         <v>-1.5480000000000001E-2</v>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       <c r="A984">
         <v>-7.3434299999999997</v>
       </c>
-      <c r="B984" s="1">
+      <c r="B984">
         <v>-1.52E-2</v>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       <c r="A986">
         <v>-7.0314699999999997</v>
       </c>
-      <c r="B986" s="1">
+      <c r="B986">
         <v>-1.448E-2</v>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       <c r="A987">
         <v>-6.8741300000000001</v>
       </c>
-      <c r="B987" s="1">
+      <c r="B987">
         <v>-1.422E-2</v>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       <c r="A988">
         <v>-6.71814</v>
       </c>
-      <c r="B988" s="1">
+      <c r="B988">
         <v>-1.389E-2</v>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       <c r="A989">
         <v>-6.5621600000000004</v>
       </c>
-      <c r="B989" s="1">
+      <c r="B989">
         <v>-1.355E-2</v>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       <c r="A991">
         <v>-6.2501899999999999</v>
       </c>
-      <c r="B991" s="1">
+      <c r="B991">
         <v>-1.289E-2</v>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       <c r="A992">
         <v>-6.0928500000000003</v>
       </c>
-      <c r="B992" s="1">
+      <c r="B992">
         <v>-1.255E-2</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="A993">
         <v>-5.9368699999999999</v>
       </c>
-      <c r="B993" s="1">
+      <c r="B993">
         <v>-1.227E-2</v>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       <c r="A994">
         <v>-5.7808799999999998</v>
       </c>
-      <c r="B994" s="1">
+      <c r="B994">
         <v>-1.1939999999999999E-2</v>
       </c>
     </row>
@@ -8275,7 +8275,7 @@
       <c r="A995">
         <v>-5.6249000000000002</v>
       </c>
-      <c r="B995" s="1">
+      <c r="B995">
         <v>-1.1599999999999999E-2</v>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       <c r="A996">
         <v>-5.4689199999999998</v>
       </c>
-      <c r="B996" s="1">
+      <c r="B996">
         <v>-1.125E-2</v>
       </c>
     </row>
@@ -8291,7 +8291,7 @@
       <c r="A997">
         <v>-5.3115800000000002</v>
       </c>
-      <c r="B997" s="1">
+      <c r="B997">
         <v>-1.094E-2</v>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       <c r="A998">
         <v>-5.1555900000000001</v>
       </c>
-      <c r="B998" s="1">
+      <c r="B998">
         <v>-1.064E-2</v>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       <c r="A999">
         <v>-4.9996099999999997</v>
       </c>
-      <c r="B999" s="1">
+      <c r="B999">
         <v>-1.023E-2</v>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       <c r="A1000">
         <v>-4.8436300000000001</v>
       </c>
-      <c r="B1000" s="1">
+      <c r="B1000">
         <v>-9.9000000000000008E-3</v>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       <c r="A1001">
         <v>-4.68764</v>
       </c>
-      <c r="B1001" s="1">
+      <c r="B1001">
         <v>-9.5099999999999994E-3</v>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       <c r="A1002">
         <v>-4.5303000000000004</v>
       </c>
-      <c r="B1002" s="1">
+      <c r="B1002">
         <v>-9.0799999999999995E-3</v>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       <c r="A1003">
         <v>-4.37432</v>
       </c>
-      <c r="B1003" s="1">
+      <c r="B1003">
         <v>-8.6E-3</v>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       <c r="A1004">
         <v>-4.2183400000000004</v>
       </c>
-      <c r="B1004" s="1">
+      <c r="B1004">
         <v>-8.1399999999999997E-3</v>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       <c r="A1005">
         <v>-4.0623500000000003</v>
       </c>
-      <c r="B1005" s="1">
+      <c r="B1005">
         <v>-7.6499999999999997E-3</v>
       </c>
     </row>
@@ -8363,7 +8363,7 @@
       <c r="A1006">
         <v>-3.9063699999999999</v>
       </c>
-      <c r="B1006" s="1">
+      <c r="B1006">
         <v>-7.1300000000000001E-3</v>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       <c r="A1007">
         <v>-3.7490299999999999</v>
       </c>
-      <c r="B1007" s="1">
+      <c r="B1007">
         <v>-6.6600000000000001E-3</v>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       <c r="A1008">
         <v>-3.5930499999999999</v>
       </c>
-      <c r="B1008" s="1">
+      <c r="B1008">
         <v>-6.2199999999999998E-3</v>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       <c r="A1009">
         <v>-3.4370599999999998</v>
       </c>
-      <c r="B1009" s="1">
+      <c r="B1009">
         <v>-5.7999999999999996E-3</v>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       <c r="A1010">
         <v>-3.2810800000000002</v>
       </c>
-      <c r="B1010" s="1">
+      <c r="B1010">
         <v>-5.3800000000000002E-3</v>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       <c r="A1011">
         <v>-3.1251000000000002</v>
       </c>
-      <c r="B1011" s="1">
+      <c r="B1011">
         <v>-4.9399999999999999E-3</v>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       <c r="A1012">
         <v>-2.9677600000000002</v>
       </c>
-      <c r="B1012" s="1">
+      <c r="B1012">
         <v>-4.5500000000000002E-3</v>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       <c r="A1013">
         <v>-2.8117700000000001</v>
       </c>
-      <c r="B1013" s="1">
+      <c r="B1013">
         <v>-4.1999999999999997E-3</v>
       </c>
     </row>
@@ -8427,7 +8427,7 @@
       <c r="A1014">
         <v>-2.6557900000000001</v>
       </c>
-      <c r="B1014" s="1">
+      <c r="B1014">
         <v>-3.82E-3</v>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       <c r="A1015">
         <v>-2.4998100000000001</v>
       </c>
-      <c r="B1015" s="1">
+      <c r="B1015">
         <v>-3.46E-3</v>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       <c r="A1016">
         <v>-2.34382</v>
       </c>
-      <c r="B1016" s="1">
+      <c r="B1016">
         <v>-3.0699999999999998E-3</v>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       <c r="A1017">
         <v>-2.18648</v>
       </c>
-      <c r="B1017" s="1">
+      <c r="B1017">
         <v>-2.7399999999999998E-3</v>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       <c r="A1018">
         <v>-2.0305</v>
       </c>
-      <c r="B1018" s="1">
+      <c r="B1018">
         <v>-2.4099999999999998E-3</v>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       <c r="A1019">
         <v>-1.87452</v>
       </c>
-      <c r="B1019" s="1">
+      <c r="B1019">
         <v>-2.0899999999999998E-3</v>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       <c r="A1020">
         <v>-1.7185299999999999</v>
       </c>
-      <c r="B1020" s="1">
+      <c r="B1020">
         <v>-1.72E-3</v>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       <c r="A1021">
         <v>-1.5625500000000001</v>
       </c>
-      <c r="B1021" s="1">
+      <c r="B1021">
         <v>-1.39E-3</v>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       <c r="A1029">
         <v>-0.31197000000000003</v>
       </c>
-      <c r="B1029" s="1">
+      <c r="B1029">
         <v>0</v>
       </c>
     </row>
